--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699068</v>
+        <v>123699047</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>79766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855190</v>
+        <v>854770</v>
       </c>
       <c r="R2" t="n">
-        <v>7477967</v>
+        <v>7477947</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699063</v>
+        <v>123699074</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
+        <v>82568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855109</v>
+        <v>855205</v>
       </c>
       <c r="R3" t="n">
-        <v>7478143</v>
+        <v>7477980</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699071</v>
+        <v>123699086</v>
       </c>
       <c r="B4" t="n">
-        <v>82562</v>
+        <v>79797</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855073</v>
+        <v>854738</v>
       </c>
       <c r="R4" t="n">
-        <v>7478043</v>
+        <v>7477969</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699041</v>
+        <v>123699069</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854968</v>
+        <v>855047</v>
       </c>
       <c r="R5" t="n">
-        <v>7478151</v>
+        <v>7478172</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699058</v>
+        <v>123699059</v>
       </c>
       <c r="B6" t="n">
-        <v>56683</v>
+        <v>90979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855091</v>
+        <v>855112</v>
       </c>
       <c r="R6" t="n">
-        <v>7478072</v>
+        <v>7478087</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1164,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699050</v>
+        <v>123699058</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>56689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855140</v>
+        <v>855091</v>
       </c>
       <c r="R7" t="n">
-        <v>7478022</v>
+        <v>7478072</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699046</v>
+        <v>123699042</v>
       </c>
       <c r="B8" t="n">
-        <v>79760</v>
+        <v>79863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855119</v>
+        <v>855063</v>
       </c>
       <c r="R8" t="n">
-        <v>7478027</v>
+        <v>7478073</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>79797</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R9" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699072</v>
+        <v>123699077</v>
       </c>
       <c r="B10" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855123</v>
+        <v>855121</v>
       </c>
       <c r="R10" t="n">
-        <v>7478116</v>
+        <v>7478158</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699048</v>
+        <v>123699070</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>82568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855062</v>
+        <v>855114</v>
       </c>
       <c r="R11" t="n">
-        <v>7478067</v>
+        <v>7478219</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699071</v>
       </c>
       <c r="B12" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>855073</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699082</v>
+        <v>123699051</v>
       </c>
       <c r="B13" t="n">
-        <v>79791</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855140</v>
+        <v>854961</v>
       </c>
       <c r="R13" t="n">
-        <v>7478068</v>
+        <v>7478150</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699083</v>
+        <v>123699045</v>
       </c>
       <c r="B14" t="n">
-        <v>79791</v>
+        <v>79766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855119</v>
+        <v>855058</v>
       </c>
       <c r="R14" t="n">
-        <v>7478027</v>
+        <v>7478025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699045</v>
+        <v>123699090</v>
       </c>
       <c r="B15" t="n">
-        <v>79760</v>
+        <v>79897</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855058</v>
+        <v>854901</v>
       </c>
       <c r="R15" t="n">
-        <v>7478025</v>
+        <v>7478143</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699086</v>
+        <v>123699050</v>
       </c>
       <c r="B16" t="n">
-        <v>79791</v>
+        <v>79898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>854738</v>
+        <v>855140</v>
       </c>
       <c r="R16" t="n">
-        <v>7477969</v>
+        <v>7478022</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699060</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>91001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855099</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7478014</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699074</v>
+        <v>123699046</v>
       </c>
       <c r="B18" t="n">
-        <v>82562</v>
+        <v>79766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855205</v>
+        <v>855119</v>
       </c>
       <c r="R18" t="n">
-        <v>7477980</v>
+        <v>7478027</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699073</v>
+        <v>123699044</v>
       </c>
       <c r="B19" t="n">
-        <v>82562</v>
+        <v>79766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855119</v>
+        <v>854836</v>
       </c>
       <c r="R19" t="n">
-        <v>7477995</v>
+        <v>7478088</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2497,12 +2492,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699065</v>
+        <v>123699067</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855061</v>
+        <v>855198</v>
       </c>
       <c r="R20" t="n">
-        <v>7478034</v>
+        <v>7477984</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2623,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699049</v>
+        <v>123699084</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>79797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2640,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855147</v>
+        <v>855181</v>
       </c>
       <c r="R21" t="n">
-        <v>7477980</v>
+        <v>7478022</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699066</v>
+        <v>123699089</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>79897</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,20 +2738,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2765,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855081</v>
+        <v>855063</v>
       </c>
       <c r="R22" t="n">
-        <v>7478053</v>
+        <v>7478073</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699064</v>
+        <v>123699083</v>
       </c>
       <c r="B23" t="n">
-        <v>90984</v>
+        <v>79797</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855084</v>
+        <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478212</v>
+        <v>7478027</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699041</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>56689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>854968</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478151</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3005,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699044</v>
+        <v>123699060</v>
       </c>
       <c r="B25" t="n">
-        <v>79760</v>
+        <v>90979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854836</v>
+        <v>855099</v>
       </c>
       <c r="R25" t="n">
-        <v>7478088</v>
+        <v>7478014</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3109,18 +3115,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699084</v>
+        <v>123699066</v>
       </c>
       <c r="B26" t="n">
-        <v>79791</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855181</v>
+        <v>855081</v>
       </c>
       <c r="R26" t="n">
-        <v>7478022</v>
+        <v>7478053</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699069</v>
+        <v>123699087</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>79797</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855047</v>
+        <v>854993</v>
       </c>
       <c r="R27" t="n">
-        <v>7478172</v>
+        <v>7478183</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699077</v>
+        <v>123699049</v>
       </c>
       <c r="B28" t="n">
-        <v>82562</v>
+        <v>79898</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855121</v>
+        <v>855147</v>
       </c>
       <c r="R28" t="n">
-        <v>7478158</v>
+        <v>7477980</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699089</v>
+        <v>123699073</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>82568</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R29" t="n">
-        <v>7478073</v>
+        <v>7477995</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699047</v>
+        <v>123699063</v>
       </c>
       <c r="B30" t="n">
-        <v>79760</v>
+        <v>91001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3559,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>854770</v>
+        <v>855109</v>
       </c>
       <c r="R30" t="n">
-        <v>7477947</v>
+        <v>7478143</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699067</v>
+        <v>123699065</v>
       </c>
       <c r="B31" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855198</v>
+        <v>855061</v>
       </c>
       <c r="R31" t="n">
-        <v>7477984</v>
+        <v>7478034</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699040</v>
+        <v>123699048</v>
       </c>
       <c r="B32" t="n">
-        <v>90966</v>
+        <v>79898</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855106</v>
+        <v>855062</v>
       </c>
       <c r="R32" t="n">
-        <v>7478141</v>
+        <v>7478067</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699042</v>
+        <v>123699068</v>
       </c>
       <c r="B33" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855063</v>
+        <v>855190</v>
       </c>
       <c r="R33" t="n">
-        <v>7478073</v>
+        <v>7477967</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699087</v>
+        <v>123699072</v>
       </c>
       <c r="B34" t="n">
-        <v>79791</v>
+        <v>82568</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854993</v>
+        <v>855123</v>
       </c>
       <c r="R34" t="n">
-        <v>7478183</v>
+        <v>7478116</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699051</v>
+        <v>123699040</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>90983</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854961</v>
+        <v>855106</v>
       </c>
       <c r="R35" t="n">
-        <v>7478150</v>
+        <v>7478141</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R2" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B3" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R3" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699046</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>79766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855119</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478027</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699046</v>
+        <v>123699044</v>
       </c>
       <c r="B18" t="n">
         <v>79766</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855119</v>
+        <v>854836</v>
       </c>
       <c r="R18" t="n">
-        <v>7478027</v>
+        <v>7478088</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,12 +2390,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699044</v>
+        <v>123699064</v>
       </c>
       <c r="B19" t="n">
-        <v>79766</v>
+        <v>91001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2432,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>854836</v>
+        <v>855084</v>
       </c>
       <c r="R19" t="n">
-        <v>7478088</v>
+        <v>7478212</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2492,18 +2498,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B25" t="n">
-        <v>90979</v>
+        <v>79797</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R25" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699087</v>
+        <v>123699060</v>
       </c>
       <c r="B27" t="n">
-        <v>79797</v>
+        <v>90979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854993</v>
+        <v>855099</v>
       </c>
       <c r="R27" t="n">
-        <v>7478183</v>
+        <v>7478014</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B2" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R2" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B3" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R3" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699046</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>79766</v>
+        <v>91001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855119</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7478027</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699044</v>
+        <v>123699046</v>
       </c>
       <c r="B18" t="n">
         <v>79766</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854836</v>
+        <v>855119</v>
       </c>
       <c r="R18" t="n">
-        <v>7478088</v>
+        <v>7478027</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,18 +2390,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699064</v>
+        <v>123699044</v>
       </c>
       <c r="B19" t="n">
-        <v>91001</v>
+        <v>79766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2432,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855084</v>
+        <v>854836</v>
       </c>
       <c r="R19" t="n">
-        <v>7478212</v>
+        <v>7478088</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2498,12 +2492,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699087</v>
+        <v>123699060</v>
       </c>
       <c r="B25" t="n">
-        <v>79797</v>
+        <v>90979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854993</v>
+        <v>855099</v>
       </c>
       <c r="R25" t="n">
-        <v>7478183</v>
+        <v>7478014</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B27" t="n">
-        <v>90979</v>
+        <v>79797</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R27" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R2" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B3" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R3" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699060</v>
+        <v>123699066</v>
       </c>
       <c r="B25" t="n">
-        <v>90979</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855099</v>
+        <v>855081</v>
       </c>
       <c r="R25" t="n">
-        <v>7478014</v>
+        <v>7478053</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699066</v>
+        <v>123699060</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855081</v>
+        <v>855099</v>
       </c>
       <c r="R26" t="n">
-        <v>7478053</v>
+        <v>7478014</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699074</v>
+        <v>123699071</v>
       </c>
       <c r="B2" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855205</v>
+        <v>855073</v>
       </c>
       <c r="R2" t="n">
-        <v>7477980</v>
+        <v>7478043</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699047</v>
+        <v>123699072</v>
       </c>
       <c r="B3" t="n">
-        <v>79766</v>
+        <v>82573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854770</v>
+        <v>855123</v>
       </c>
       <c r="R3" t="n">
-        <v>7477947</v>
+        <v>7478116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699086</v>
+        <v>123699090</v>
       </c>
       <c r="B4" t="n">
-        <v>79797</v>
+        <v>79902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854738</v>
+        <v>854901</v>
       </c>
       <c r="R4" t="n">
-        <v>7477969</v>
+        <v>7478143</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699069</v>
+        <v>123699050</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>79903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855047</v>
+        <v>855140</v>
       </c>
       <c r="R5" t="n">
-        <v>7478172</v>
+        <v>7478022</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699059</v>
+        <v>123699069</v>
       </c>
       <c r="B6" t="n">
-        <v>90979</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855112</v>
+        <v>855047</v>
       </c>
       <c r="R6" t="n">
-        <v>7478087</v>
+        <v>7478172</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699058</v>
+        <v>123699040</v>
       </c>
       <c r="B7" t="n">
-        <v>56689</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855091</v>
+        <v>855106</v>
       </c>
       <c r="R7" t="n">
-        <v>7478072</v>
+        <v>7478141</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699042</v>
+        <v>123699066</v>
       </c>
       <c r="B8" t="n">
-        <v>79863</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855063</v>
+        <v>855081</v>
       </c>
       <c r="R8" t="n">
-        <v>7478073</v>
+        <v>7478053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699082</v>
+        <v>123699089</v>
       </c>
       <c r="B9" t="n">
-        <v>79797</v>
+        <v>79902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855140</v>
+        <v>855063</v>
       </c>
       <c r="R9" t="n">
-        <v>7478068</v>
+        <v>7478073</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699077</v>
+        <v>123699047</v>
       </c>
       <c r="B10" t="n">
-        <v>82568</v>
+        <v>79771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855121</v>
+        <v>854770</v>
       </c>
       <c r="R10" t="n">
-        <v>7478158</v>
+        <v>7477947</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699070</v>
+        <v>123699068</v>
       </c>
       <c r="B11" t="n">
-        <v>82568</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855114</v>
+        <v>855190</v>
       </c>
       <c r="R11" t="n">
-        <v>7478219</v>
+        <v>7477967</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699071</v>
+        <v>123699087</v>
       </c>
       <c r="B12" t="n">
-        <v>82568</v>
+        <v>79802</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855073</v>
+        <v>854993</v>
       </c>
       <c r="R12" t="n">
-        <v>7478043</v>
+        <v>7478183</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699051</v>
+        <v>123699049</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>79903</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>854961</v>
+        <v>855147</v>
       </c>
       <c r="R13" t="n">
-        <v>7478150</v>
+        <v>7477980</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699045</v>
+        <v>123699077</v>
       </c>
       <c r="B14" t="n">
-        <v>79766</v>
+        <v>82573</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855058</v>
+        <v>855121</v>
       </c>
       <c r="R14" t="n">
-        <v>7478025</v>
+        <v>7478158</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699090</v>
+        <v>123699051</v>
       </c>
       <c r="B15" t="n">
-        <v>79897</v>
+        <v>79903</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854901</v>
+        <v>854961</v>
       </c>
       <c r="R15" t="n">
-        <v>7478143</v>
+        <v>7478150</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699050</v>
+        <v>123699084</v>
       </c>
       <c r="B16" t="n">
-        <v>79898</v>
+        <v>79802</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,7 +2143,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855140</v>
+        <v>855181</v>
       </c>
       <c r="R16" t="n">
         <v>7478022</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699082</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>79802</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855140</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478068</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699046</v>
+        <v>123699048</v>
       </c>
       <c r="B18" t="n">
-        <v>79766</v>
+        <v>79903</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855119</v>
+        <v>855062</v>
       </c>
       <c r="R18" t="n">
-        <v>7478027</v>
+        <v>7478067</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699044</v>
+        <v>123699083</v>
       </c>
       <c r="B19" t="n">
-        <v>79766</v>
+        <v>79802</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>854836</v>
+        <v>855119</v>
       </c>
       <c r="R19" t="n">
-        <v>7478088</v>
+        <v>7478027</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2492,18 +2487,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699067</v>
+        <v>123699086</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>79802</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2534,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855198</v>
+        <v>854738</v>
       </c>
       <c r="R20" t="n">
-        <v>7477984</v>
+        <v>7477969</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2624,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B21" t="n">
-        <v>79797</v>
+        <v>82573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2636,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R21" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699089</v>
+        <v>123699058</v>
       </c>
       <c r="B22" t="n">
-        <v>79897</v>
+        <v>56692</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2738,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R22" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2802,6 +2791,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699083</v>
+        <v>123699073</v>
       </c>
       <c r="B23" t="n">
-        <v>79797</v>
+        <v>82573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2840,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,7 +2865,7 @@
         <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478027</v>
+        <v>7477995</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699041</v>
+        <v>123699063</v>
       </c>
       <c r="B24" t="n">
-        <v>56689</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854968</v>
+        <v>855109</v>
       </c>
       <c r="R24" t="n">
-        <v>7478151</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,11 +3000,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699066</v>
+        <v>123699042</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>79868</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855081</v>
+        <v>855063</v>
       </c>
       <c r="R25" t="n">
-        <v>7478053</v>
+        <v>7478073</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699060</v>
+        <v>123699059</v>
       </c>
       <c r="B26" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855099</v>
+        <v>855112</v>
       </c>
       <c r="R26" t="n">
-        <v>7478014</v>
+        <v>7478087</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699087</v>
+        <v>123699065</v>
       </c>
       <c r="B27" t="n">
-        <v>79797</v>
+        <v>78786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854993</v>
+        <v>855061</v>
       </c>
       <c r="R27" t="n">
-        <v>7478183</v>
+        <v>7478034</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699049</v>
+        <v>123699044</v>
       </c>
       <c r="B28" t="n">
-        <v>79898</v>
+        <v>79771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855147</v>
+        <v>854836</v>
       </c>
       <c r="R28" t="n">
-        <v>7477980</v>
+        <v>7478088</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3421,12 +3410,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3445,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699073</v>
+        <v>123699070</v>
       </c>
       <c r="B29" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855119</v>
+        <v>855114</v>
       </c>
       <c r="R29" t="n">
-        <v>7477995</v>
+        <v>7478219</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699063</v>
+        <v>123699045</v>
       </c>
       <c r="B30" t="n">
-        <v>91001</v>
+        <v>79771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3554,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855109</v>
+        <v>855058</v>
       </c>
       <c r="R30" t="n">
-        <v>7478143</v>
+        <v>7478025</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699065</v>
+        <v>123699046</v>
       </c>
       <c r="B31" t="n">
-        <v>78781</v>
+        <v>79771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3656,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855061</v>
+        <v>855119</v>
       </c>
       <c r="R31" t="n">
-        <v>7478034</v>
+        <v>7478027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3746,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699048</v>
+        <v>123699067</v>
       </c>
       <c r="B32" t="n">
-        <v>79898</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3758,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855062</v>
+        <v>855198</v>
       </c>
       <c r="R32" t="n">
-        <v>7478067</v>
+        <v>7477984</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3848,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699068</v>
+        <v>123699041</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
+        <v>56692</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3864,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3888,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855190</v>
+        <v>854968</v>
       </c>
       <c r="R33" t="n">
-        <v>7477967</v>
+        <v>7478151</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699072</v>
+        <v>123699060</v>
       </c>
       <c r="B34" t="n">
-        <v>82568</v>
+        <v>90984</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855123</v>
+        <v>855099</v>
       </c>
       <c r="R34" t="n">
-        <v>7478116</v>
+        <v>7478014</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699040</v>
+        <v>123699064</v>
       </c>
       <c r="B35" t="n">
-        <v>90983</v>
+        <v>91006</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855106</v>
+        <v>855084</v>
       </c>
       <c r="R35" t="n">
-        <v>7478141</v>
+        <v>7478212</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699071</v>
+        <v>123699069</v>
       </c>
       <c r="B2" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855073</v>
+        <v>855047</v>
       </c>
       <c r="R2" t="n">
-        <v>7478043</v>
+        <v>7478172</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699072</v>
+        <v>123699044</v>
       </c>
       <c r="B3" t="n">
-        <v>82573</v>
+        <v>79773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855123</v>
+        <v>854836</v>
       </c>
       <c r="R3" t="n">
-        <v>7478116</v>
+        <v>7478088</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +855,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699090</v>
+        <v>123699041</v>
       </c>
       <c r="B4" t="n">
-        <v>79902</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +897,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854901</v>
+        <v>854968</v>
       </c>
       <c r="R4" t="n">
-        <v>7478143</v>
+        <v>7478151</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,6 +961,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699050</v>
+        <v>123699073</v>
       </c>
       <c r="B5" t="n">
-        <v>79903</v>
+        <v>82575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1004,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R5" t="n">
-        <v>7478022</v>
+        <v>7477995</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699069</v>
+        <v>123699071</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>82575</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855047</v>
+        <v>855073</v>
       </c>
       <c r="R6" t="n">
-        <v>7478172</v>
+        <v>7478043</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699040</v>
+        <v>123699059</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855106</v>
+        <v>855112</v>
       </c>
       <c r="R7" t="n">
-        <v>7478141</v>
+        <v>7478087</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699066</v>
+        <v>123699065</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855081</v>
+        <v>855061</v>
       </c>
       <c r="R8" t="n">
-        <v>7478053</v>
+        <v>7478034</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699089</v>
+        <v>123699074</v>
       </c>
       <c r="B9" t="n">
-        <v>79902</v>
+        <v>82575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1412,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855063</v>
+        <v>855205</v>
       </c>
       <c r="R9" t="n">
-        <v>7478073</v>
+        <v>7477980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699047</v>
+        <v>123699051</v>
       </c>
       <c r="B10" t="n">
-        <v>79771</v>
+        <v>79905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854770</v>
+        <v>854961</v>
       </c>
       <c r="R10" t="n">
-        <v>7477947</v>
+        <v>7478150</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699068</v>
+        <v>123699089</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>79904</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,20 +1616,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1633,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855190</v>
+        <v>855063</v>
       </c>
       <c r="R11" t="n">
-        <v>7477967</v>
+        <v>7478073</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699087</v>
+        <v>123699067</v>
       </c>
       <c r="B12" t="n">
-        <v>79802</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1718,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>854993</v>
+        <v>855198</v>
       </c>
       <c r="R12" t="n">
-        <v>7478183</v>
+        <v>7477984</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699049</v>
+        <v>123699058</v>
       </c>
       <c r="B13" t="n">
-        <v>79903</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855147</v>
+        <v>855091</v>
       </c>
       <c r="R13" t="n">
-        <v>7477980</v>
+        <v>7478072</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1873,6 +1884,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699077</v>
+        <v>123699042</v>
       </c>
       <c r="B14" t="n">
-        <v>82573</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855121</v>
+        <v>855063</v>
       </c>
       <c r="R14" t="n">
-        <v>7478158</v>
+        <v>7478073</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699051</v>
+        <v>123699047</v>
       </c>
       <c r="B15" t="n">
-        <v>79903</v>
+        <v>79773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854961</v>
+        <v>854770</v>
       </c>
       <c r="R15" t="n">
-        <v>7478150</v>
+        <v>7477947</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699084</v>
+        <v>123699040</v>
       </c>
       <c r="B16" t="n">
-        <v>79802</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855181</v>
+        <v>855106</v>
       </c>
       <c r="R16" t="n">
-        <v>7478022</v>
+        <v>7478141</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699082</v>
+        <v>123699049</v>
       </c>
       <c r="B17" t="n">
-        <v>79802</v>
+        <v>79905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2237,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855140</v>
+        <v>855147</v>
       </c>
       <c r="R17" t="n">
-        <v>7478068</v>
+        <v>7477980</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699048</v>
+        <v>123699086</v>
       </c>
       <c r="B18" t="n">
-        <v>79903</v>
+        <v>79804</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855062</v>
+        <v>854738</v>
       </c>
       <c r="R18" t="n">
-        <v>7478067</v>
+        <v>7477969</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699083</v>
+        <v>123699068</v>
       </c>
       <c r="B19" t="n">
-        <v>79802</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2437,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R19" t="n">
-        <v>7478027</v>
+        <v>7477967</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699086</v>
+        <v>123699060</v>
       </c>
       <c r="B20" t="n">
-        <v>79802</v>
+        <v>90986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>854738</v>
+        <v>855099</v>
       </c>
       <c r="R20" t="n">
-        <v>7477969</v>
+        <v>7478014</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699074</v>
+        <v>123699082</v>
       </c>
       <c r="B21" t="n">
-        <v>82573</v>
+        <v>79804</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855205</v>
+        <v>855140</v>
       </c>
       <c r="R21" t="n">
-        <v>7477980</v>
+        <v>7478068</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699058</v>
+        <v>123699084</v>
       </c>
       <c r="B22" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2743,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855091</v>
+        <v>855181</v>
       </c>
       <c r="R22" t="n">
-        <v>7478072</v>
+        <v>7478022</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,11 +2807,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699073</v>
+        <v>123699077</v>
       </c>
       <c r="B23" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855119</v>
+        <v>855121</v>
       </c>
       <c r="R23" t="n">
-        <v>7477995</v>
+        <v>7478158</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699063</v>
+        <v>123699066</v>
       </c>
       <c r="B24" t="n">
-        <v>91006</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2951,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2975,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855109</v>
+        <v>855081</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478053</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699042</v>
+        <v>123699048</v>
       </c>
       <c r="B25" t="n">
-        <v>79868</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855063</v>
+        <v>855062</v>
       </c>
       <c r="R25" t="n">
-        <v>7478073</v>
+        <v>7478067</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699059</v>
+        <v>123699070</v>
       </c>
       <c r="B26" t="n">
-        <v>90984</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3155,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855112</v>
+        <v>855114</v>
       </c>
       <c r="R26" t="n">
-        <v>7478087</v>
+        <v>7478219</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3230,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699065</v>
+        <v>123699046</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>79773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855061</v>
+        <v>855119</v>
       </c>
       <c r="R27" t="n">
-        <v>7478034</v>
+        <v>7478027</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699044</v>
+        <v>123699072</v>
       </c>
       <c r="B28" t="n">
-        <v>79771</v>
+        <v>82575</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>854836</v>
+        <v>855123</v>
       </c>
       <c r="R28" t="n">
-        <v>7478088</v>
+        <v>7478116</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3410,18 +3421,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3440,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699070</v>
+        <v>123699064</v>
       </c>
       <c r="B29" t="n">
-        <v>82573</v>
+        <v>91008</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,21 +3461,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855114</v>
+        <v>855084</v>
       </c>
       <c r="R29" t="n">
-        <v>7478219</v>
+        <v>7478212</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3545,7 +3550,7 @@
         <v>123699045</v>
       </c>
       <c r="B30" t="n">
-        <v>79771</v>
+        <v>79773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699046</v>
+        <v>123699050</v>
       </c>
       <c r="B31" t="n">
-        <v>79771</v>
+        <v>79905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3684,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R31" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3746,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699067</v>
+        <v>123699087</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>79804</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3758,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855198</v>
+        <v>854993</v>
       </c>
       <c r="R32" t="n">
-        <v>7477984</v>
+        <v>7478183</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3848,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699041</v>
+        <v>123699083</v>
       </c>
       <c r="B33" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3860,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3888,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>854968</v>
+        <v>855119</v>
       </c>
       <c r="R33" t="n">
-        <v>7478151</v>
+        <v>7478027</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699060</v>
+        <v>123699063</v>
       </c>
       <c r="B34" t="n">
-        <v>90984</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855099</v>
+        <v>855109</v>
       </c>
       <c r="R34" t="n">
-        <v>7478014</v>
+        <v>7478143</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699064</v>
+        <v>123699090</v>
       </c>
       <c r="B35" t="n">
-        <v>91006</v>
+        <v>79904</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855084</v>
+        <v>854901</v>
       </c>
       <c r="R35" t="n">
-        <v>7478212</v>
+        <v>7478143</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699069</v>
+        <v>123699044</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855047</v>
+        <v>854836</v>
       </c>
       <c r="R2" t="n">
-        <v>7478172</v>
+        <v>7478088</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,12 +753,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699044</v>
+        <v>123699069</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +795,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854836</v>
+        <v>855047</v>
       </c>
       <c r="R3" t="n">
-        <v>7478088</v>
+        <v>7478172</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,18 +861,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699074</v>
+        <v>123699051</v>
       </c>
       <c r="B9" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855205</v>
+        <v>854961</v>
       </c>
       <c r="R9" t="n">
-        <v>7477980</v>
+        <v>7478150</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699051</v>
+        <v>123699074</v>
       </c>
       <c r="B10" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,25 +1514,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854961</v>
+        <v>855205</v>
       </c>
       <c r="R10" t="n">
-        <v>7478150</v>
+        <v>7477980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699058</v>
+        <v>123699047</v>
       </c>
       <c r="B13" t="n">
-        <v>56692</v>
+        <v>79773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1820,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855091</v>
+        <v>854770</v>
       </c>
       <c r="R13" t="n">
-        <v>7478072</v>
+        <v>7477947</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1884,11 +1884,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699042</v>
+        <v>123699058</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>56692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R14" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1991,6 +1986,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699047</v>
+        <v>123699042</v>
       </c>
       <c r="B15" t="n">
-        <v>79773</v>
+        <v>79870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,25 +2029,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854770</v>
+        <v>855063</v>
       </c>
       <c r="R15" t="n">
-        <v>7477947</v>
+        <v>7478073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699068</v>
+        <v>123699060</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855190</v>
+        <v>855099</v>
       </c>
       <c r="R19" t="n">
-        <v>7477967</v>
+        <v>7478014</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699060</v>
+        <v>123699068</v>
       </c>
       <c r="B20" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855099</v>
+        <v>855190</v>
       </c>
       <c r="R20" t="n">
-        <v>7478014</v>
+        <v>7477967</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699063</v>
+        <v>123699090</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>79904</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855109</v>
+        <v>854901</v>
       </c>
       <c r="R34" t="n">
         <v>7478143</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699090</v>
+        <v>123699063</v>
       </c>
       <c r="B35" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854901</v>
+        <v>855109</v>
       </c>
       <c r="R35" t="n">
         <v>7478143</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699060</v>
+        <v>123699068</v>
       </c>
       <c r="B19" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855099</v>
+        <v>855190</v>
       </c>
       <c r="R19" t="n">
-        <v>7478014</v>
+        <v>7477967</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699068</v>
+        <v>123699060</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855190</v>
+        <v>855099</v>
       </c>
       <c r="R20" t="n">
-        <v>7477967</v>
+        <v>7478014</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699069</v>
+        <v>123699040</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855047</v>
+        <v>855106</v>
       </c>
       <c r="R3" t="n">
-        <v>7478172</v>
+        <v>7478141</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699041</v>
+        <v>123699065</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854968</v>
+        <v>855061</v>
       </c>
       <c r="R4" t="n">
-        <v>7478151</v>
+        <v>7478034</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -961,11 +961,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699073</v>
+        <v>123699064</v>
       </c>
       <c r="B5" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855119</v>
+        <v>855084</v>
       </c>
       <c r="R5" t="n">
-        <v>7477995</v>
+        <v>7478212</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1094,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699071</v>
+        <v>123699059</v>
       </c>
       <c r="B6" t="n">
-        <v>82575</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855073</v>
+        <v>855112</v>
       </c>
       <c r="R6" t="n">
-        <v>7478043</v>
+        <v>7478087</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,25 +1203,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R7" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1298,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699065</v>
+        <v>123699047</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1310,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855061</v>
+        <v>854770</v>
       </c>
       <c r="R8" t="n">
-        <v>7478034</v>
+        <v>7477947</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1502,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699074</v>
+        <v>123699087</v>
       </c>
       <c r="B10" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,25 +1509,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855205</v>
+        <v>854993</v>
       </c>
       <c r="R10" t="n">
-        <v>7477980</v>
+        <v>7478183</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1604,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699089</v>
+        <v>123699046</v>
       </c>
       <c r="B11" t="n">
-        <v>79904</v>
+        <v>79773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R11" t="n">
-        <v>7478073</v>
+        <v>7478027</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1808,7 +1803,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699047</v>
+        <v>123699045</v>
       </c>
       <c r="B13" t="n">
         <v>79773</v>
@@ -1848,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>854770</v>
+        <v>855058</v>
       </c>
       <c r="R13" t="n">
-        <v>7477947</v>
+        <v>7478025</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1910,7 +1905,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699058</v>
+        <v>123699041</v>
       </c>
       <c r="B14" t="n">
         <v>56692</v>
@@ -1950,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855091</v>
+        <v>854968</v>
       </c>
       <c r="R14" t="n">
-        <v>7478072</v>
+        <v>7478151</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1990,7 +1985,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Adult 1</t>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699042</v>
+        <v>123699058</v>
       </c>
       <c r="B15" t="n">
-        <v>79870</v>
+        <v>56692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R15" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2093,6 +2088,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699040</v>
+        <v>123699060</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>90986</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855106</v>
+        <v>855099</v>
       </c>
       <c r="R16" t="n">
-        <v>7478141</v>
+        <v>7478014</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699049</v>
+        <v>123699074</v>
       </c>
       <c r="B17" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855147</v>
+        <v>855205</v>
       </c>
       <c r="R17" t="n">
         <v>7477980</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699068</v>
+        <v>123699089</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,20 +2437,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855190</v>
+        <v>855063</v>
       </c>
       <c r="R19" t="n">
-        <v>7477967</v>
+        <v>7478073</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699060</v>
+        <v>123699084</v>
       </c>
       <c r="B20" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855099</v>
+        <v>855181</v>
       </c>
       <c r="R20" t="n">
-        <v>7478014</v>
+        <v>7478022</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699082</v>
+        <v>123699073</v>
       </c>
       <c r="B21" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R21" t="n">
-        <v>7478068</v>
+        <v>7477995</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699084</v>
+        <v>123699066</v>
       </c>
       <c r="B22" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855181</v>
+        <v>855081</v>
       </c>
       <c r="R22" t="n">
-        <v>7478022</v>
+        <v>7478053</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699077</v>
+        <v>123699042</v>
       </c>
       <c r="B23" t="n">
-        <v>82575</v>
+        <v>79870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,21 +2849,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855121</v>
+        <v>855063</v>
       </c>
       <c r="R23" t="n">
-        <v>7478158</v>
+        <v>7478073</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699066</v>
+        <v>123699090</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2947,20 +2947,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855081</v>
+        <v>854901</v>
       </c>
       <c r="R24" t="n">
-        <v>7478053</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699048</v>
+        <v>123699072</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855062</v>
+        <v>855123</v>
       </c>
       <c r="R25" t="n">
-        <v>7478067</v>
+        <v>7478116</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699070</v>
+        <v>123699048</v>
       </c>
       <c r="B26" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855114</v>
+        <v>855062</v>
       </c>
       <c r="R26" t="n">
-        <v>7478219</v>
+        <v>7478067</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699046</v>
+        <v>123699069</v>
       </c>
       <c r="B27" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855119</v>
+        <v>855047</v>
       </c>
       <c r="R27" t="n">
-        <v>7478027</v>
+        <v>7478172</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699072</v>
+        <v>123699049</v>
       </c>
       <c r="B28" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855123</v>
+        <v>855147</v>
       </c>
       <c r="R28" t="n">
-        <v>7478116</v>
+        <v>7477980</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699064</v>
+        <v>123699050</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>79905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855084</v>
+        <v>855140</v>
       </c>
       <c r="R29" t="n">
-        <v>7478212</v>
+        <v>7478022</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699045</v>
+        <v>123699077</v>
       </c>
       <c r="B30" t="n">
-        <v>79773</v>
+        <v>82575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3559,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855058</v>
+        <v>855121</v>
       </c>
       <c r="R30" t="n">
-        <v>7478025</v>
+        <v>7478158</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699050</v>
+        <v>123699083</v>
       </c>
       <c r="B31" t="n">
-        <v>79905</v>
+        <v>79804</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R31" t="n">
-        <v>7478022</v>
+        <v>7478027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699087</v>
+        <v>123699068</v>
       </c>
       <c r="B32" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>854993</v>
+        <v>855190</v>
       </c>
       <c r="R32" t="n">
-        <v>7478183</v>
+        <v>7477967</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699083</v>
+        <v>123699070</v>
       </c>
       <c r="B33" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3865,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855119</v>
+        <v>855114</v>
       </c>
       <c r="R33" t="n">
-        <v>7478027</v>
+        <v>7478219</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699090</v>
+        <v>123699071</v>
       </c>
       <c r="B34" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854901</v>
+        <v>855073</v>
       </c>
       <c r="R34" t="n">
-        <v>7478143</v>
+        <v>7478043</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,25 +1101,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R6" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699082</v>
+        <v>123699059</v>
       </c>
       <c r="B7" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,25 +1203,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R7" t="n">
-        <v>7478068</v>
+        <v>7478087</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1803,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699045</v>
+        <v>123699060</v>
       </c>
       <c r="B13" t="n">
-        <v>79773</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,25 +1815,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855058</v>
+        <v>855099</v>
       </c>
       <c r="R13" t="n">
-        <v>7478025</v>
+        <v>7478014</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699041</v>
+        <v>123699045</v>
       </c>
       <c r="B14" t="n">
-        <v>56692</v>
+        <v>79773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,25 +1917,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>854968</v>
+        <v>855058</v>
       </c>
       <c r="R14" t="n">
-        <v>7478151</v>
+        <v>7478025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1981,11 +1981,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2007,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699058</v>
+        <v>123699041</v>
       </c>
       <c r="B15" t="n">
         <v>56692</v>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855091</v>
+        <v>854968</v>
       </c>
       <c r="R15" t="n">
-        <v>7478072</v>
+        <v>7478151</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Adult 1</t>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699060</v>
+        <v>123699058</v>
       </c>
       <c r="B16" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2130,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855099</v>
+        <v>855091</v>
       </c>
       <c r="R16" t="n">
-        <v>7478014</v>
+        <v>7478072</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2195,6 +2190,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699084</v>
+        <v>123699073</v>
       </c>
       <c r="B20" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855181</v>
+        <v>855119</v>
       </c>
       <c r="R20" t="n">
-        <v>7478022</v>
+        <v>7477995</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699073</v>
+        <v>123699084</v>
       </c>
       <c r="B21" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855119</v>
+        <v>855181</v>
       </c>
       <c r="R21" t="n">
-        <v>7477995</v>
+        <v>7478022</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699048</v>
+        <v>123699069</v>
       </c>
       <c r="B26" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855062</v>
+        <v>855047</v>
       </c>
       <c r="R26" t="n">
-        <v>7478067</v>
+        <v>7478172</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699069</v>
+        <v>123699048</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855047</v>
+        <v>855062</v>
       </c>
       <c r="R27" t="n">
-        <v>7478172</v>
+        <v>7478067</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699083</v>
+        <v>123699068</v>
       </c>
       <c r="B31" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3661,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R31" t="n">
-        <v>7478027</v>
+        <v>7477967</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699068</v>
+        <v>123699083</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855190</v>
+        <v>855119</v>
       </c>
       <c r="R32" t="n">
-        <v>7477967</v>
+        <v>7478027</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699044</v>
+        <v>123699087</v>
       </c>
       <c r="B2" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854836</v>
+        <v>854993</v>
       </c>
       <c r="R2" t="n">
-        <v>7478088</v>
+        <v>7478183</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,18 +753,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699040</v>
+        <v>123699058</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855106</v>
+        <v>855091</v>
       </c>
       <c r="R3" t="n">
-        <v>7478141</v>
+        <v>7478072</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -859,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699065</v>
+        <v>123699045</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855061</v>
+        <v>855058</v>
       </c>
       <c r="R4" t="n">
-        <v>7478034</v>
+        <v>7478025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699064</v>
+        <v>123699090</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>79904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855084</v>
+        <v>854901</v>
       </c>
       <c r="R5" t="n">
-        <v>7478212</v>
+        <v>7478143</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1089,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699082</v>
+        <v>123699042</v>
       </c>
       <c r="B6" t="n">
-        <v>79804</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6457</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855140</v>
+        <v>855063</v>
       </c>
       <c r="R6" t="n">
-        <v>7478068</v>
+        <v>7478073</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699059</v>
+        <v>123699069</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855112</v>
+        <v>855047</v>
       </c>
       <c r="R7" t="n">
-        <v>7478087</v>
+        <v>7478172</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699047</v>
+        <v>123699065</v>
       </c>
       <c r="B8" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>854770</v>
+        <v>855061</v>
       </c>
       <c r="R8" t="n">
-        <v>7477947</v>
+        <v>7478034</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1395,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699051</v>
+        <v>123699050</v>
       </c>
       <c r="B9" t="n">
         <v>79905</v>
@@ -1435,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>854961</v>
+        <v>855140</v>
       </c>
       <c r="R9" t="n">
-        <v>7478150</v>
+        <v>7478022</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1497,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699087</v>
+        <v>123699086</v>
       </c>
       <c r="B10" t="n">
         <v>79804</v>
@@ -1537,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854993</v>
+        <v>854738</v>
       </c>
       <c r="R10" t="n">
-        <v>7478183</v>
+        <v>7477969</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699046</v>
+        <v>123699049</v>
       </c>
       <c r="B11" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R11" t="n">
-        <v>7478027</v>
+        <v>7477980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1701,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699067</v>
+        <v>123699070</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855198</v>
+        <v>855114</v>
       </c>
       <c r="R12" t="n">
-        <v>7477984</v>
+        <v>7478219</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1803,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699060</v>
+        <v>123699048</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>79905</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855099</v>
+        <v>855062</v>
       </c>
       <c r="R13" t="n">
-        <v>7478014</v>
+        <v>7478067</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1905,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699045</v>
+        <v>123699051</v>
       </c>
       <c r="B14" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855058</v>
+        <v>854961</v>
       </c>
       <c r="R14" t="n">
-        <v>7478025</v>
+        <v>7478150</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2007,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699041</v>
+        <v>123699089</v>
       </c>
       <c r="B15" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2019,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854968</v>
+        <v>855063</v>
       </c>
       <c r="R15" t="n">
-        <v>7478151</v>
+        <v>7478073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2083,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2114,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699058</v>
+        <v>123699083</v>
       </c>
       <c r="B16" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2126,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2154,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855091</v>
+        <v>855119</v>
       </c>
       <c r="R16" t="n">
-        <v>7478072</v>
+        <v>7478027</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2190,11 +2184,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2221,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699074</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855205</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7477980</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2323,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699086</v>
+        <v>123699044</v>
       </c>
       <c r="B18" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854738</v>
+        <v>854836</v>
       </c>
       <c r="R18" t="n">
-        <v>7477969</v>
+        <v>7478088</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2401,12 +2390,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699089</v>
+        <v>123699084</v>
       </c>
       <c r="B19" t="n">
-        <v>79904</v>
+        <v>79804</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2436,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855063</v>
+        <v>855181</v>
       </c>
       <c r="R19" t="n">
-        <v>7478073</v>
+        <v>7478022</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699073</v>
+        <v>123699040</v>
       </c>
       <c r="B20" t="n">
-        <v>82575</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2538,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855119</v>
+        <v>855106</v>
       </c>
       <c r="R20" t="n">
-        <v>7477995</v>
+        <v>7478141</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699084</v>
+        <v>123699072</v>
       </c>
       <c r="B21" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2636,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855181</v>
+        <v>855123</v>
       </c>
       <c r="R21" t="n">
-        <v>7478022</v>
+        <v>7478116</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2731,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699066</v>
+        <v>123699073</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855081</v>
+        <v>855119</v>
       </c>
       <c r="R22" t="n">
-        <v>7478053</v>
+        <v>7477995</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2833,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699042</v>
+        <v>123699046</v>
       </c>
       <c r="B23" t="n">
-        <v>79870</v>
+        <v>79773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2845,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478073</v>
+        <v>7478027</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699063</v>
       </c>
       <c r="B24" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2947,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>855109</v>
       </c>
       <c r="R24" t="n">
         <v>7478143</v>
@@ -3037,7 +3032,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699072</v>
+        <v>123699077</v>
       </c>
       <c r="B25" t="n">
         <v>82575</v>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855123</v>
+        <v>855121</v>
       </c>
       <c r="R25" t="n">
-        <v>7478116</v>
+        <v>7478158</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699069</v>
+        <v>123699074</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,21 +3150,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855047</v>
+        <v>855205</v>
       </c>
       <c r="R26" t="n">
-        <v>7478172</v>
+        <v>7477980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3236,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699048</v>
+        <v>123699047</v>
       </c>
       <c r="B27" t="n">
-        <v>79905</v>
+        <v>79773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,21 +3252,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855062</v>
+        <v>854770</v>
       </c>
       <c r="R27" t="n">
-        <v>7478067</v>
+        <v>7477947</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3338,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699049</v>
+        <v>123699067</v>
       </c>
       <c r="B28" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3350,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855147</v>
+        <v>855198</v>
       </c>
       <c r="R28" t="n">
-        <v>7477980</v>
+        <v>7477984</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699050</v>
+        <v>123699059</v>
       </c>
       <c r="B29" t="n">
-        <v>79905</v>
+        <v>90986</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3452,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R29" t="n">
-        <v>7478022</v>
+        <v>7478087</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699077</v>
+        <v>123699041</v>
       </c>
       <c r="B30" t="n">
-        <v>82575</v>
+        <v>56692</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,21 +3558,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855121</v>
+        <v>854968</v>
       </c>
       <c r="R30" t="n">
-        <v>7478158</v>
+        <v>7478151</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3623,6 +3618,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699068</v>
+        <v>123699071</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855190</v>
+        <v>855073</v>
       </c>
       <c r="R31" t="n">
-        <v>7477967</v>
+        <v>7478043</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699083</v>
+        <v>123699060</v>
       </c>
       <c r="B32" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855119</v>
+        <v>855099</v>
       </c>
       <c r="R32" t="n">
-        <v>7478027</v>
+        <v>7478014</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699070</v>
+        <v>123699066</v>
       </c>
       <c r="B33" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855114</v>
+        <v>855081</v>
       </c>
       <c r="R33" t="n">
-        <v>7478219</v>
+        <v>7478053</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699071</v>
+        <v>123699068</v>
       </c>
       <c r="B34" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855073</v>
+        <v>855190</v>
       </c>
       <c r="R34" t="n">
-        <v>7478043</v>
+        <v>7477967</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699063</v>
+        <v>123699082</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>79804</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855109</v>
+        <v>855140</v>
       </c>
       <c r="R35" t="n">
-        <v>7478143</v>
+        <v>7478068</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699087</v>
+        <v>123699059</v>
       </c>
       <c r="B2" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854993</v>
+        <v>855112</v>
       </c>
       <c r="R2" t="n">
-        <v>7478183</v>
+        <v>7478087</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699058</v>
+        <v>123699048</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>79905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855091</v>
+        <v>855062</v>
       </c>
       <c r="R3" t="n">
-        <v>7478072</v>
+        <v>7478067</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699045</v>
+        <v>123699064</v>
       </c>
       <c r="B4" t="n">
-        <v>79773</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855058</v>
+        <v>855084</v>
       </c>
       <c r="R4" t="n">
-        <v>7478025</v>
+        <v>7478212</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699090</v>
+        <v>123699077</v>
       </c>
       <c r="B5" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854901</v>
+        <v>855121</v>
       </c>
       <c r="R5" t="n">
-        <v>7478143</v>
+        <v>7478158</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699042</v>
+        <v>123699084</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855063</v>
+        <v>855181</v>
       </c>
       <c r="R6" t="n">
-        <v>7478073</v>
+        <v>7478022</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699069</v>
+        <v>123699072</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855047</v>
+        <v>855123</v>
       </c>
       <c r="R7" t="n">
-        <v>7478172</v>
+        <v>7478116</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699065</v>
+        <v>123699070</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855061</v>
+        <v>855114</v>
       </c>
       <c r="R8" t="n">
-        <v>7478034</v>
+        <v>7478219</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699050</v>
+        <v>123699090</v>
       </c>
       <c r="B9" t="n">
-        <v>79905</v>
+        <v>79904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855140</v>
+        <v>854901</v>
       </c>
       <c r="R9" t="n">
-        <v>7478022</v>
+        <v>7478143</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699086</v>
+        <v>123699046</v>
       </c>
       <c r="B10" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854738</v>
+        <v>855119</v>
       </c>
       <c r="R10" t="n">
-        <v>7477969</v>
+        <v>7478027</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699049</v>
+        <v>123699041</v>
       </c>
       <c r="B11" t="n">
-        <v>79905</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855147</v>
+        <v>854968</v>
       </c>
       <c r="R11" t="n">
-        <v>7477980</v>
+        <v>7478151</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699040</v>
       </c>
       <c r="B12" t="n">
-        <v>82575</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>855106</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478141</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699048</v>
+        <v>123699058</v>
       </c>
       <c r="B13" t="n">
-        <v>79905</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855062</v>
+        <v>855091</v>
       </c>
       <c r="R13" t="n">
-        <v>7478067</v>
+        <v>7478072</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1878,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699051</v>
+        <v>123699063</v>
       </c>
       <c r="B14" t="n">
-        <v>79905</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>854961</v>
+        <v>855109</v>
       </c>
       <c r="R14" t="n">
-        <v>7478150</v>
+        <v>7478143</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699089</v>
+        <v>123699049</v>
       </c>
       <c r="B15" t="n">
-        <v>79904</v>
+        <v>79905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855063</v>
+        <v>855147</v>
       </c>
       <c r="R15" t="n">
-        <v>7478073</v>
+        <v>7477980</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699083</v>
+        <v>123699050</v>
       </c>
       <c r="B16" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R16" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699069</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855047</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478172</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699044</v>
+        <v>123699089</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79904</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854836</v>
+        <v>855063</v>
       </c>
       <c r="R18" t="n">
-        <v>7478088</v>
+        <v>7478073</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,18 +2395,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B19" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2432,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R19" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2522,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699040</v>
+        <v>123699066</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855106</v>
+        <v>855081</v>
       </c>
       <c r="R20" t="n">
-        <v>7478141</v>
+        <v>7478053</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2624,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699072</v>
+        <v>123699047</v>
       </c>
       <c r="B21" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2636,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855123</v>
+        <v>854770</v>
       </c>
       <c r="R21" t="n">
-        <v>7478116</v>
+        <v>7477947</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699073</v>
+        <v>123699068</v>
       </c>
       <c r="B22" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R22" t="n">
-        <v>7477995</v>
+        <v>7477967</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699046</v>
+        <v>123699086</v>
       </c>
       <c r="B23" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855119</v>
+        <v>854738</v>
       </c>
       <c r="R23" t="n">
-        <v>7478027</v>
+        <v>7477969</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699063</v>
+        <v>123699073</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855109</v>
+        <v>855119</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7477995</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3032,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699077</v>
+        <v>123699051</v>
       </c>
       <c r="B25" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3044,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3072,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855121</v>
+        <v>854961</v>
       </c>
       <c r="R25" t="n">
-        <v>7478158</v>
+        <v>7478150</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3134,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699074</v>
+        <v>123699045</v>
       </c>
       <c r="B26" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3146,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3174,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855205</v>
+        <v>855058</v>
       </c>
       <c r="R26" t="n">
-        <v>7477980</v>
+        <v>7478025</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3236,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699047</v>
+        <v>123699044</v>
       </c>
       <c r="B27" t="n">
         <v>79773</v>
@@ -3276,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854770</v>
+        <v>854836</v>
       </c>
       <c r="R27" t="n">
-        <v>7477947</v>
+        <v>7478088</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3314,12 +3313,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3338,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699067</v>
+        <v>123699060</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,21 +3359,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855198</v>
+        <v>855099</v>
       </c>
       <c r="R28" t="n">
-        <v>7477984</v>
+        <v>7478014</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3440,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699059</v>
+        <v>123699087</v>
       </c>
       <c r="B29" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3452,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855112</v>
+        <v>854993</v>
       </c>
       <c r="R29" t="n">
-        <v>7478087</v>
+        <v>7478183</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3542,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699041</v>
+        <v>123699071</v>
       </c>
       <c r="B30" t="n">
-        <v>56692</v>
+        <v>82575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,21 +3563,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>854968</v>
+        <v>855073</v>
       </c>
       <c r="R30" t="n">
-        <v>7478151</v>
+        <v>7478043</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3618,11 +3623,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699071</v>
+        <v>123699065</v>
       </c>
       <c r="B31" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855073</v>
+        <v>855061</v>
       </c>
       <c r="R31" t="n">
-        <v>7478043</v>
+        <v>7478034</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699060</v>
+        <v>123699042</v>
       </c>
       <c r="B32" t="n">
-        <v>90986</v>
+        <v>79870</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855099</v>
+        <v>855063</v>
       </c>
       <c r="R32" t="n">
-        <v>7478014</v>
+        <v>7478073</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699066</v>
+        <v>123699082</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3865,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855081</v>
+        <v>855140</v>
       </c>
       <c r="R33" t="n">
-        <v>7478053</v>
+        <v>7478068</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699068</v>
+        <v>123699067</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855190</v>
+        <v>855198</v>
       </c>
       <c r="R34" t="n">
-        <v>7477967</v>
+        <v>7477984</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699082</v>
+        <v>123699083</v>
       </c>
       <c r="B35" t="n">
         <v>79804</v>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R35" t="n">
-        <v>7478068</v>
+        <v>7478027</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699059</v>
+        <v>123699077</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>82575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855112</v>
+        <v>855121</v>
       </c>
       <c r="R2" t="n">
-        <v>7478087</v>
+        <v>7478158</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699048</v>
+        <v>123699040</v>
       </c>
       <c r="B3" t="n">
-        <v>79905</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855062</v>
+        <v>855106</v>
       </c>
       <c r="R3" t="n">
-        <v>7478067</v>
+        <v>7478141</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699064</v>
+        <v>123699059</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855084</v>
+        <v>855112</v>
       </c>
       <c r="R4" t="n">
-        <v>7478212</v>
+        <v>7478087</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699077</v>
+        <v>123699086</v>
       </c>
       <c r="B5" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855121</v>
+        <v>854738</v>
       </c>
       <c r="R5" t="n">
-        <v>7478158</v>
+        <v>7477969</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699084</v>
+        <v>123699041</v>
       </c>
       <c r="B6" t="n">
-        <v>79804</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855181</v>
+        <v>854968</v>
       </c>
       <c r="R6" t="n">
-        <v>7478022</v>
+        <v>7478151</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699072</v>
+        <v>123699071</v>
       </c>
       <c r="B7" t="n">
         <v>82575</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855123</v>
+        <v>855073</v>
       </c>
       <c r="R7" t="n">
-        <v>7478116</v>
+        <v>7478043</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699070</v>
+        <v>123699064</v>
       </c>
       <c r="B8" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855114</v>
+        <v>855084</v>
       </c>
       <c r="R8" t="n">
-        <v>7478219</v>
+        <v>7478212</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699090</v>
+        <v>123699073</v>
       </c>
       <c r="B9" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>854901</v>
+        <v>855119</v>
       </c>
       <c r="R9" t="n">
-        <v>7478143</v>
+        <v>7477995</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699046</v>
+        <v>123699049</v>
       </c>
       <c r="B10" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R10" t="n">
-        <v>7478027</v>
+        <v>7477980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699041</v>
+        <v>123699087</v>
       </c>
       <c r="B11" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>854968</v>
+        <v>854993</v>
       </c>
       <c r="R11" t="n">
-        <v>7478151</v>
+        <v>7478183</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699040</v>
+        <v>123699070</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>82575</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855106</v>
+        <v>855114</v>
       </c>
       <c r="R12" t="n">
-        <v>7478141</v>
+        <v>7478219</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699058</v>
+        <v>123699060</v>
       </c>
       <c r="B13" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855091</v>
+        <v>855099</v>
       </c>
       <c r="R13" t="n">
-        <v>7478072</v>
+        <v>7478014</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1878,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699049</v>
+        <v>123699067</v>
       </c>
       <c r="B15" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855147</v>
+        <v>855198</v>
       </c>
       <c r="R15" t="n">
-        <v>7477980</v>
+        <v>7477984</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699050</v>
+        <v>123699069</v>
       </c>
       <c r="B16" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855140</v>
+        <v>855047</v>
       </c>
       <c r="R16" t="n">
-        <v>7478022</v>
+        <v>7478172</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699069</v>
+        <v>123699045</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855047</v>
+        <v>855058</v>
       </c>
       <c r="R17" t="n">
-        <v>7478172</v>
+        <v>7478025</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699089</v>
+        <v>123699072</v>
       </c>
       <c r="B18" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855063</v>
+        <v>855123</v>
       </c>
       <c r="R18" t="n">
-        <v>7478073</v>
+        <v>7478116</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699074</v>
+        <v>123699084</v>
       </c>
       <c r="B19" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855205</v>
+        <v>855181</v>
       </c>
       <c r="R19" t="n">
-        <v>7477980</v>
+        <v>7478022</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2521,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699066</v>
+        <v>123699044</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855081</v>
+        <v>854836</v>
       </c>
       <c r="R20" t="n">
-        <v>7478053</v>
+        <v>7478088</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2599,12 +2594,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699047</v>
+        <v>123699066</v>
       </c>
       <c r="B21" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2636,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>854770</v>
+        <v>855081</v>
       </c>
       <c r="R21" t="n">
-        <v>7477947</v>
+        <v>7478053</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699068</v>
+        <v>123699083</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2738,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855190</v>
+        <v>855119</v>
       </c>
       <c r="R22" t="n">
-        <v>7477967</v>
+        <v>7478027</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699086</v>
+        <v>123699048</v>
       </c>
       <c r="B23" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2844,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>854738</v>
+        <v>855062</v>
       </c>
       <c r="R23" t="n">
-        <v>7477969</v>
+        <v>7478067</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699073</v>
+        <v>123699090</v>
       </c>
       <c r="B24" t="n">
-        <v>82575</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855119</v>
+        <v>854901</v>
       </c>
       <c r="R24" t="n">
-        <v>7477995</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3031,10 +3032,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699051</v>
+        <v>123699042</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>79870</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3044,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854961</v>
+        <v>855063</v>
       </c>
       <c r="R25" t="n">
-        <v>7478150</v>
+        <v>7478073</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699045</v>
+        <v>123699058</v>
       </c>
       <c r="B26" t="n">
-        <v>79773</v>
+        <v>56692</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3146,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855058</v>
+        <v>855091</v>
       </c>
       <c r="R26" t="n">
-        <v>7478025</v>
+        <v>7478072</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3209,6 +3210,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3235,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699044</v>
+        <v>123699074</v>
       </c>
       <c r="B27" t="n">
-        <v>79773</v>
+        <v>82575</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854836</v>
+        <v>855205</v>
       </c>
       <c r="R27" t="n">
-        <v>7478088</v>
+        <v>7477980</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3313,18 +3319,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699060</v>
+        <v>123699082</v>
       </c>
       <c r="B28" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855099</v>
+        <v>855140</v>
       </c>
       <c r="R28" t="n">
-        <v>7478014</v>
+        <v>7478068</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699087</v>
+        <v>123699046</v>
       </c>
       <c r="B29" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>854993</v>
+        <v>855119</v>
       </c>
       <c r="R29" t="n">
-        <v>7478183</v>
+        <v>7478027</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699071</v>
+        <v>123699068</v>
       </c>
       <c r="B30" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855073</v>
+        <v>855190</v>
       </c>
       <c r="R30" t="n">
-        <v>7478043</v>
+        <v>7477967</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699065</v>
+        <v>123699051</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3661,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855061</v>
+        <v>854961</v>
       </c>
       <c r="R31" t="n">
-        <v>7478034</v>
+        <v>7478150</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699042</v>
+        <v>123699089</v>
       </c>
       <c r="B32" t="n">
-        <v>79870</v>
+        <v>79904</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699082</v>
+        <v>123699047</v>
       </c>
       <c r="B33" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855140</v>
+        <v>854770</v>
       </c>
       <c r="R33" t="n">
-        <v>7478068</v>
+        <v>7477947</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699067</v>
+        <v>123699065</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855198</v>
+        <v>855061</v>
       </c>
       <c r="R34" t="n">
-        <v>7477984</v>
+        <v>7478034</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699083</v>
+        <v>123699050</v>
       </c>
       <c r="B35" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R35" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699041</v>
+        <v>123699064</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>854968</v>
+        <v>855084</v>
       </c>
       <c r="R6" t="n">
-        <v>7478151</v>
+        <v>7478212</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699071</v>
+        <v>123699041</v>
       </c>
       <c r="B7" t="n">
-        <v>82575</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855073</v>
+        <v>854968</v>
       </c>
       <c r="R7" t="n">
-        <v>7478043</v>
+        <v>7478151</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699064</v>
+        <v>123699071</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855084</v>
+        <v>855073</v>
       </c>
       <c r="R8" t="n">
-        <v>7478212</v>
+        <v>7478043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699069</v>
+        <v>123699072</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855047</v>
+        <v>855123</v>
       </c>
       <c r="R16" t="n">
-        <v>7478172</v>
+        <v>7478116</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699045</v>
+        <v>123699069</v>
       </c>
       <c r="B17" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855058</v>
+        <v>855047</v>
       </c>
       <c r="R17" t="n">
-        <v>7478025</v>
+        <v>7478172</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699072</v>
+        <v>123699045</v>
       </c>
       <c r="B18" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855123</v>
+        <v>855058</v>
       </c>
       <c r="R18" t="n">
-        <v>7478116</v>
+        <v>7478025</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699048</v>
+        <v>123699042</v>
       </c>
       <c r="B23" t="n">
-        <v>79905</v>
+        <v>79870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2840,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855062</v>
+        <v>855063</v>
       </c>
       <c r="R23" t="n">
-        <v>7478067</v>
+        <v>7478073</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699058</v>
       </c>
       <c r="B24" t="n">
-        <v>79904</v>
+        <v>56692</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2942,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>855091</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478072</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699042</v>
+        <v>123699048</v>
       </c>
       <c r="B25" t="n">
-        <v>79870</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3044,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855063</v>
+        <v>855062</v>
       </c>
       <c r="R25" t="n">
-        <v>7478073</v>
+        <v>7478067</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3134,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699058</v>
+        <v>123699090</v>
       </c>
       <c r="B26" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3146,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855091</v>
+        <v>854901</v>
       </c>
       <c r="R26" t="n">
-        <v>7478072</v>
+        <v>7478143</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3210,11 +3215,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699077</v>
+        <v>123699090</v>
       </c>
       <c r="B2" t="n">
-        <v>82575</v>
+        <v>79904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855121</v>
+        <v>854901</v>
       </c>
       <c r="R2" t="n">
-        <v>7478158</v>
+        <v>7478143</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699040</v>
+        <v>123699042</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855106</v>
+        <v>855063</v>
       </c>
       <c r="R3" t="n">
-        <v>7478141</v>
+        <v>7478073</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699059</v>
+        <v>123699073</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>82575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855112</v>
+        <v>855119</v>
       </c>
       <c r="R4" t="n">
-        <v>7478087</v>
+        <v>7477995</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699086</v>
+        <v>123699084</v>
       </c>
       <c r="B5" t="n">
         <v>79804</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854738</v>
+        <v>855181</v>
       </c>
       <c r="R5" t="n">
-        <v>7477969</v>
+        <v>7478022</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699064</v>
+        <v>123699086</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855084</v>
+        <v>854738</v>
       </c>
       <c r="R6" t="n">
-        <v>7478212</v>
+        <v>7477969</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699041</v>
+        <v>123699063</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>854968</v>
+        <v>855109</v>
       </c>
       <c r="R7" t="n">
-        <v>7478151</v>
+        <v>7478143</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699071</v>
+        <v>123699064</v>
       </c>
       <c r="B8" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855073</v>
+        <v>855084</v>
       </c>
       <c r="R8" t="n">
-        <v>7478043</v>
+        <v>7478212</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699073</v>
+        <v>123699049</v>
       </c>
       <c r="B9" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R9" t="n">
-        <v>7477995</v>
+        <v>7477980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699049</v>
+        <v>123699066</v>
       </c>
       <c r="B10" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855147</v>
+        <v>855081</v>
       </c>
       <c r="R10" t="n">
-        <v>7477980</v>
+        <v>7478053</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699087</v>
+        <v>123699058</v>
       </c>
       <c r="B11" t="n">
-        <v>79804</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>854993</v>
+        <v>855091</v>
       </c>
       <c r="R11" t="n">
-        <v>7478183</v>
+        <v>7478072</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699051</v>
       </c>
       <c r="B12" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>854961</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478150</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R13" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699063</v>
+        <v>123699050</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855109</v>
+        <v>855140</v>
       </c>
       <c r="R14" t="n">
-        <v>7478143</v>
+        <v>7478022</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699067</v>
+        <v>123699041</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855198</v>
+        <v>854968</v>
       </c>
       <c r="R15" t="n">
-        <v>7477984</v>
+        <v>7478151</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699072</v>
+        <v>123699067</v>
       </c>
       <c r="B16" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855123</v>
+        <v>855198</v>
       </c>
       <c r="R16" t="n">
-        <v>7478116</v>
+        <v>7477984</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699069</v>
+        <v>123699047</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855047</v>
+        <v>854770</v>
       </c>
       <c r="R17" t="n">
-        <v>7478172</v>
+        <v>7477947</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699045</v>
+        <v>123699048</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855058</v>
+        <v>855062</v>
       </c>
       <c r="R18" t="n">
-        <v>7478025</v>
+        <v>7478067</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B19" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R19" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699044</v>
+        <v>123699068</v>
       </c>
       <c r="B20" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>854836</v>
+        <v>855190</v>
       </c>
       <c r="R20" t="n">
-        <v>7478088</v>
+        <v>7477967</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2594,18 +2599,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699066</v>
+        <v>123699040</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855081</v>
+        <v>855106</v>
       </c>
       <c r="R21" t="n">
-        <v>7478053</v>
+        <v>7478141</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699083</v>
+        <v>123699071</v>
       </c>
       <c r="B22" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2738,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855119</v>
+        <v>855073</v>
       </c>
       <c r="R22" t="n">
-        <v>7478027</v>
+        <v>7478043</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699042</v>
+        <v>123699069</v>
       </c>
       <c r="B23" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855063</v>
+        <v>855047</v>
       </c>
       <c r="R23" t="n">
-        <v>7478073</v>
+        <v>7478172</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699058</v>
+        <v>123699089</v>
       </c>
       <c r="B24" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2942,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855091</v>
+        <v>855063</v>
       </c>
       <c r="R24" t="n">
-        <v>7478072</v>
+        <v>7478073</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699048</v>
+        <v>123699083</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>79804</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855062</v>
+        <v>855119</v>
       </c>
       <c r="R25" t="n">
-        <v>7478067</v>
+        <v>7478027</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699090</v>
+        <v>123699072</v>
       </c>
       <c r="B26" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>854901</v>
+        <v>855123</v>
       </c>
       <c r="R26" t="n">
-        <v>7478143</v>
+        <v>7478116</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699074</v>
+        <v>123699070</v>
       </c>
       <c r="B27" t="n">
         <v>82575</v>
@@ -3281,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855205</v>
+        <v>855114</v>
       </c>
       <c r="R27" t="n">
-        <v>7477980</v>
+        <v>7478219</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699082</v>
+        <v>123699045</v>
       </c>
       <c r="B28" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855140</v>
+        <v>855058</v>
       </c>
       <c r="R28" t="n">
-        <v>7478068</v>
+        <v>7478025</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699046</v>
+        <v>123699082</v>
       </c>
       <c r="B29" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R29" t="n">
-        <v>7478027</v>
+        <v>7478068</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699068</v>
+        <v>123699065</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3587,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855190</v>
+        <v>855061</v>
       </c>
       <c r="R30" t="n">
-        <v>7477967</v>
+        <v>7478034</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699051</v>
+        <v>123699077</v>
       </c>
       <c r="B31" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>854961</v>
+        <v>855121</v>
       </c>
       <c r="R31" t="n">
-        <v>7478150</v>
+        <v>7478158</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699089</v>
+        <v>123699060</v>
       </c>
       <c r="B32" t="n">
-        <v>79904</v>
+        <v>90986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855063</v>
+        <v>855099</v>
       </c>
       <c r="R32" t="n">
-        <v>7478073</v>
+        <v>7478014</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699047</v>
+        <v>123699046</v>
       </c>
       <c r="B33" t="n">
         <v>79773</v>
@@ -3893,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>854770</v>
+        <v>855119</v>
       </c>
       <c r="R33" t="n">
-        <v>7477947</v>
+        <v>7478027</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699065</v>
+        <v>123699044</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855061</v>
+        <v>854836</v>
       </c>
       <c r="R34" t="n">
-        <v>7478034</v>
+        <v>7478088</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4033,12 +4027,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699050</v>
+        <v>123699059</v>
       </c>
       <c r="B35" t="n">
-        <v>79905</v>
+        <v>90986</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R35" t="n">
-        <v>7478022</v>
+        <v>7478087</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4157,6 +4157,2213 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124427351</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>855056</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7478165</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124427369</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>854943</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7478362</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124427401</v>
+      </c>
+      <c r="B38" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>855011</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7478352</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124427365</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>854939</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7478324</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124427391</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>855091</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7478207</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124427356</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>854977</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7478167</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124427388</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>855074</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7478164</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124427386</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>855066</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7478180</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124427352</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>855059</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7478173</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124427375</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>854922</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7478323</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124427345</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>854967</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7478177</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124427389</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>855110</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7478072</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124427347</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>855063</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7478044</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124427346</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>855044</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7478074</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124427354</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>855018</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7478119</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124427403</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79826</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>854946</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7478367</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124427393</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>854990</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7478363</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124427387</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>855102</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7478191</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124427398</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>855100</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7478058</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124427406</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91579</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>760</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>855096</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7478199</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124427399</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>855007</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7478357</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,7 +4159,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427391</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4194,19 +4194,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>855091</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427369</v>
+        <v>124427403</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>79826</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,25 +4278,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854943</v>
+        <v>854946</v>
       </c>
       <c r="R37" t="n">
-        <v>7478362</v>
+        <v>7478367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4350,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4368,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427347</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4380,38 +4381,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>855063</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,10 +4471,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427365</v>
+        <v>124427352</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4483,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854939</v>
+        <v>855059</v>
       </c>
       <c r="R39" t="n">
-        <v>7478324</v>
+        <v>7478173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,6 +4559,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,7 +4578,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427391</v>
+        <v>124427389</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4607,7 +4613,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4616,10 +4622,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855091</v>
+        <v>855110</v>
       </c>
       <c r="R40" t="n">
-        <v>7478207</v>
+        <v>7478072</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427356</v>
+        <v>124427387</v>
       </c>
       <c r="B41" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,38 +4697,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854977</v>
+        <v>855102</v>
       </c>
       <c r="R41" t="n">
-        <v>7478167</v>
+        <v>7478191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,6 +4773,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427388</v>
+        <v>124427406</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4797,38 +4808,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855074</v>
+        <v>855096</v>
       </c>
       <c r="R42" t="n">
-        <v>7478164</v>
+        <v>7478199</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4861,6 +4875,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4888,10 +4907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427386</v>
+        <v>124427345</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4900,42 +4919,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855066</v>
+        <v>854967</v>
       </c>
       <c r="R43" t="n">
-        <v>7478180</v>
+        <v>7478177</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,7 +4991,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4995,7 +5009,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427352</v>
+        <v>124427388</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5030,19 +5044,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855059</v>
+        <v>855074</v>
       </c>
       <c r="R44" t="n">
-        <v>7478173</v>
+        <v>7478164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5102,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427375</v>
+        <v>124427399</v>
       </c>
       <c r="B45" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5114,25 +5128,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5142,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854922</v>
+        <v>855007</v>
       </c>
       <c r="R45" t="n">
-        <v>7478323</v>
+        <v>7478357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,24 +5200,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5220,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427345</v>
+        <v>124427354</v>
       </c>
       <c r="B46" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5232,25 +5230,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5260,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854967</v>
+        <v>855018</v>
       </c>
       <c r="R46" t="n">
-        <v>7478177</v>
+        <v>7478119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5322,7 +5320,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427389</v>
+        <v>124427351</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5357,19 +5355,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855110</v>
+        <v>855056</v>
       </c>
       <c r="R47" t="n">
-        <v>7478072</v>
+        <v>7478165</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5429,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427347</v>
+        <v>124427365</v>
       </c>
       <c r="B48" t="n">
-        <v>79927</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5441,38 +5439,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855063</v>
+        <v>854939</v>
       </c>
       <c r="R48" t="n">
-        <v>7478044</v>
+        <v>7478324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5531,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427346</v>
+        <v>124427369</v>
       </c>
       <c r="B49" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5543,38 +5541,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855044</v>
+        <v>854943</v>
       </c>
       <c r="R49" t="n">
-        <v>7478074</v>
+        <v>7478362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5633,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427354</v>
+        <v>124427386</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5645,38 +5643,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855018</v>
+        <v>855066</v>
       </c>
       <c r="R50" t="n">
-        <v>7478119</v>
+        <v>7478180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5717,6 +5719,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5735,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427403</v>
+        <v>124427393</v>
       </c>
       <c r="B51" t="n">
-        <v>79826</v>
+        <v>56714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5747,25 +5750,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5775,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854946</v>
+        <v>854990</v>
       </c>
       <c r="R51" t="n">
-        <v>7478367</v>
+        <v>7478363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5819,7 +5822,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5838,10 +5840,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427393</v>
+        <v>124427398</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5854,21 +5856,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854990</v>
+        <v>855100</v>
       </c>
       <c r="R52" t="n">
-        <v>7478363</v>
+        <v>7478058</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5940,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427387</v>
+        <v>124427401</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5952,42 +5954,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855102</v>
+        <v>855011</v>
       </c>
       <c r="R53" t="n">
-        <v>7478191</v>
+        <v>7478352</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6028,7 +6026,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6047,10 +6044,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427398</v>
+        <v>124427346</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6059,38 +6056,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855100</v>
+        <v>855044</v>
       </c>
       <c r="R54" t="n">
-        <v>7478058</v>
+        <v>7478074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6149,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427406</v>
+        <v>124427375</v>
       </c>
       <c r="B55" t="n">
-        <v>91579</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6161,45 +6158,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855096</v>
+        <v>854922</v>
       </c>
       <c r="R55" t="n">
-        <v>7478199</v>
+        <v>7478323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,11 +6224,6 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6248,6 +6233,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6264,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427399</v>
+        <v>124427356</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,20 +6276,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6300,14 +6300,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855007</v>
+        <v>854977</v>
       </c>
       <c r="R56" t="n">
-        <v>7478357</v>
+        <v>7478167</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427391</v>
+        <v>124427345</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855091</v>
+        <v>854967</v>
       </c>
       <c r="R36" t="n">
-        <v>7478207</v>
+        <v>7478177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427403</v>
+        <v>124427399</v>
       </c>
       <c r="B37" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,25 +4273,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4306,10 +4301,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854946</v>
+        <v>855007</v>
       </c>
       <c r="R37" t="n">
-        <v>7478367</v>
+        <v>7478357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,7 +4345,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4369,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427347</v>
+        <v>124427403</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>79826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4385,34 +4379,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855063</v>
+        <v>854946</v>
       </c>
       <c r="R38" t="n">
-        <v>7478044</v>
+        <v>7478367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,6 +4447,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4471,10 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4483,42 +4478,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R39" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4559,7 +4550,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4578,10 +4568,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427389</v>
+        <v>124427393</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4590,42 +4580,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855110</v>
+        <v>854990</v>
       </c>
       <c r="R40" t="n">
-        <v>7478072</v>
+        <v>7478363</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4652,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4670,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427387</v>
+        <v>124427389</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4720,7 +4705,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4729,10 +4714,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855102</v>
+        <v>855110</v>
       </c>
       <c r="R41" t="n">
-        <v>7478191</v>
+        <v>7478072</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4792,10 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427406</v>
+        <v>124427369</v>
       </c>
       <c r="B42" t="n">
-        <v>91579</v>
+        <v>57666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,45 +4789,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>760</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855096</v>
+        <v>854943</v>
       </c>
       <c r="R42" t="n">
-        <v>7478199</v>
+        <v>7478362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,18 +4855,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4907,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427345</v>
+        <v>124427401</v>
       </c>
       <c r="B43" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4919,38 +4891,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854967</v>
+        <v>855011</v>
       </c>
       <c r="R43" t="n">
-        <v>7478177</v>
+        <v>7478352</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427388</v>
+        <v>124427398</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,42 +4993,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855074</v>
+        <v>855100</v>
       </c>
       <c r="R44" t="n">
-        <v>7478164</v>
+        <v>7478058</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,7 +5065,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5116,10 +5083,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427399</v>
+        <v>124427347</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,38 +5095,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855007</v>
+        <v>855063</v>
       </c>
       <c r="R45" t="n">
-        <v>7478357</v>
+        <v>7478044</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427354</v>
+        <v>124427365</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,34 +5201,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855018</v>
+        <v>854939</v>
       </c>
       <c r="R46" t="n">
-        <v>7478119</v>
+        <v>7478324</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,7 +5287,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427351</v>
+        <v>124427387</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5355,19 +5322,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855056</v>
+        <v>855102</v>
       </c>
       <c r="R47" t="n">
-        <v>7478165</v>
+        <v>7478191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427365</v>
+        <v>124427375</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5439,25 +5406,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5434,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854939</v>
+        <v>854922</v>
       </c>
       <c r="R48" t="n">
-        <v>7478324</v>
+        <v>7478323</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5511,8 +5478,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5529,10 +5512,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427369</v>
+        <v>124427351</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5541,38 +5524,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854943</v>
+        <v>855056</v>
       </c>
       <c r="R49" t="n">
-        <v>7478362</v>
+        <v>7478165</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5613,6 +5600,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5631,7 +5619,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427386</v>
+        <v>124427352</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5666,19 +5654,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855066</v>
+        <v>855059</v>
       </c>
       <c r="R50" t="n">
-        <v>7478180</v>
+        <v>7478173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5738,10 +5726,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427393</v>
+        <v>124427406</v>
       </c>
       <c r="B51" t="n">
-        <v>56714</v>
+        <v>91579</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,38 +5738,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>760</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854990</v>
+        <v>855096</v>
       </c>
       <c r="R51" t="n">
-        <v>7478363</v>
+        <v>7478199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5816,12 +5811,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5840,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427398</v>
+        <v>124427356</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,20 +5853,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5876,14 +5877,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855100</v>
+        <v>854977</v>
       </c>
       <c r="R52" t="n">
-        <v>7478058</v>
+        <v>7478167</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5942,10 +5943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427401</v>
+        <v>124427354</v>
       </c>
       <c r="B53" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5958,34 +5959,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855011</v>
+        <v>855018</v>
       </c>
       <c r="R53" t="n">
-        <v>7478352</v>
+        <v>7478119</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6044,10 +6045,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427346</v>
+        <v>124427386</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6056,38 +6057,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855044</v>
+        <v>855066</v>
       </c>
       <c r="R54" t="n">
-        <v>7478074</v>
+        <v>7478180</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6128,6 +6133,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6146,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427375</v>
+        <v>124427388</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6158,38 +6164,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854922</v>
+        <v>855074</v>
       </c>
       <c r="R55" t="n">
-        <v>7478323</v>
+        <v>7478164</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,21 +6243,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6264,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427356</v>
+        <v>124427391</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,38 +6271,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854977</v>
+        <v>855091</v>
       </c>
       <c r="R56" t="n">
-        <v>7478167</v>
+        <v>7478207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,6 +6347,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6364,6 +6364,5502 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124855474</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>855065</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7478197</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124855376</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>854741</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7477958</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124855512</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>854911</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7478164</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124855381</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>854803</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124855424</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>854780</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7477939</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124855483</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>855251</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7478036</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124855423</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>854915</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7477851</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124855389</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>854906</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7477891</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124855404</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>854832</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7477880</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124855366</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>854807</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7477926</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124855417</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>855202</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7477976</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>124855232</v>
+      </c>
+      <c r="B68" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>855094</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7477931</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124855329</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56725</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>854676</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7477840</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>124855467</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>855062</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7478002</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>124855468</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>855069</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7477999</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124855364</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>855120</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7477887</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124855316</v>
+      </c>
+      <c r="B73" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>855019</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7477888</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>124855469</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>854979</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7477885</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>124855394</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>854897</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7477846</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>124855380</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>854745</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7477946</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>124855358</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>854772</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7477881</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>124855318</v>
+      </c>
+      <c r="B78" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>854817</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7477931</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124854791</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>854840</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7477716</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>124855420</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>855071</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7477912</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>124855250</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>854814</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7477852</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>124855482</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>855134</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7477890</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>124855233</v>
+      </c>
+      <c r="B83" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>855073</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7477920</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>124854790</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>854766</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7478012</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>124855415</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>854928</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7478107</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>124855466</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>854921</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7478082</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>124855536</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>854869</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7477778</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>124855401</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>854928</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7477769</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>124855416</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>855002</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7478149</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>124855313</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>658</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>854814</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7477852</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>124855333</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>854924</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7478087</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>124855277</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>855068</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7478046</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>124855386</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>854810</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>124855231</v>
+      </c>
+      <c r="B94" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>854954</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7478125</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124855421</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>854951</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7477899</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124855275</v>
+      </c>
+      <c r="B96" t="n">
+        <v>92321</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>854889</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7477847</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>124855328</v>
+      </c>
+      <c r="B97" t="n">
+        <v>56725</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>854802</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7477769</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124855390</v>
+      </c>
+      <c r="B98" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>854899</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7477831</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>124855500</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79826</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>854850</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7477915</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>124855240</v>
+      </c>
+      <c r="B100" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>854937</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7477782</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>124855371</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>854845</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7477869</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>124855257</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>854894</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7477768</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124855359</v>
+      </c>
+      <c r="B103" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>854838</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7477840</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>124855524</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>854793</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7477805</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>124855464</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>854898</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7478156</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124855418</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>855131</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7477924</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>124855475</v>
+      </c>
+      <c r="B107" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>854813</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7477923</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>124855317</v>
+      </c>
+      <c r="B108" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>854783</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7477935</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>124855244</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>855187</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7478029</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427345</v>
+        <v>124427388</v>
       </c>
       <c r="B36" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854967</v>
+        <v>855074</v>
       </c>
       <c r="R36" t="n">
-        <v>7478177</v>
+        <v>7478164</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427399</v>
+        <v>124427406</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,38 +4278,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855007</v>
+        <v>855096</v>
       </c>
       <c r="R37" t="n">
-        <v>7478357</v>
+        <v>7478199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4339,12 +4351,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427403</v>
+        <v>124427365</v>
       </c>
       <c r="B38" t="n">
-        <v>79826</v>
+        <v>79428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,25 +4393,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4403,10 +4421,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854946</v>
+        <v>854939</v>
       </c>
       <c r="R38" t="n">
-        <v>7478367</v>
+        <v>7478324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,7 +4465,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4483,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427346</v>
+        <v>124427345</v>
       </c>
       <c r="B39" t="n">
         <v>79927</v>
@@ -4506,10 +4523,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855044</v>
+        <v>854967</v>
       </c>
       <c r="R39" t="n">
-        <v>7478074</v>
+        <v>7478177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4568,10 +4585,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427393</v>
+        <v>124427403</v>
       </c>
       <c r="B40" t="n">
-        <v>56714</v>
+        <v>79826</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4580,25 +4597,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4608,10 +4625,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854990</v>
+        <v>854946</v>
       </c>
       <c r="R40" t="n">
-        <v>7478363</v>
+        <v>7478367</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,6 +4669,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4670,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427389</v>
+        <v>124427347</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4682,42 +4700,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855110</v>
+        <v>855063</v>
       </c>
       <c r="R41" t="n">
-        <v>7478072</v>
+        <v>7478044</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,7 +4772,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4777,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427369</v>
+        <v>124427398</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4806,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854943</v>
+        <v>855100</v>
       </c>
       <c r="R42" t="n">
-        <v>7478362</v>
+        <v>7478058</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427401</v>
+        <v>124427391</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4891,38 +4904,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855011</v>
+        <v>855091</v>
       </c>
       <c r="R43" t="n">
-        <v>7478352</v>
+        <v>7478207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,6 +4980,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4981,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427398</v>
+        <v>124427352</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4993,38 +5011,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855100</v>
+        <v>855059</v>
       </c>
       <c r="R44" t="n">
-        <v>7478058</v>
+        <v>7478173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,6 +5087,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5083,10 +5106,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427347</v>
+        <v>124427387</v>
       </c>
       <c r="B45" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5095,38 +5118,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855063</v>
+        <v>855102</v>
       </c>
       <c r="R45" t="n">
-        <v>7478044</v>
+        <v>7478191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5167,6 +5194,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5185,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427365</v>
+        <v>124427393</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>56714</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5201,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5225,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854939</v>
+        <v>854990</v>
       </c>
       <c r="R46" t="n">
-        <v>7478324</v>
+        <v>7478363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427387</v>
+        <v>124427369</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5299,42 +5327,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855102</v>
+        <v>854943</v>
       </c>
       <c r="R47" t="n">
-        <v>7478191</v>
+        <v>7478362</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,7 +5399,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5394,10 +5417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427375</v>
+        <v>124427354</v>
       </c>
       <c r="B48" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5406,38 +5429,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854922</v>
+        <v>855018</v>
       </c>
       <c r="R48" t="n">
-        <v>7478323</v>
+        <v>7478119</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,24 +5501,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5619,10 +5626,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427352</v>
+        <v>124427356</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5631,42 +5638,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855059</v>
+        <v>854977</v>
       </c>
       <c r="R50" t="n">
-        <v>7478173</v>
+        <v>7478167</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5707,7 +5710,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5726,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427406</v>
+        <v>124427401</v>
       </c>
       <c r="B51" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5738,45 +5740,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855096</v>
+        <v>855011</v>
       </c>
       <c r="R51" t="n">
-        <v>7478199</v>
+        <v>7478352</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,18 +5806,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427356</v>
+        <v>124427389</v>
       </c>
       <c r="B52" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,38 +5842,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854977</v>
+        <v>855110</v>
       </c>
       <c r="R52" t="n">
-        <v>7478167</v>
+        <v>7478072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,6 +5918,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5943,10 +5937,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427354</v>
+        <v>124427346</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5955,25 +5949,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5983,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855018</v>
+        <v>855044</v>
       </c>
       <c r="R53" t="n">
-        <v>7478119</v>
+        <v>7478074</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6152,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427388</v>
+        <v>124427375</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,42 +6158,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855074</v>
+        <v>854922</v>
       </c>
       <c r="R55" t="n">
-        <v>7478164</v>
+        <v>7478323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,6 +6233,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6259,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427391</v>
+        <v>124427399</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,42 +6276,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855091</v>
+        <v>855007</v>
       </c>
       <c r="R56" t="n">
-        <v>7478207</v>
+        <v>7478357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,7 +6348,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855474</v>
+        <v>124855389</v>
       </c>
       <c r="B57" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6378,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855065</v>
+        <v>854906</v>
       </c>
       <c r="R57" t="n">
-        <v>7478197</v>
+        <v>7477891</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,6 +6454,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6468,7 +6473,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855376</v>
+        <v>124855423</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6501,21 +6506,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854741</v>
+        <v>854915</v>
       </c>
       <c r="R58" t="n">
-        <v>7477958</v>
+        <v>7477851</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6556,7 +6557,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855512</v>
+        <v>124855404</v>
       </c>
       <c r="B59" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6587,38 +6587,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854911</v>
+        <v>854832</v>
       </c>
       <c r="R59" t="n">
-        <v>7478164</v>
+        <v>7477880</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6659,6 +6663,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6677,10 +6682,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855381</v>
+        <v>124855318</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,25 +6694,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6722,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854803</v>
+        <v>854817</v>
       </c>
       <c r="R60" t="n">
-        <v>7477930</v>
+        <v>7477931</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6761,7 +6766,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6780,7 +6784,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855424</v>
+        <v>124855380</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6820,10 +6824,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854780</v>
+        <v>854745</v>
       </c>
       <c r="R61" t="n">
-        <v>7477939</v>
+        <v>7477946</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6864,6 +6868,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6882,10 +6887,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855483</v>
+        <v>124854790</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6894,38 +6899,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855251</v>
+        <v>854766</v>
       </c>
       <c r="R62" t="n">
-        <v>7478036</v>
+        <v>7478012</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6966,6 +6975,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6984,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855423</v>
+        <v>124855328</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,38 +7006,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854915</v>
+        <v>854802</v>
       </c>
       <c r="R63" t="n">
-        <v>7477851</v>
+        <v>7477769</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,12 +7064,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7086,10 +7101,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855389</v>
+        <v>124855524</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7098,42 +7113,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854906</v>
+        <v>854793</v>
       </c>
       <c r="R64" t="n">
-        <v>7477891</v>
+        <v>7477805</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7160,12 +7171,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7174,7 +7185,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7193,7 +7203,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855404</v>
+        <v>124855421</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7226,21 +7236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854832</v>
+        <v>854951</v>
       </c>
       <c r="R65" t="n">
-        <v>7477880</v>
+        <v>7477899</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7281,7 +7287,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7300,7 +7305,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855366</v>
+        <v>124855468</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7333,21 +7338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854807</v>
+        <v>855069</v>
       </c>
       <c r="R66" t="n">
-        <v>7477926</v>
+        <v>7477999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7388,7 +7389,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855417</v>
+        <v>124855277</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7419,25 +7419,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855202</v>
+        <v>855068</v>
       </c>
       <c r="R67" t="n">
-        <v>7477976</v>
+        <v>7478046</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855232</v>
+        <v>124855483</v>
       </c>
       <c r="B68" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7521,25 +7521,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855094</v>
+        <v>855251</v>
       </c>
       <c r="R68" t="n">
-        <v>7477931</v>
+        <v>7478036</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855329</v>
+        <v>124855482</v>
       </c>
       <c r="B69" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7623,38 +7623,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854676</v>
+        <v>855134</v>
       </c>
       <c r="R69" t="n">
-        <v>7477840</v>
+        <v>7477890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,17 +7681,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7718,10 +7713,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855467</v>
+        <v>124855250</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7730,25 +7725,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7758,10 +7753,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855062</v>
+        <v>854814</v>
       </c>
       <c r="R70" t="n">
-        <v>7478002</v>
+        <v>7477852</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7820,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855468</v>
+        <v>124855317</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7832,25 +7827,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7860,10 +7855,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855069</v>
+        <v>854783</v>
       </c>
       <c r="R71" t="n">
-        <v>7477999</v>
+        <v>7477935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7922,7 +7917,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855364</v>
+        <v>124855366</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7955,17 +7950,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855120</v>
+        <v>854807</v>
       </c>
       <c r="R72" t="n">
-        <v>7477887</v>
+        <v>7477926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7998,11 +7997,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8132,7 +8126,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855469</v>
+        <v>124855359</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8168,14 +8162,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854979</v>
+        <v>854838</v>
       </c>
       <c r="R74" t="n">
-        <v>7477885</v>
+        <v>7477840</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8210,12 +8204,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855394</v>
+        <v>124855424</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8267,21 +8267,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854897</v>
+        <v>854780</v>
       </c>
       <c r="R75" t="n">
-        <v>7477846</v>
+        <v>7477939</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8322,7 +8318,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8341,7 +8336,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855380</v>
+        <v>124855417</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8381,10 +8376,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854745</v>
+        <v>855202</v>
       </c>
       <c r="R76" t="n">
-        <v>7477946</v>
+        <v>7477976</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8425,7 +8420,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8444,10 +8438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855358</v>
+        <v>124855244</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8456,38 +8450,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854772</v>
+        <v>855187</v>
       </c>
       <c r="R77" t="n">
-        <v>7477881</v>
+        <v>7478029</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8522,18 +8516,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8540,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855318</v>
+        <v>124855329</v>
       </c>
       <c r="B78" t="n">
-        <v>96985</v>
+        <v>56725</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8568,34 +8556,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854817</v>
+        <v>854676</v>
       </c>
       <c r="R78" t="n">
-        <v>7477931</v>
+        <v>7477840</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8622,12 +8610,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8654,10 +8647,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124854791</v>
+        <v>124855474</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8670,34 +8663,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854840</v>
+        <v>855065</v>
       </c>
       <c r="R79" t="n">
-        <v>7477716</v>
+        <v>7478197</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8724,12 +8717,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8858,10 +8851,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855250</v>
+        <v>124855500</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>79826</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8870,25 +8863,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6457</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8898,10 +8891,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854814</v>
+        <v>854850</v>
       </c>
       <c r="R81" t="n">
-        <v>7477852</v>
+        <v>7477915</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8960,10 +8953,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855482</v>
+        <v>124855512</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,20 +8965,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9000,10 +8993,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855134</v>
+        <v>854911</v>
       </c>
       <c r="R82" t="n">
-        <v>7477890</v>
+        <v>7478164</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9062,10 +9055,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855233</v>
+        <v>124855390</v>
       </c>
       <c r="B83" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9074,38 +9067,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855073</v>
+        <v>854899</v>
       </c>
       <c r="R83" t="n">
-        <v>7477920</v>
+        <v>7477831</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9146,6 +9143,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9164,7 +9162,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124854790</v>
+        <v>124855358</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9197,21 +9195,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854766</v>
+        <v>854772</v>
       </c>
       <c r="R84" t="n">
-        <v>7478012</v>
+        <v>7477881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9244,6 +9238,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9271,7 +9270,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855415</v>
+        <v>124855376</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9304,17 +9303,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854928</v>
+        <v>854741</v>
       </c>
       <c r="R85" t="n">
-        <v>7478107</v>
+        <v>7477958</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9355,6 +9358,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9373,7 +9377,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855466</v>
+        <v>124855416</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9413,10 +9417,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854921</v>
+        <v>855002</v>
       </c>
       <c r="R86" t="n">
-        <v>7478082</v>
+        <v>7478149</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9475,10 +9479,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855536</v>
+        <v>124855401</v>
       </c>
       <c r="B87" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9487,38 +9491,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854869</v>
+        <v>854928</v>
       </c>
       <c r="R87" t="n">
-        <v>7477778</v>
+        <v>7477769</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9553,17 +9561,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9582,7 +9586,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855401</v>
+        <v>124855418</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9615,21 +9619,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854928</v>
+        <v>855131</v>
       </c>
       <c r="R88" t="n">
-        <v>7477769</v>
+        <v>7477924</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9656,12 +9656,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9670,7 +9670,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9689,7 +9688,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855416</v>
+        <v>124855467</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9729,10 +9728,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855002</v>
+        <v>855062</v>
       </c>
       <c r="R89" t="n">
-        <v>7478149</v>
+        <v>7478002</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9791,10 +9790,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855313</v>
+        <v>124855536</v>
       </c>
       <c r="B90" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9807,21 +9806,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9831,10 +9830,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854814</v>
+        <v>854869</v>
       </c>
       <c r="R90" t="n">
-        <v>7477852</v>
+        <v>7477778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9861,12 +9860,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9893,10 +9897,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855333</v>
+        <v>124855364</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9905,38 +9909,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854924</v>
+        <v>855120</v>
       </c>
       <c r="R91" t="n">
-        <v>7478087</v>
+        <v>7477887</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9971,12 +9975,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9995,10 +10005,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855277</v>
+        <v>124855381</v>
       </c>
       <c r="B92" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10007,25 +10017,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10035,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855068</v>
+        <v>854803</v>
       </c>
       <c r="R92" t="n">
-        <v>7478046</v>
+        <v>7477930</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10079,6 +10089,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10097,10 +10108,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855386</v>
+        <v>124855333</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10109,42 +10120,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854810</v>
+        <v>854924</v>
       </c>
       <c r="R93" t="n">
-        <v>7477930</v>
+        <v>7478087</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10185,7 +10192,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10204,7 +10210,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855231</v>
+        <v>124855233</v>
       </c>
       <c r="B94" t="n">
         <v>105102</v>
@@ -10244,10 +10250,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854954</v>
+        <v>855073</v>
       </c>
       <c r="R94" t="n">
-        <v>7478125</v>
+        <v>7477920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10306,10 +10312,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855421</v>
+        <v>124855313</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10318,25 +10324,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10346,10 +10352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854951</v>
+        <v>854814</v>
       </c>
       <c r="R95" t="n">
-        <v>7477899</v>
+        <v>7477852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10408,10 +10414,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855275</v>
+        <v>124854791</v>
       </c>
       <c r="B96" t="n">
-        <v>92321</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10424,21 +10430,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10448,10 +10454,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854889</v>
+        <v>854840</v>
       </c>
       <c r="R96" t="n">
-        <v>7477847</v>
+        <v>7477716</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10478,12 +10484,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10510,10 +10516,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855328</v>
+        <v>124855232</v>
       </c>
       <c r="B97" t="n">
-        <v>56725</v>
+        <v>105102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10526,34 +10532,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102613</v>
+        <v>221725</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854802</v>
+        <v>855094</v>
       </c>
       <c r="R97" t="n">
-        <v>7477769</v>
+        <v>7477931</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10580,17 +10586,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10617,7 +10618,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855390</v>
+        <v>124855469</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10650,21 +10651,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854899</v>
+        <v>854979</v>
       </c>
       <c r="R98" t="n">
-        <v>7477831</v>
+        <v>7477885</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10705,7 +10702,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10724,10 +10720,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855500</v>
+        <v>124855466</v>
       </c>
       <c r="B99" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10736,25 +10732,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10764,10 +10760,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854850</v>
+        <v>854921</v>
       </c>
       <c r="R99" t="n">
-        <v>7477915</v>
+        <v>7478082</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10826,10 +10822,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855240</v>
+        <v>124855386</v>
       </c>
       <c r="B100" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10838,38 +10834,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854937</v>
+        <v>854810</v>
       </c>
       <c r="R100" t="n">
-        <v>7477782</v>
+        <v>7477930</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10896,12 +10896,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10910,6 +10910,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10928,10 +10929,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855371</v>
+        <v>124855475</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10940,42 +10941,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854845</v>
+        <v>854813</v>
       </c>
       <c r="R101" t="n">
-        <v>7477869</v>
+        <v>7477923</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11016,7 +11013,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11035,10 +11031,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855257</v>
+        <v>124855415</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11047,25 +11043,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11075,10 +11071,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854894</v>
+        <v>854928</v>
       </c>
       <c r="R102" t="n">
-        <v>7477768</v>
+        <v>7478107</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11105,17 +11101,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11142,7 +11133,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855359</v>
+        <v>124855371</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11175,17 +11166,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854838</v>
+        <v>854845</v>
       </c>
       <c r="R103" t="n">
-        <v>7477840</v>
+        <v>7477869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11218,11 +11213,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11250,10 +11240,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855524</v>
+        <v>124855464</v>
       </c>
       <c r="B104" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11262,25 +11252,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11290,10 +11280,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854793</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477805</v>
+        <v>7478156</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11320,12 +11310,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11352,10 +11342,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855464</v>
+        <v>124855231</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11364,25 +11354,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11392,10 +11382,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854898</v>
+        <v>854954</v>
       </c>
       <c r="R105" t="n">
-        <v>7478156</v>
+        <v>7478125</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11454,10 +11444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855418</v>
+        <v>124855257</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11466,25 +11456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11494,10 +11484,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855131</v>
+        <v>854894</v>
       </c>
       <c r="R106" t="n">
-        <v>7477924</v>
+        <v>7477768</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11524,12 +11514,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11556,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855475</v>
+        <v>124855275</v>
       </c>
       <c r="B107" t="n">
-        <v>56714</v>
+        <v>92321</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11572,34 +11567,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>5449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854813</v>
+        <v>854889</v>
       </c>
       <c r="R107" t="n">
-        <v>7477923</v>
+        <v>7477847</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11658,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855317</v>
+        <v>124855240</v>
       </c>
       <c r="B108" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11674,21 +11669,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11698,10 +11693,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854783</v>
+        <v>854937</v>
       </c>
       <c r="R108" t="n">
-        <v>7477935</v>
+        <v>7477782</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11728,12 +11723,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11760,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855244</v>
+        <v>124855394</v>
       </c>
       <c r="B109" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11772,38 +11767,42 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855187</v>
+        <v>854897</v>
       </c>
       <c r="R109" t="n">
-        <v>7478029</v>
+        <v>7477846</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,6 +11843,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427388</v>
+        <v>124427406</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,38 +4175,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855074</v>
+        <v>855096</v>
       </c>
       <c r="R36" t="n">
-        <v>7478164</v>
+        <v>7478199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,6 +4242,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4266,10 +4274,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427406</v>
+        <v>124427365</v>
       </c>
       <c r="B37" t="n">
-        <v>91579</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,45 +4286,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855096</v>
+        <v>854939</v>
       </c>
       <c r="R37" t="n">
-        <v>7478199</v>
+        <v>7478324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,18 +4352,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4381,10 +4376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427365</v>
+        <v>124427388</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,38 +4388,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854939</v>
+        <v>855074</v>
       </c>
       <c r="R38" t="n">
-        <v>7478324</v>
+        <v>7478164</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,6 +4464,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427351</v>
+        <v>124427356</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,42 +5531,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855056</v>
+        <v>854977</v>
       </c>
       <c r="R49" t="n">
-        <v>7478165</v>
+        <v>7478167</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,7 +5603,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5626,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427356</v>
+        <v>124427351</v>
       </c>
       <c r="B50" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5638,38 +5633,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854977</v>
+        <v>855056</v>
       </c>
       <c r="R50" t="n">
-        <v>7478167</v>
+        <v>7478165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5710,6 +5709,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855483</v>
+        <v>124855250</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855251</v>
+        <v>854814</v>
       </c>
       <c r="R68" t="n">
-        <v>7478036</v>
+        <v>7477852</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855482</v>
+        <v>124855317</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7623,25 +7623,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855134</v>
+        <v>854783</v>
       </c>
       <c r="R69" t="n">
-        <v>7477890</v>
+        <v>7477935</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7713,10 +7713,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855250</v>
+        <v>124855366</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7725,38 +7725,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854814</v>
+        <v>854807</v>
       </c>
       <c r="R70" t="n">
-        <v>7477852</v>
+        <v>7477926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,6 +7801,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855317</v>
+        <v>124855483</v>
       </c>
       <c r="B71" t="n">
-        <v>96985</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7827,25 +7832,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7855,10 +7860,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854783</v>
+        <v>855251</v>
       </c>
       <c r="R71" t="n">
-        <v>7477935</v>
+        <v>7478036</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,10 +7922,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855366</v>
+        <v>124855482</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7929,42 +7934,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854807</v>
+        <v>855134</v>
       </c>
       <c r="R72" t="n">
-        <v>7477926</v>
+        <v>7477890</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8005,7 +8006,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -6994,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855328</v>
+        <v>124855468</v>
       </c>
       <c r="B63" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7006,38 +7006,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854802</v>
+        <v>855069</v>
       </c>
       <c r="R63" t="n">
-        <v>7477769</v>
+        <v>7477999</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,17 +7064,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7101,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855524</v>
+        <v>124855328</v>
       </c>
       <c r="B64" t="n">
-        <v>79926</v>
+        <v>56725</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7117,34 +7112,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>102613</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854793</v>
+        <v>854802</v>
       </c>
       <c r="R64" t="n">
-        <v>7477805</v>
+        <v>7477769</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7177,6 +7172,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855421</v>
+        <v>124855524</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7215,25 +7215,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854951</v>
+        <v>854793</v>
       </c>
       <c r="R65" t="n">
-        <v>7477899</v>
+        <v>7477805</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,7 +7305,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855468</v>
+        <v>124855421</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855069</v>
+        <v>854951</v>
       </c>
       <c r="R66" t="n">
-        <v>7477999</v>
+        <v>7477899</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855317</v>
+        <v>124855483</v>
       </c>
       <c r="B69" t="n">
-        <v>96985</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7623,25 +7623,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854783</v>
+        <v>855251</v>
       </c>
       <c r="R69" t="n">
-        <v>7477935</v>
+        <v>7478036</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7713,10 +7713,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855366</v>
+        <v>124855482</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7725,42 +7725,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854807</v>
+        <v>855134</v>
       </c>
       <c r="R70" t="n">
-        <v>7477926</v>
+        <v>7477890</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7801,7 +7797,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7820,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855483</v>
+        <v>124855317</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7832,25 +7827,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7860,10 +7855,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855251</v>
+        <v>854783</v>
       </c>
       <c r="R71" t="n">
-        <v>7478036</v>
+        <v>7477935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7922,10 +7917,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855482</v>
+        <v>124855366</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7934,38 +7929,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855134</v>
+        <v>854807</v>
       </c>
       <c r="R72" t="n">
-        <v>7477890</v>
+        <v>7477926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8006,6 +8005,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -11551,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855275</v>
+        <v>124855394</v>
       </c>
       <c r="B107" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,38 +11563,42 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854889</v>
+        <v>854897</v>
       </c>
       <c r="R107" t="n">
-        <v>7477847</v>
+        <v>7477846</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11635,6 +11639,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11653,10 +11658,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855240</v>
+        <v>124855275</v>
       </c>
       <c r="B108" t="n">
-        <v>105102</v>
+        <v>92321</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,38 +11670,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>5449</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854937</v>
+        <v>854889</v>
       </c>
       <c r="R108" t="n">
-        <v>7477782</v>
+        <v>7477847</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11723,12 +11728,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11755,10 +11760,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855394</v>
+        <v>124855240</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,42 +11772,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854897</v>
+        <v>854937</v>
       </c>
       <c r="R109" t="n">
-        <v>7477846</v>
+        <v>7477782</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11829,12 +11830,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11843,7 +11844,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427406</v>
+        <v>124427356</v>
       </c>
       <c r="B36" t="n">
-        <v>91579</v>
+        <v>79926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,45 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855096</v>
+        <v>854977</v>
       </c>
       <c r="R36" t="n">
-        <v>7478199</v>
+        <v>7478167</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,18 +4237,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427365</v>
+        <v>124427345</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,38 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854939</v>
+        <v>854967</v>
       </c>
       <c r="R37" t="n">
-        <v>7478324</v>
+        <v>7478177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427388</v>
+        <v>124427347</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,42 +4375,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855074</v>
+        <v>855063</v>
       </c>
       <c r="R38" t="n">
-        <v>7478164</v>
+        <v>7478044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4447,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4483,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427345</v>
+        <v>124427401</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,38 +4477,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854967</v>
+        <v>855011</v>
       </c>
       <c r="R39" t="n">
-        <v>7478177</v>
+        <v>7478352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427403</v>
+        <v>124427365</v>
       </c>
       <c r="B40" t="n">
-        <v>79826</v>
+        <v>79428</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,25 +4579,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4625,10 +4607,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854946</v>
+        <v>854939</v>
       </c>
       <c r="R40" t="n">
-        <v>7478367</v>
+        <v>7478324</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,7 +4651,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4688,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427347</v>
+        <v>124427406</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,38 +4681,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855063</v>
+        <v>855096</v>
       </c>
       <c r="R41" t="n">
-        <v>7478044</v>
+        <v>7478199</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4766,12 +4754,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4790,10 +4784,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427398</v>
+        <v>124427369</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4806,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4830,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855100</v>
+        <v>854943</v>
       </c>
       <c r="R42" t="n">
-        <v>7478058</v>
+        <v>7478362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427391</v>
+        <v>124427403</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4904,42 +4898,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855091</v>
+        <v>854946</v>
       </c>
       <c r="R43" t="n">
-        <v>7478207</v>
+        <v>7478367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427352</v>
+        <v>124427399</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,42 +5001,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855059</v>
+        <v>855007</v>
       </c>
       <c r="R44" t="n">
-        <v>7478173</v>
+        <v>7478357</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,7 +5073,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5106,7 +5091,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427387</v>
+        <v>124427389</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5141,7 +5126,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5150,10 +5135,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855102</v>
+        <v>855110</v>
       </c>
       <c r="R45" t="n">
-        <v>7478191</v>
+        <v>7478072</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B46" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5229,34 +5214,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R46" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427369</v>
+        <v>124427375</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5327,25 +5312,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5355,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854943</v>
+        <v>854922</v>
       </c>
       <c r="R47" t="n">
-        <v>7478362</v>
+        <v>7478323</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5399,8 +5384,24 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5417,10 +5418,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427354</v>
+        <v>124427393</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,34 +5434,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855018</v>
+        <v>854990</v>
       </c>
       <c r="R48" t="n">
-        <v>7478119</v>
+        <v>7478363</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5520,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427356</v>
+        <v>124427387</v>
       </c>
       <c r="B49" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,38 +5532,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854977</v>
+        <v>855102</v>
       </c>
       <c r="R49" t="n">
-        <v>7478167</v>
+        <v>7478191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5603,6 +5608,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5728,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B51" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5740,38 +5746,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R51" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,6 +5822,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5830,7 +5841,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -5865,7 +5876,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5874,10 +5885,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R52" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427346</v>
+        <v>124427398</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5949,38 +5960,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855044</v>
+        <v>855100</v>
       </c>
       <c r="R53" t="n">
-        <v>7478074</v>
+        <v>7478058</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427386</v>
+        <v>124427346</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,42 +6062,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855066</v>
+        <v>855044</v>
       </c>
       <c r="R54" t="n">
-        <v>7478180</v>
+        <v>7478074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6127,7 +6134,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6146,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427375</v>
+        <v>124427388</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6158,38 +6164,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854922</v>
+        <v>855074</v>
       </c>
       <c r="R55" t="n">
-        <v>7478323</v>
+        <v>7478164</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,21 +6243,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6264,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427399</v>
+        <v>124427386</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,38 +6271,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855007</v>
+        <v>855066</v>
       </c>
       <c r="R56" t="n">
-        <v>7478357</v>
+        <v>7478180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,6 +6347,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855389</v>
+        <v>124855512</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,42 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854906</v>
+        <v>854911</v>
       </c>
       <c r="R57" t="n">
-        <v>7477891</v>
+        <v>7478164</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6454,7 +6450,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6473,7 +6468,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855423</v>
+        <v>124855420</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6513,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854915</v>
+        <v>855071</v>
       </c>
       <c r="R58" t="n">
-        <v>7477851</v>
+        <v>7477912</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6575,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855404</v>
+        <v>124855231</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6587,42 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854832</v>
+        <v>854954</v>
       </c>
       <c r="R59" t="n">
-        <v>7477880</v>
+        <v>7478125</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6663,7 +6654,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6682,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855318</v>
+        <v>124855404</v>
       </c>
       <c r="B60" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6694,38 +6684,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854817</v>
+        <v>854832</v>
       </c>
       <c r="R60" t="n">
-        <v>7477931</v>
+        <v>7477880</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6766,6 +6760,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6784,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855380</v>
+        <v>124855313</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6796,25 +6791,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6824,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854745</v>
+        <v>854814</v>
       </c>
       <c r="R61" t="n">
-        <v>7477946</v>
+        <v>7477852</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6868,7 +6863,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6887,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124854790</v>
+        <v>124855536</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6899,42 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854766</v>
+        <v>854869</v>
       </c>
       <c r="R62" t="n">
-        <v>7478012</v>
+        <v>7477778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,12 +6951,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6975,7 +6970,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6988,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855468</v>
+        <v>124855277</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7006,25 +7000,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7034,10 +7028,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855069</v>
+        <v>855068</v>
       </c>
       <c r="R63" t="n">
-        <v>7477999</v>
+        <v>7478046</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7096,10 +7090,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855328</v>
+        <v>124854790</v>
       </c>
       <c r="B64" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7108,38 +7102,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854802</v>
+        <v>854766</v>
       </c>
       <c r="R64" t="n">
-        <v>7477769</v>
+        <v>7478012</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,17 +7164,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7185,6 +7178,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7203,10 +7197,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855524</v>
+        <v>124855371</v>
       </c>
       <c r="B65" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7215,38 +7209,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854793</v>
+        <v>854845</v>
       </c>
       <c r="R65" t="n">
-        <v>7477805</v>
+        <v>7477869</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,12 +7271,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7287,6 +7285,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7305,7 +7304,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855421</v>
+        <v>124855401</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7338,17 +7337,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854951</v>
+        <v>854928</v>
       </c>
       <c r="R66" t="n">
-        <v>7477899</v>
+        <v>7477769</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,12 +7378,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7389,6 +7392,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7407,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855277</v>
+        <v>124855358</v>
       </c>
       <c r="B67" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7419,38 +7423,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855068</v>
+        <v>854772</v>
       </c>
       <c r="R67" t="n">
-        <v>7478046</v>
+        <v>7477881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7485,12 +7489,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7509,10 +7519,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855250</v>
+        <v>124855394</v>
       </c>
       <c r="B68" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7521,38 +7531,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854814</v>
+        <v>854897</v>
       </c>
       <c r="R68" t="n">
-        <v>7477852</v>
+        <v>7477846</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7593,6 +7607,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7626,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855483</v>
+        <v>124855329</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>56725</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7623,38 +7638,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855251</v>
+        <v>854676</v>
       </c>
       <c r="R69" t="n">
-        <v>7478036</v>
+        <v>7477840</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,12 +7696,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7713,10 +7733,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855482</v>
+        <v>124855366</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7725,38 +7745,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855134</v>
+        <v>854807</v>
       </c>
       <c r="R70" t="n">
-        <v>7477890</v>
+        <v>7477926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,6 +7821,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7840,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855317</v>
+        <v>124855475</v>
       </c>
       <c r="B71" t="n">
-        <v>96985</v>
+        <v>56714</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7827,25 +7852,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7855,10 +7880,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854783</v>
+        <v>854813</v>
       </c>
       <c r="R71" t="n">
-        <v>7477935</v>
+        <v>7477923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,7 +7942,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855366</v>
+        <v>124855466</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7950,21 +7975,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854807</v>
+        <v>854921</v>
       </c>
       <c r="R72" t="n">
-        <v>7477926</v>
+        <v>7478082</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8005,7 +8026,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8024,10 +8044,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855316</v>
+        <v>124855233</v>
       </c>
       <c r="B73" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8040,21 +8060,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8064,10 +8084,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855019</v>
+        <v>855073</v>
       </c>
       <c r="R73" t="n">
-        <v>7477888</v>
+        <v>7477920</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8126,10 +8146,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855359</v>
+        <v>124855316</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8138,38 +8158,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854838</v>
+        <v>855019</v>
       </c>
       <c r="R74" t="n">
-        <v>7477840</v>
+        <v>7477888</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8204,18 +8224,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8234,7 +8248,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855424</v>
+        <v>124855415</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8274,10 +8288,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854780</v>
+        <v>854928</v>
       </c>
       <c r="R75" t="n">
-        <v>7477939</v>
+        <v>7478107</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,7 +8350,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855417</v>
+        <v>124855423</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8376,10 +8390,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855202</v>
+        <v>854915</v>
       </c>
       <c r="R76" t="n">
-        <v>7477976</v>
+        <v>7477851</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8438,10 +8452,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855244</v>
+        <v>124855232</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8450,25 +8464,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8478,10 +8492,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855187</v>
+        <v>855094</v>
       </c>
       <c r="R77" t="n">
-        <v>7478029</v>
+        <v>7477931</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8540,10 +8554,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855329</v>
+        <v>124855364</v>
       </c>
       <c r="B78" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8552,25 +8566,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8580,10 +8594,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854676</v>
+        <v>855120</v>
       </c>
       <c r="R78" t="n">
-        <v>7477840</v>
+        <v>7477887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8610,17 +8624,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8629,6 +8643,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8647,10 +8662,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855474</v>
+        <v>124855380</v>
       </c>
       <c r="B79" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8659,25 +8674,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8687,10 +8702,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855065</v>
+        <v>854745</v>
       </c>
       <c r="R79" t="n">
-        <v>7478197</v>
+        <v>7477946</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8731,6 +8746,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8749,7 +8765,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855420</v>
+        <v>124855418</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8789,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855071</v>
+        <v>855131</v>
       </c>
       <c r="R80" t="n">
-        <v>7477912</v>
+        <v>7477924</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8851,10 +8867,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855500</v>
+        <v>124855240</v>
       </c>
       <c r="B81" t="n">
-        <v>79826</v>
+        <v>105102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8867,21 +8883,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6457</v>
+        <v>221725</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8891,10 +8907,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854850</v>
+        <v>854937</v>
       </c>
       <c r="R81" t="n">
-        <v>7477915</v>
+        <v>7477782</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8921,12 +8937,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8953,10 +8969,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855512</v>
+        <v>124854791</v>
       </c>
       <c r="B82" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8965,20 +8981,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8989,14 +9005,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854911</v>
+        <v>854840</v>
       </c>
       <c r="R82" t="n">
-        <v>7478164</v>
+        <v>7477716</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9023,12 +9039,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9055,10 +9071,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855390</v>
+        <v>124855257</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9067,42 +9083,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854899</v>
+        <v>854894</v>
       </c>
       <c r="R83" t="n">
-        <v>7477831</v>
+        <v>7477768</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,12 +9141,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9143,7 +9160,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9162,7 +9178,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855358</v>
+        <v>124855381</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9198,14 +9214,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854772</v>
+        <v>854803</v>
       </c>
       <c r="R84" t="n">
-        <v>7477881</v>
+        <v>7477930</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9238,11 +9254,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9270,10 +9281,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855376</v>
+        <v>124855474</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9282,42 +9293,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854741</v>
+        <v>855065</v>
       </c>
       <c r="R85" t="n">
-        <v>7477958</v>
+        <v>7478197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9358,7 +9365,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9377,7 +9383,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855416</v>
+        <v>124855421</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9417,10 +9423,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855002</v>
+        <v>854951</v>
       </c>
       <c r="R86" t="n">
-        <v>7478149</v>
+        <v>7477899</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9479,7 +9485,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855401</v>
+        <v>124855417</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9512,21 +9518,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854928</v>
+        <v>855202</v>
       </c>
       <c r="R87" t="n">
-        <v>7477769</v>
+        <v>7477976</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9553,12 +9555,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9567,7 +9569,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9586,7 +9587,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855418</v>
+        <v>124855464</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9626,10 +9627,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855131</v>
+        <v>854898</v>
       </c>
       <c r="R88" t="n">
-        <v>7477924</v>
+        <v>7478156</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9688,10 +9689,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855467</v>
+        <v>124855244</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9700,25 +9701,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9728,10 +9729,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855062</v>
+        <v>855187</v>
       </c>
       <c r="R89" t="n">
-        <v>7478002</v>
+        <v>7478029</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9790,10 +9791,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855536</v>
+        <v>124855416</v>
       </c>
       <c r="B90" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9802,25 +9803,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9830,10 +9831,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854869</v>
+        <v>855002</v>
       </c>
       <c r="R90" t="n">
-        <v>7477778</v>
+        <v>7478149</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9860,17 +9861,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9897,7 +9893,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855364</v>
+        <v>124855467</v>
       </c>
       <c r="B91" t="n">
         <v>98101</v>
@@ -9933,14 +9929,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855120</v>
+        <v>855062</v>
       </c>
       <c r="R91" t="n">
-        <v>7477887</v>
+        <v>7478002</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9975,18 +9971,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10005,10 +9995,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855381</v>
+        <v>124855524</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10017,25 +10007,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10045,10 +10035,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854803</v>
+        <v>854793</v>
       </c>
       <c r="R92" t="n">
-        <v>7477930</v>
+        <v>7477805</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10075,12 +10065,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10089,7 +10079,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10108,10 +10097,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855333</v>
+        <v>124855328</v>
       </c>
       <c r="B93" t="n">
-        <v>79927</v>
+        <v>56725</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10124,34 +10113,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>102613</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854924</v>
+        <v>854802</v>
       </c>
       <c r="R93" t="n">
-        <v>7478087</v>
+        <v>7477769</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10178,12 +10167,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10210,10 +10204,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855233</v>
+        <v>124855386</v>
       </c>
       <c r="B94" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10222,38 +10216,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855073</v>
+        <v>854810</v>
       </c>
       <c r="R94" t="n">
-        <v>7477920</v>
+        <v>7477930</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10294,6 +10292,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10312,10 +10311,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855313</v>
+        <v>124855275</v>
       </c>
       <c r="B95" t="n">
-        <v>91299</v>
+        <v>92321</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10328,34 +10327,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854814</v>
+        <v>854889</v>
       </c>
       <c r="R95" t="n">
-        <v>7477852</v>
+        <v>7477847</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10414,10 +10413,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124854791</v>
+        <v>124855250</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10430,34 +10429,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854840</v>
+        <v>854814</v>
       </c>
       <c r="R96" t="n">
-        <v>7477716</v>
+        <v>7477852</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10484,12 +10483,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10516,10 +10515,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855232</v>
+        <v>124855468</v>
       </c>
       <c r="B97" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10528,25 +10527,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10556,10 +10555,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855094</v>
+        <v>855069</v>
       </c>
       <c r="R97" t="n">
-        <v>7477931</v>
+        <v>7477999</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10618,7 +10617,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855469</v>
+        <v>124855424</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10658,10 +10657,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854979</v>
+        <v>854780</v>
       </c>
       <c r="R98" t="n">
-        <v>7477885</v>
+        <v>7477939</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10720,10 +10719,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855466</v>
+        <v>124855500</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10732,25 +10731,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,10 +10759,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854921</v>
+        <v>854850</v>
       </c>
       <c r="R99" t="n">
-        <v>7478082</v>
+        <v>7477915</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10822,10 +10821,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855386</v>
+        <v>124855483</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10834,42 +10833,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854810</v>
+        <v>855251</v>
       </c>
       <c r="R100" t="n">
-        <v>7477930</v>
+        <v>7478036</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10910,7 +10905,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10929,10 +10923,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855475</v>
+        <v>124855359</v>
       </c>
       <c r="B101" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10941,38 +10935,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854813</v>
+        <v>854838</v>
       </c>
       <c r="R101" t="n">
-        <v>7477923</v>
+        <v>7477840</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11007,12 +11001,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11031,7 +11031,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855415</v>
+        <v>124855389</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11064,17 +11064,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854928</v>
+        <v>854906</v>
       </c>
       <c r="R102" t="n">
-        <v>7478107</v>
+        <v>7477891</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11115,6 +11119,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11133,7 +11138,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855371</v>
+        <v>124855376</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11168,7 +11173,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>71</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11177,10 +11182,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854845</v>
+        <v>854741</v>
       </c>
       <c r="R103" t="n">
-        <v>7477869</v>
+        <v>7477958</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11240,10 +11245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855464</v>
+        <v>124855333</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11252,25 +11257,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11280,10 +11285,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854898</v>
+        <v>854924</v>
       </c>
       <c r="R104" t="n">
-        <v>7478156</v>
+        <v>7478087</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11342,10 +11347,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855231</v>
+        <v>124855318</v>
       </c>
       <c r="B105" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11358,21 +11363,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11382,10 +11387,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854954</v>
+        <v>854817</v>
       </c>
       <c r="R105" t="n">
-        <v>7478125</v>
+        <v>7477931</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11444,10 +11449,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855257</v>
+        <v>124855482</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11460,21 +11465,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11484,10 +11489,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854894</v>
+        <v>855134</v>
       </c>
       <c r="R106" t="n">
-        <v>7477768</v>
+        <v>7477890</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11514,17 +11519,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11551,7 +11551,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855394</v>
+        <v>124855469</v>
       </c>
       <c r="B107" t="n">
         <v>98101</v>
@@ -11584,21 +11584,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854897</v>
+        <v>854979</v>
       </c>
       <c r="R107" t="n">
-        <v>7477846</v>
+        <v>7477885</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11639,7 +11635,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11658,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855275</v>
+        <v>124855390</v>
       </c>
       <c r="B108" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11670,38 +11665,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854889</v>
+        <v>854899</v>
       </c>
       <c r="R108" t="n">
-        <v>7477847</v>
+        <v>7477831</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11742,6 +11741,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11760,10 +11760,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855240</v>
+        <v>124855317</v>
       </c>
       <c r="B109" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11776,21 +11776,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854937</v>
+        <v>854783</v>
       </c>
       <c r="R109" t="n">
-        <v>7477782</v>
+        <v>7477935</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11830,12 +11830,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427356</v>
+        <v>124427375</v>
       </c>
       <c r="B36" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,34 +4175,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854977</v>
+        <v>854922</v>
       </c>
       <c r="R36" t="n">
-        <v>7478167</v>
+        <v>7478323</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,8 +4243,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4261,10 +4277,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427345</v>
+        <v>124427351</v>
       </c>
       <c r="B37" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,38 +4289,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854967</v>
+        <v>855056</v>
       </c>
       <c r="R37" t="n">
-        <v>7478177</v>
+        <v>7478165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,6 +4365,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427347</v>
+        <v>124427389</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4396,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855063</v>
+        <v>855110</v>
       </c>
       <c r="R38" t="n">
-        <v>7478044</v>
+        <v>7478072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,6 +4472,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4465,10 +4491,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427401</v>
+        <v>124427391</v>
       </c>
       <c r="B39" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,38 +4503,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855011</v>
+        <v>855091</v>
       </c>
       <c r="R39" t="n">
-        <v>7478352</v>
+        <v>7478207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,6 +4579,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4567,10 +4598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427365</v>
+        <v>124427401</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
+        <v>82597</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4583,21 +4614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4607,10 +4638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854939</v>
+        <v>855011</v>
       </c>
       <c r="R40" t="n">
-        <v>7478324</v>
+        <v>7478352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,10 +4700,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427406</v>
+        <v>124427386</v>
       </c>
       <c r="B41" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,41 +4716,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855096</v>
+        <v>855066</v>
       </c>
       <c r="R41" t="n">
-        <v>7478199</v>
+        <v>7478180</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4752,11 +4780,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,10 +4807,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427369</v>
+        <v>124427388</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,38 +4819,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854943</v>
+        <v>855074</v>
       </c>
       <c r="R42" t="n">
-        <v>7478362</v>
+        <v>7478164</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4868,6 +4895,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4886,10 +4914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427403</v>
+        <v>124427352</v>
       </c>
       <c r="B43" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,38 +4926,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854946</v>
+        <v>855059</v>
       </c>
       <c r="R43" t="n">
-        <v>7478367</v>
+        <v>7478173</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,10 +5021,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427399</v>
+        <v>124427387</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5001,38 +5033,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855007</v>
+        <v>855102</v>
       </c>
       <c r="R44" t="n">
-        <v>7478357</v>
+        <v>7478191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5073,6 +5109,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5091,10 +5128,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427389</v>
+        <v>124427406</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,38 +5144,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855110</v>
+        <v>855096</v>
       </c>
       <c r="R45" t="n">
-        <v>7478072</v>
+        <v>7478199</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5171,6 +5211,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5198,10 +5243,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427354</v>
+        <v>124427403</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5210,38 +5255,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855018</v>
+        <v>854946</v>
       </c>
       <c r="R46" t="n">
-        <v>7478119</v>
+        <v>7478367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,6 +5327,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5300,10 +5346,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427375</v>
+        <v>124427398</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5312,25 +5358,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5340,10 +5386,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854922</v>
+        <v>855100</v>
       </c>
       <c r="R47" t="n">
-        <v>7478323</v>
+        <v>7478058</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,24 +5430,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5418,10 +5448,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B48" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5434,34 +5464,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R48" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5520,10 +5550,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427387</v>
+        <v>124427393</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5532,42 +5562,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855102</v>
+        <v>854990</v>
       </c>
       <c r="R49" t="n">
-        <v>7478191</v>
+        <v>7478363</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5608,7 +5634,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5627,10 +5652,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427351</v>
+        <v>124427345</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5639,42 +5664,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855056</v>
+        <v>854967</v>
       </c>
       <c r="R50" t="n">
-        <v>7478165</v>
+        <v>7478177</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,7 +5736,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5734,10 +5754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5746,42 +5766,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R51" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5822,7 +5838,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5856,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427391</v>
+        <v>124427347</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,42 +5868,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855091</v>
+        <v>855063</v>
       </c>
       <c r="R52" t="n">
-        <v>7478207</v>
+        <v>7478044</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,7 +5940,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5948,10 +5958,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427398</v>
+        <v>124427356</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5960,20 +5970,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5984,14 +5994,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855100</v>
+        <v>854977</v>
       </c>
       <c r="R53" t="n">
-        <v>7478058</v>
+        <v>7478167</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6050,10 +6060,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427346</v>
+        <v>124427365</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6062,38 +6072,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855044</v>
+        <v>854939</v>
       </c>
       <c r="R54" t="n">
-        <v>7478074</v>
+        <v>7478324</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6152,10 +6162,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427388</v>
+        <v>124427369</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,42 +6174,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855074</v>
+        <v>854943</v>
       </c>
       <c r="R55" t="n">
-        <v>7478164</v>
+        <v>7478362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,7 +6246,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6259,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427386</v>
+        <v>124427399</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,42 +6276,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855066</v>
+        <v>855007</v>
       </c>
       <c r="R56" t="n">
-        <v>7478180</v>
+        <v>7478357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,7 +6348,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855512</v>
+        <v>124855421</v>
       </c>
       <c r="B57" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,25 +6378,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854911</v>
+        <v>854951</v>
       </c>
       <c r="R57" t="n">
-        <v>7478164</v>
+        <v>7477899</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855420</v>
+        <v>124855404</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6501,17 +6501,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855071</v>
+        <v>854832</v>
       </c>
       <c r="R58" t="n">
-        <v>7477912</v>
+        <v>7477880</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6556,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855231</v>
+        <v>124855418</v>
       </c>
       <c r="B59" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6587,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854954</v>
+        <v>855131</v>
       </c>
       <c r="R59" t="n">
-        <v>7478125</v>
+        <v>7477924</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855404</v>
+        <v>124855317</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,42 +6689,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854832</v>
+        <v>854783</v>
       </c>
       <c r="R60" t="n">
-        <v>7477880</v>
+        <v>7477935</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6760,7 +6761,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855313</v>
+        <v>124855250</v>
       </c>
       <c r="B61" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855536</v>
+        <v>124855475</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6897,16 +6897,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854869</v>
+        <v>854813</v>
       </c>
       <c r="R62" t="n">
-        <v>7477778</v>
+        <v>7477923</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,17 +6951,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6988,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855277</v>
+        <v>124855381</v>
       </c>
       <c r="B63" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7000,25 +6995,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7028,10 +7023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855068</v>
+        <v>854803</v>
       </c>
       <c r="R63" t="n">
-        <v>7478046</v>
+        <v>7477930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,6 +7067,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7090,7 +7086,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124854790</v>
+        <v>124855423</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7123,21 +7119,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854766</v>
+        <v>854915</v>
       </c>
       <c r="R64" t="n">
-        <v>7478012</v>
+        <v>7477851</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7178,7 +7170,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7197,10 +7188,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855371</v>
+        <v>124855275</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7209,42 +7200,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854845</v>
+        <v>854889</v>
       </c>
       <c r="R65" t="n">
-        <v>7477869</v>
+        <v>7477847</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7285,7 +7272,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7304,10 +7290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855401</v>
+        <v>124855232</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7316,42 +7302,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854928</v>
+        <v>855094</v>
       </c>
       <c r="R66" t="n">
-        <v>7477769</v>
+        <v>7477931</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7378,12 +7360,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7392,7 +7374,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7411,7 +7392,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855358</v>
+        <v>124855390</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7444,17 +7425,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854772</v>
+        <v>854899</v>
       </c>
       <c r="R67" t="n">
-        <v>7477881</v>
+        <v>7477831</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7487,11 +7472,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7519,7 +7499,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855394</v>
+        <v>124855358</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7552,21 +7532,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854897</v>
+        <v>854772</v>
       </c>
       <c r="R68" t="n">
-        <v>7477846</v>
+        <v>7477881</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7599,6 +7575,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7626,10 +7607,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855329</v>
+        <v>124855257</v>
       </c>
       <c r="B69" t="n">
-        <v>56725</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7638,20 +7619,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7662,14 +7643,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854676</v>
+        <v>854894</v>
       </c>
       <c r="R69" t="n">
-        <v>7477840</v>
+        <v>7477768</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7706,7 +7687,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7733,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855366</v>
+        <v>124854791</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7745,42 +7726,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854807</v>
+        <v>854840</v>
       </c>
       <c r="R70" t="n">
-        <v>7477926</v>
+        <v>7477716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7807,12 +7784,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7821,7 +7798,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7840,10 +7816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855475</v>
+        <v>124855464</v>
       </c>
       <c r="B71" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7852,25 +7828,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7880,10 +7856,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854813</v>
+        <v>854898</v>
       </c>
       <c r="R71" t="n">
-        <v>7477923</v>
+        <v>7478156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7942,7 +7918,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855466</v>
+        <v>124855389</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7975,17 +7951,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854921</v>
+        <v>854906</v>
       </c>
       <c r="R72" t="n">
-        <v>7478082</v>
+        <v>7477891</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8026,6 +8006,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8044,10 +8025,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855233</v>
+        <v>124855424</v>
       </c>
       <c r="B73" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8056,25 +8037,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8084,10 +8065,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855073</v>
+        <v>854780</v>
       </c>
       <c r="R73" t="n">
-        <v>7477920</v>
+        <v>7477939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8146,10 +8127,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855316</v>
+        <v>124855467</v>
       </c>
       <c r="B74" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8158,25 +8139,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8186,10 +8167,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855019</v>
+        <v>855062</v>
       </c>
       <c r="R74" t="n">
-        <v>7477888</v>
+        <v>7478002</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8248,10 +8229,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855415</v>
+        <v>124855330</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8260,38 +8241,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854928</v>
+        <v>854676</v>
       </c>
       <c r="R75" t="n">
-        <v>7478107</v>
+        <v>7477840</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8324,6 +8313,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8350,7 +8344,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855423</v>
+        <v>124855386</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8383,17 +8377,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854915</v>
+        <v>854810</v>
       </c>
       <c r="R76" t="n">
-        <v>7477851</v>
+        <v>7477930</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8434,6 +8432,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8452,10 +8451,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855232</v>
+        <v>124855277</v>
       </c>
       <c r="B77" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8468,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8492,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855094</v>
+        <v>855068</v>
       </c>
       <c r="R77" t="n">
-        <v>7477931</v>
+        <v>7478046</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8554,7 +8553,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855364</v>
+        <v>124855415</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8590,14 +8589,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855120</v>
+        <v>854928</v>
       </c>
       <c r="R78" t="n">
-        <v>7477887</v>
+        <v>7478107</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8632,18 +8631,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8662,7 +8655,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855380</v>
+        <v>124855394</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8695,17 +8688,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854745</v>
+        <v>854897</v>
       </c>
       <c r="R79" t="n">
-        <v>7477946</v>
+        <v>7477846</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8765,7 +8762,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855418</v>
+        <v>124855469</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8805,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855131</v>
+        <v>854979</v>
       </c>
       <c r="R80" t="n">
-        <v>7477924</v>
+        <v>7477885</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8867,10 +8864,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855240</v>
+        <v>124855468</v>
       </c>
       <c r="B81" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8879,25 +8876,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8907,10 +8904,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854937</v>
+        <v>855069</v>
       </c>
       <c r="R81" t="n">
-        <v>7477782</v>
+        <v>7477999</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8937,12 +8934,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8969,10 +8966,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124854791</v>
+        <v>124855420</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8981,38 +8978,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854840</v>
+        <v>855071</v>
       </c>
       <c r="R82" t="n">
-        <v>7477716</v>
+        <v>7477912</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9039,12 +9036,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9071,10 +9068,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855257</v>
+        <v>124855466</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9083,25 +9080,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9111,10 +9108,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854894</v>
+        <v>854921</v>
       </c>
       <c r="R83" t="n">
-        <v>7477768</v>
+        <v>7478082</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9141,17 +9138,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9178,10 +9170,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855381</v>
+        <v>124855328</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9190,38 +9182,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854803</v>
+        <v>854802</v>
       </c>
       <c r="R84" t="n">
-        <v>7477930</v>
+        <v>7477769</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9248,12 +9240,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9262,7 +9259,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9281,10 +9277,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855474</v>
+        <v>124855359</v>
       </c>
       <c r="B85" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9293,38 +9289,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855065</v>
+        <v>854838</v>
       </c>
       <c r="R85" t="n">
-        <v>7478197</v>
+        <v>7477840</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9359,12 +9355,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9383,10 +9385,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855421</v>
+        <v>124855483</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9395,25 +9397,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9423,10 +9425,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854951</v>
+        <v>855251</v>
       </c>
       <c r="R86" t="n">
-        <v>7477899</v>
+        <v>7478036</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9485,7 +9487,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855417</v>
+        <v>124855366</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9518,17 +9520,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855202</v>
+        <v>854807</v>
       </c>
       <c r="R87" t="n">
-        <v>7477976</v>
+        <v>7477926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9569,6 +9575,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9587,7 +9594,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855464</v>
+        <v>124855376</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9620,17 +9627,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854898</v>
+        <v>854741</v>
       </c>
       <c r="R88" t="n">
-        <v>7478156</v>
+        <v>7477958</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9671,6 +9682,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9689,10 +9701,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855244</v>
+        <v>124855316</v>
       </c>
       <c r="B89" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9701,25 +9713,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9729,10 +9741,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855187</v>
+        <v>855019</v>
       </c>
       <c r="R89" t="n">
-        <v>7478029</v>
+        <v>7477888</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9791,10 +9803,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855416</v>
+        <v>124855318</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9803,25 +9815,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9831,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855002</v>
+        <v>854817</v>
       </c>
       <c r="R90" t="n">
-        <v>7478149</v>
+        <v>7477931</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9893,7 +9905,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855467</v>
+        <v>124855371</v>
       </c>
       <c r="B91" t="n">
         <v>98101</v>
@@ -9926,17 +9938,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855062</v>
+        <v>854845</v>
       </c>
       <c r="R91" t="n">
-        <v>7478002</v>
+        <v>7477869</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9977,6 +9993,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9995,10 +10012,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855524</v>
+        <v>124855240</v>
       </c>
       <c r="B92" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10011,21 +10028,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10035,10 +10052,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854793</v>
+        <v>854937</v>
       </c>
       <c r="R92" t="n">
-        <v>7477805</v>
+        <v>7477782</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10097,10 +10114,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855328</v>
+        <v>124855233</v>
       </c>
       <c r="B93" t="n">
-        <v>56725</v>
+        <v>105102</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10113,34 +10130,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102613</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854802</v>
+        <v>855073</v>
       </c>
       <c r="R93" t="n">
-        <v>7477769</v>
+        <v>7477920</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10167,17 +10184,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10204,10 +10216,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855386</v>
+        <v>124855313</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10216,42 +10228,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854810</v>
+        <v>854814</v>
       </c>
       <c r="R94" t="n">
-        <v>7477930</v>
+        <v>7477852</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10292,7 +10300,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10311,10 +10318,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855275</v>
+        <v>124855512</v>
       </c>
       <c r="B95" t="n">
-        <v>92321</v>
+        <v>79926</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10323,38 +10330,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854889</v>
+        <v>854911</v>
       </c>
       <c r="R95" t="n">
-        <v>7477847</v>
+        <v>7478164</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10413,10 +10420,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855250</v>
+        <v>124855474</v>
       </c>
       <c r="B96" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10429,21 +10436,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10453,10 +10460,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854814</v>
+        <v>855065</v>
       </c>
       <c r="R96" t="n">
-        <v>7477852</v>
+        <v>7478197</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10515,10 +10522,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855468</v>
+        <v>124855231</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10527,25 +10534,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10555,10 +10562,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855069</v>
+        <v>854954</v>
       </c>
       <c r="R97" t="n">
-        <v>7477999</v>
+        <v>7478125</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10617,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855424</v>
+        <v>124855500</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10629,25 +10636,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10657,10 +10664,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854780</v>
+        <v>854850</v>
       </c>
       <c r="R98" t="n">
-        <v>7477939</v>
+        <v>7477915</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10719,10 +10726,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855500</v>
+        <v>124855482</v>
       </c>
       <c r="B99" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10731,25 +10738,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10759,10 +10766,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854850</v>
+        <v>855134</v>
       </c>
       <c r="R99" t="n">
-        <v>7477915</v>
+        <v>7477890</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10821,10 +10828,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855483</v>
+        <v>124854790</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10833,38 +10840,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855251</v>
+        <v>854766</v>
       </c>
       <c r="R100" t="n">
-        <v>7478036</v>
+        <v>7478012</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10905,6 +10916,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10923,10 +10935,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855359</v>
+        <v>124855536</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10935,38 +10947,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854838</v>
+        <v>854869</v>
       </c>
       <c r="R101" t="n">
-        <v>7477840</v>
+        <v>7477778</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10993,17 +11005,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11012,7 +11024,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11031,10 +11042,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855389</v>
+        <v>124855244</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11043,42 +11054,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854906</v>
+        <v>855187</v>
       </c>
       <c r="R102" t="n">
-        <v>7477891</v>
+        <v>7478029</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11119,7 +11126,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11138,10 +11144,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855376</v>
+        <v>124855524</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11150,42 +11156,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854741</v>
+        <v>854793</v>
       </c>
       <c r="R103" t="n">
-        <v>7477958</v>
+        <v>7477805</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11212,12 +11214,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11226,7 +11228,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11245,10 +11246,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855333</v>
+        <v>124855417</v>
       </c>
       <c r="B104" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11257,25 +11258,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11286,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854924</v>
+        <v>855202</v>
       </c>
       <c r="R104" t="n">
-        <v>7478087</v>
+        <v>7477976</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,10 +11348,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855318</v>
+        <v>124855401</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11359,38 +11360,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854817</v>
+        <v>854928</v>
       </c>
       <c r="R105" t="n">
-        <v>7477931</v>
+        <v>7477769</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11417,12 +11422,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11431,6 +11436,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11449,10 +11455,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855482</v>
+        <v>124855380</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11461,25 +11467,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11489,10 +11495,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855134</v>
+        <v>854745</v>
       </c>
       <c r="R106" t="n">
-        <v>7477890</v>
+        <v>7477946</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11533,6 +11539,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11551,10 +11558,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855469</v>
+        <v>124855333</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11570,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854979</v>
+        <v>854924</v>
       </c>
       <c r="R107" t="n">
-        <v>7477885</v>
+        <v>7478087</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,7 +11660,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855390</v>
+        <v>124855364</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11686,21 +11693,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854899</v>
+        <v>855120</v>
       </c>
       <c r="R108" t="n">
-        <v>7477831</v>
+        <v>7477887</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11733,6 +11736,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11760,10 +11768,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855317</v>
+        <v>124855416</v>
       </c>
       <c r="B109" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11772,25 +11780,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11808,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854783</v>
+        <v>855002</v>
       </c>
       <c r="R109" t="n">
-        <v>7477935</v>
+        <v>7478149</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4384,7 +4384,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R38" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427391</v>
+        <v>124427389</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855091</v>
+        <v>855110</v>
       </c>
       <c r="R39" t="n">
-        <v>7478207</v>
+        <v>7478072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -7086,10 +7086,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855423</v>
+        <v>124855232</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7098,25 +7098,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854915</v>
+        <v>855094</v>
       </c>
       <c r="R64" t="n">
-        <v>7477851</v>
+        <v>7477931</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7188,10 +7188,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855275</v>
+        <v>124855390</v>
       </c>
       <c r="B65" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7200,38 +7200,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854889</v>
+        <v>854899</v>
       </c>
       <c r="R65" t="n">
-        <v>7477847</v>
+        <v>7477831</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7272,6 +7276,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7290,10 +7295,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855232</v>
+        <v>124855358</v>
       </c>
       <c r="B66" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7302,38 +7307,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855094</v>
+        <v>854772</v>
       </c>
       <c r="R66" t="n">
-        <v>7477931</v>
+        <v>7477881</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7368,12 +7373,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7392,10 +7403,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855390</v>
+        <v>124855257</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7404,42 +7415,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854899</v>
+        <v>854894</v>
       </c>
       <c r="R67" t="n">
-        <v>7477831</v>
+        <v>7477768</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7466,12 +7473,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7480,7 +7492,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7499,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855358</v>
+        <v>124854791</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7511,25 +7522,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7539,10 +7550,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854772</v>
+        <v>854840</v>
       </c>
       <c r="R68" t="n">
-        <v>7477881</v>
+        <v>7477716</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,17 +7580,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7588,7 +7594,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7607,10 +7612,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855257</v>
+        <v>124855423</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7619,25 +7624,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7647,10 +7652,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854894</v>
+        <v>854915</v>
       </c>
       <c r="R69" t="n">
-        <v>7477768</v>
+        <v>7477851</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,17 +7682,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7714,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124854791</v>
+        <v>124855275</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>92321</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7730,21 +7730,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7754,10 +7754,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854840</v>
+        <v>854889</v>
       </c>
       <c r="R70" t="n">
-        <v>7477716</v>
+        <v>7477847</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7816,7 +7816,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855464</v>
+        <v>124855389</v>
       </c>
       <c r="B71" t="n">
         <v>98101</v>
@@ -7849,17 +7849,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854898</v>
+        <v>854906</v>
       </c>
       <c r="R71" t="n">
-        <v>7478156</v>
+        <v>7477891</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7900,6 +7904,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7918,7 +7923,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855389</v>
+        <v>124855424</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7951,21 +7956,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854906</v>
+        <v>854780</v>
       </c>
       <c r="R72" t="n">
-        <v>7477891</v>
+        <v>7477939</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8006,7 +8007,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855424</v>
+        <v>124855464</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854780</v>
+        <v>854898</v>
       </c>
       <c r="R73" t="n">
-        <v>7477939</v>
+        <v>7478156</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855483</v>
+        <v>124855366</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9397,38 +9397,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855251</v>
+        <v>854807</v>
       </c>
       <c r="R86" t="n">
-        <v>7478036</v>
+        <v>7477926</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9469,6 +9473,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9487,10 +9492,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855366</v>
+        <v>124855483</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9499,42 +9504,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854807</v>
+        <v>855251</v>
       </c>
       <c r="R87" t="n">
-        <v>7477926</v>
+        <v>7478036</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9575,7 +9576,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427375</v>
+        <v>124427351</v>
       </c>
       <c r="B36" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854922</v>
+        <v>855056</v>
       </c>
       <c r="R36" t="n">
-        <v>7478323</v>
+        <v>7478165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4246,21 +4250,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4277,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427351</v>
+        <v>124427365</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,42 +4278,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855056</v>
+        <v>854939</v>
       </c>
       <c r="R37" t="n">
-        <v>7478165</v>
+        <v>7478324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4365,7 +4350,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427391</v>
+        <v>124427401</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,42 +4380,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855091</v>
+        <v>855011</v>
       </c>
       <c r="R38" t="n">
-        <v>7478207</v>
+        <v>7478352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4472,7 +4452,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4491,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427389</v>
+        <v>124427369</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4503,42 +4482,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855110</v>
+        <v>854943</v>
       </c>
       <c r="R39" t="n">
-        <v>7478072</v>
+        <v>7478362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,7 +4554,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4598,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427401</v>
+        <v>124427386</v>
       </c>
       <c r="B40" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4610,38 +4584,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855011</v>
+        <v>855066</v>
       </c>
       <c r="R40" t="n">
-        <v>7478352</v>
+        <v>7478180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4682,6 +4660,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4700,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427386</v>
+        <v>124427356</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4712,42 +4691,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855066</v>
+        <v>854977</v>
       </c>
       <c r="R41" t="n">
-        <v>7478180</v>
+        <v>7478167</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4788,7 +4763,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4807,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427388</v>
+        <v>124427399</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4819,42 +4793,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855074</v>
+        <v>855007</v>
       </c>
       <c r="R42" t="n">
-        <v>7478164</v>
+        <v>7478357</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4895,7 +4865,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4914,7 +4883,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427352</v>
+        <v>124427389</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -4949,19 +4918,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855059</v>
+        <v>855110</v>
       </c>
       <c r="R43" t="n">
-        <v>7478173</v>
+        <v>7478072</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5021,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427387</v>
+        <v>124427345</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5033,42 +5002,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855102</v>
+        <v>854967</v>
       </c>
       <c r="R44" t="n">
-        <v>7478191</v>
+        <v>7478177</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,7 +5074,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5128,10 +5092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427406</v>
+        <v>124427388</v>
       </c>
       <c r="B45" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5144,41 +5108,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855096</v>
+        <v>855074</v>
       </c>
       <c r="R45" t="n">
-        <v>7478199</v>
+        <v>7478164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5211,11 +5172,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5243,10 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427403</v>
+        <v>124427398</v>
       </c>
       <c r="B46" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5255,25 +5211,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5283,10 +5239,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854946</v>
+        <v>855100</v>
       </c>
       <c r="R46" t="n">
-        <v>7478367</v>
+        <v>7478058</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5327,7 +5283,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5346,10 +5301,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427398</v>
+        <v>124427352</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5358,38 +5313,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855100</v>
+        <v>855059</v>
       </c>
       <c r="R47" t="n">
-        <v>7478058</v>
+        <v>7478173</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,6 +5389,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5448,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427354</v>
+        <v>124427387</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5460,38 +5420,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855018</v>
+        <v>855102</v>
       </c>
       <c r="R48" t="n">
-        <v>7478119</v>
+        <v>7478191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5532,6 +5496,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5515,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5566,34 +5531,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5652,7 +5617,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427345</v>
+        <v>124427346</v>
       </c>
       <c r="B50" t="n">
         <v>79927</v>
@@ -5692,10 +5657,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854967</v>
+        <v>855044</v>
       </c>
       <c r="R50" t="n">
-        <v>7478177</v>
+        <v>7478074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,10 +5719,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427346</v>
+        <v>124427406</v>
       </c>
       <c r="B51" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5766,38 +5731,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855044</v>
+        <v>855096</v>
       </c>
       <c r="R51" t="n">
-        <v>7478074</v>
+        <v>7478199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5832,12 +5804,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5856,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427347</v>
+        <v>124427391</v>
       </c>
       <c r="B52" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5868,38 +5846,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R52" t="n">
-        <v>7478044</v>
+        <v>7478207</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5940,6 +5922,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5958,10 +5941,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427356</v>
+        <v>124427375</v>
       </c>
       <c r="B53" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5974,34 +5957,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854977</v>
+        <v>854922</v>
       </c>
       <c r="R53" t="n">
-        <v>7478167</v>
+        <v>7478323</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6042,8 +6025,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6060,10 +6059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427365</v>
+        <v>124427347</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6072,38 +6071,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854939</v>
+        <v>855063</v>
       </c>
       <c r="R54" t="n">
-        <v>7478324</v>
+        <v>7478044</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6162,10 +6161,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427369</v>
+        <v>124427393</v>
       </c>
       <c r="B55" t="n">
-        <v>57666</v>
+        <v>56714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6178,21 +6177,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6202,10 +6201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854943</v>
+        <v>854990</v>
       </c>
       <c r="R55" t="n">
-        <v>7478362</v>
+        <v>7478363</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427399</v>
+        <v>124427403</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,25 +6275,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6304,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855007</v>
+        <v>854946</v>
       </c>
       <c r="R56" t="n">
-        <v>7478357</v>
+        <v>7478367</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,6 +6347,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855421</v>
+        <v>124855475</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,25 +6378,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854951</v>
+        <v>854813</v>
       </c>
       <c r="R57" t="n">
-        <v>7477899</v>
+        <v>7477923</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855404</v>
+        <v>124855417</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6501,21 +6501,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854832</v>
+        <v>855202</v>
       </c>
       <c r="R58" t="n">
-        <v>7477880</v>
+        <v>7477976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6556,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6575,7 +6570,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855418</v>
+        <v>124855376</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6608,17 +6603,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855131</v>
+        <v>854741</v>
       </c>
       <c r="R59" t="n">
-        <v>7477924</v>
+        <v>7477958</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6659,6 +6658,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855317</v>
+        <v>124855536</v>
       </c>
       <c r="B60" t="n">
-        <v>96985</v>
+        <v>57529</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,25 +6689,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854783</v>
+        <v>854869</v>
       </c>
       <c r="R60" t="n">
-        <v>7477935</v>
+        <v>7477778</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6747,12 +6747,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6779,7 +6784,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855250</v>
+        <v>124855244</v>
       </c>
       <c r="B61" t="n">
         <v>91012</v>
@@ -6819,10 +6824,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854814</v>
+        <v>855187</v>
       </c>
       <c r="R61" t="n">
-        <v>7477852</v>
+        <v>7478029</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6886,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855475</v>
+        <v>124855358</v>
       </c>
       <c r="B62" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6898,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854813</v>
+        <v>854772</v>
       </c>
       <c r="R62" t="n">
-        <v>7477923</v>
+        <v>7477881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6959,12 +6964,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6983,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855381</v>
+        <v>124854791</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6995,38 +7006,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854803</v>
+        <v>854840</v>
       </c>
       <c r="R63" t="n">
-        <v>7477930</v>
+        <v>7477716</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7053,12 +7064,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7067,7 +7078,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7086,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855232</v>
+        <v>124855421</v>
       </c>
       <c r="B64" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7098,25 +7108,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7126,10 +7136,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855094</v>
+        <v>854951</v>
       </c>
       <c r="R64" t="n">
-        <v>7477931</v>
+        <v>7477899</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7188,7 +7198,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855390</v>
+        <v>124855389</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7223,7 +7233,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7232,10 +7242,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854899</v>
+        <v>854906</v>
       </c>
       <c r="R65" t="n">
-        <v>7477831</v>
+        <v>7477891</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7295,7 +7305,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855358</v>
+        <v>124855359</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7335,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854772</v>
+        <v>854838</v>
       </c>
       <c r="R66" t="n">
-        <v>7477881</v>
+        <v>7477840</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7403,10 +7413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855257</v>
+        <v>124855277</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7415,25 +7425,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854894</v>
+        <v>855068</v>
       </c>
       <c r="R67" t="n">
-        <v>7477768</v>
+        <v>7478046</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7473,17 +7483,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7510,10 +7515,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124854791</v>
+        <v>124855512</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7522,20 +7527,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7546,14 +7551,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854840</v>
+        <v>854911</v>
       </c>
       <c r="R68" t="n">
-        <v>7477716</v>
+        <v>7478164</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7580,12 +7585,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7612,7 +7617,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855423</v>
+        <v>124855394</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -7645,17 +7650,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854915</v>
+        <v>854897</v>
       </c>
       <c r="R69" t="n">
-        <v>7477851</v>
+        <v>7477846</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7696,6 +7705,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7714,10 +7724,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855275</v>
+        <v>124855423</v>
       </c>
       <c r="B70" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,38 +7736,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854889</v>
+        <v>854915</v>
       </c>
       <c r="R70" t="n">
-        <v>7477847</v>
+        <v>7477851</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7816,7 +7826,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855389</v>
+        <v>124855424</v>
       </c>
       <c r="B71" t="n">
         <v>98101</v>
@@ -7849,21 +7859,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854906</v>
+        <v>854780</v>
       </c>
       <c r="R71" t="n">
-        <v>7477891</v>
+        <v>7477939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7904,7 +7910,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7923,7 +7928,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855424</v>
+        <v>124855468</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7963,10 +7968,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854780</v>
+        <v>855069</v>
       </c>
       <c r="R72" t="n">
-        <v>7477939</v>
+        <v>7477999</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8025,10 +8030,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855464</v>
+        <v>124855500</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8037,25 +8042,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8065,10 +8070,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854898</v>
+        <v>854850</v>
       </c>
       <c r="R73" t="n">
-        <v>7478156</v>
+        <v>7477915</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8127,10 +8132,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855467</v>
+        <v>124855328</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8139,38 +8144,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855062</v>
+        <v>854802</v>
       </c>
       <c r="R74" t="n">
-        <v>7478002</v>
+        <v>7477769</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8197,12 +8202,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8229,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855330</v>
+        <v>124855466</v>
       </c>
       <c r="B75" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8241,46 +8251,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854676</v>
+        <v>854921</v>
       </c>
       <c r="R75" t="n">
-        <v>7477840</v>
+        <v>7478082</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8313,11 +8315,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8344,7 +8341,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855386</v>
+        <v>124855380</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8377,21 +8374,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854810</v>
+        <v>854745</v>
       </c>
       <c r="R76" t="n">
-        <v>7477930</v>
+        <v>7477946</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8451,10 +8444,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855277</v>
+        <v>124855483</v>
       </c>
       <c r="B77" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8463,25 +8456,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8484,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855068</v>
+        <v>855251</v>
       </c>
       <c r="R77" t="n">
-        <v>7478046</v>
+        <v>7478036</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8553,10 +8546,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855415</v>
+        <v>124855333</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8565,25 +8558,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8593,10 +8586,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854928</v>
+        <v>854924</v>
       </c>
       <c r="R78" t="n">
-        <v>7478107</v>
+        <v>7478087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8655,7 +8648,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855394</v>
+        <v>124855415</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8688,21 +8681,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854897</v>
+        <v>854928</v>
       </c>
       <c r="R79" t="n">
-        <v>7477846</v>
+        <v>7478107</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8743,7 +8732,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8762,10 +8750,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855469</v>
+        <v>124855250</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8774,25 +8762,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8790,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854979</v>
+        <v>854814</v>
       </c>
       <c r="R80" t="n">
-        <v>7477885</v>
+        <v>7477852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8864,10 +8852,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855468</v>
+        <v>124855313</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8876,25 +8864,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8904,10 +8892,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855069</v>
+        <v>854814</v>
       </c>
       <c r="R81" t="n">
-        <v>7477999</v>
+        <v>7477852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8966,10 +8954,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855420</v>
+        <v>124855240</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8978,25 +8966,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9006,10 +8994,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855071</v>
+        <v>854937</v>
       </c>
       <c r="R82" t="n">
-        <v>7477912</v>
+        <v>7477782</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9036,12 +9024,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9068,10 +9056,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855466</v>
+        <v>124855231</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9080,25 +9068,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9108,10 +9096,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854921</v>
+        <v>854954</v>
       </c>
       <c r="R83" t="n">
-        <v>7478082</v>
+        <v>7478125</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9170,10 +9158,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855328</v>
+        <v>124855366</v>
       </c>
       <c r="B84" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9182,38 +9170,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854802</v>
+        <v>854807</v>
       </c>
       <c r="R84" t="n">
-        <v>7477769</v>
+        <v>7477926</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9240,17 +9232,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9259,6 +9246,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9277,10 +9265,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855359</v>
+        <v>124855330</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9289,35 +9277,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854838</v>
+        <v>854676</v>
       </c>
       <c r="R85" t="n">
         <v>7477840</v>
@@ -9357,7 +9353,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9366,7 +9362,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9385,10 +9380,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855366</v>
+        <v>124855257</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9397,42 +9392,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854807</v>
+        <v>854894</v>
       </c>
       <c r="R86" t="n">
-        <v>7477926</v>
+        <v>7477768</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9459,12 +9450,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9473,7 +9469,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9492,10 +9487,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855483</v>
+        <v>124855524</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9504,20 +9499,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855251</v>
+        <v>854793</v>
       </c>
       <c r="R87" t="n">
-        <v>7478036</v>
+        <v>7477805</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9562,12 +9557,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9594,7 +9589,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855376</v>
+        <v>124855420</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9627,21 +9622,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854741</v>
+        <v>855071</v>
       </c>
       <c r="R88" t="n">
-        <v>7477958</v>
+        <v>7477912</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9682,7 +9673,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9701,10 +9691,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855316</v>
+        <v>124855469</v>
       </c>
       <c r="B89" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9713,25 +9703,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9741,10 +9731,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855019</v>
+        <v>854979</v>
       </c>
       <c r="R89" t="n">
-        <v>7477888</v>
+        <v>7477885</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9803,10 +9793,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855318</v>
+        <v>124855364</v>
       </c>
       <c r="B90" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9815,38 +9805,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854817</v>
+        <v>855120</v>
       </c>
       <c r="R90" t="n">
-        <v>7477931</v>
+        <v>7477887</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9881,12 +9871,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9905,7 +9901,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855371</v>
+        <v>124855404</v>
       </c>
       <c r="B91" t="n">
         <v>98101</v>
@@ -9940,7 +9936,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9949,10 +9945,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854845</v>
+        <v>854832</v>
       </c>
       <c r="R91" t="n">
-        <v>7477869</v>
+        <v>7477880</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10012,7 +10008,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855240</v>
+        <v>124855233</v>
       </c>
       <c r="B92" t="n">
         <v>105102</v>
@@ -10052,10 +10048,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854937</v>
+        <v>855073</v>
       </c>
       <c r="R92" t="n">
-        <v>7477782</v>
+        <v>7477920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10082,12 +10078,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10114,10 +10110,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855233</v>
+        <v>124855390</v>
       </c>
       <c r="B93" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10126,38 +10122,42 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855073</v>
+        <v>854899</v>
       </c>
       <c r="R93" t="n">
-        <v>7477920</v>
+        <v>7477831</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10198,6 +10198,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10216,10 +10217,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855313</v>
+        <v>124855318</v>
       </c>
       <c r="B94" t="n">
-        <v>91299</v>
+        <v>96985</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10228,25 +10229,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10256,10 +10257,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854814</v>
+        <v>854817</v>
       </c>
       <c r="R94" t="n">
-        <v>7477852</v>
+        <v>7477931</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10318,10 +10319,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855512</v>
+        <v>124855275</v>
       </c>
       <c r="B95" t="n">
-        <v>79926</v>
+        <v>92321</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10330,38 +10331,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854911</v>
+        <v>854889</v>
       </c>
       <c r="R95" t="n">
-        <v>7478164</v>
+        <v>7477847</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10420,10 +10421,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855474</v>
+        <v>124854790</v>
       </c>
       <c r="B96" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10432,38 +10433,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855065</v>
+        <v>854766</v>
       </c>
       <c r="R96" t="n">
-        <v>7478197</v>
+        <v>7478012</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10504,6 +10509,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10522,10 +10528,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855231</v>
+        <v>124855371</v>
       </c>
       <c r="B97" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10534,38 +10540,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854954</v>
+        <v>854845</v>
       </c>
       <c r="R97" t="n">
-        <v>7478125</v>
+        <v>7477869</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10606,6 +10616,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10624,10 +10635,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855500</v>
+        <v>124855474</v>
       </c>
       <c r="B98" t="n">
-        <v>79826</v>
+        <v>56714</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10636,25 +10647,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10664,10 +10675,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854850</v>
+        <v>855065</v>
       </c>
       <c r="R98" t="n">
-        <v>7477915</v>
+        <v>7478197</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10726,10 +10737,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855482</v>
+        <v>124855386</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10738,38 +10749,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855134</v>
+        <v>854810</v>
       </c>
       <c r="R99" t="n">
-        <v>7477890</v>
+        <v>7477930</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10810,6 +10825,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10828,7 +10844,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124854790</v>
+        <v>124855381</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10861,21 +10877,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854766</v>
+        <v>854803</v>
       </c>
       <c r="R100" t="n">
-        <v>7478012</v>
+        <v>7477930</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10935,10 +10947,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855536</v>
+        <v>124855316</v>
       </c>
       <c r="B101" t="n">
-        <v>57529</v>
+        <v>96985</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10947,25 +10959,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10975,10 +10987,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854869</v>
+        <v>855019</v>
       </c>
       <c r="R101" t="n">
-        <v>7477778</v>
+        <v>7477888</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11005,17 +11017,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11042,10 +11049,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855244</v>
+        <v>124855482</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11058,21 +11065,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11082,10 +11089,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855187</v>
+        <v>855134</v>
       </c>
       <c r="R102" t="n">
-        <v>7478029</v>
+        <v>7477890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11144,10 +11151,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855524</v>
+        <v>124855232</v>
       </c>
       <c r="B103" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11160,21 +11167,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11184,10 +11191,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854793</v>
+        <v>855094</v>
       </c>
       <c r="R103" t="n">
-        <v>7477805</v>
+        <v>7477931</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11214,12 +11221,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11246,7 +11253,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855417</v>
+        <v>124855464</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11286,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855202</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477976</v>
+        <v>7478156</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11348,7 +11355,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855401</v>
+        <v>124855418</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -11381,21 +11388,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854928</v>
+        <v>855131</v>
       </c>
       <c r="R105" t="n">
-        <v>7477769</v>
+        <v>7477924</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11422,12 +11425,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11436,7 +11439,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11455,7 +11457,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855380</v>
+        <v>124855416</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11495,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854745</v>
+        <v>855002</v>
       </c>
       <c r="R106" t="n">
-        <v>7477946</v>
+        <v>7478149</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11539,7 +11541,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11558,10 +11559,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855333</v>
+        <v>124855317</v>
       </c>
       <c r="B107" t="n">
-        <v>79927</v>
+        <v>96985</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11574,21 +11575,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11599,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854924</v>
+        <v>854783</v>
       </c>
       <c r="R107" t="n">
-        <v>7478087</v>
+        <v>7477935</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11660,7 +11661,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855364</v>
+        <v>124855467</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11696,14 +11697,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855120</v>
+        <v>855062</v>
       </c>
       <c r="R108" t="n">
-        <v>7477887</v>
+        <v>7478002</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11738,18 +11739,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11768,7 +11763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855416</v>
+        <v>124855401</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11801,17 +11796,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855002</v>
+        <v>854928</v>
       </c>
       <c r="R109" t="n">
-        <v>7478149</v>
+        <v>7477769</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11838,12 +11837,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11852,6 +11851,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -6784,10 +6784,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855244</v>
+        <v>124855358</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6796,38 +6796,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855187</v>
+        <v>854772</v>
       </c>
       <c r="R61" t="n">
-        <v>7478029</v>
+        <v>7477881</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6862,12 +6862,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6886,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855358</v>
+        <v>124855244</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6898,38 +6904,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854772</v>
+        <v>855187</v>
       </c>
       <c r="R62" t="n">
-        <v>7477881</v>
+        <v>7478029</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6964,18 +6970,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427345</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>854967</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427365</v>
+        <v>124427375</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,25 +4273,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4306,10 +4301,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854939</v>
+        <v>854922</v>
       </c>
       <c r="R37" t="n">
-        <v>7478324</v>
+        <v>7478323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,8 +4345,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4368,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427406</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>91579</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4380,38 +4391,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>855096</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4446,12 +4464,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4470,10 +4494,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427369</v>
+        <v>124427365</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4510,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854943</v>
+        <v>854939</v>
       </c>
       <c r="R39" t="n">
-        <v>7478362</v>
+        <v>7478324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,7 +4596,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427386</v>
+        <v>124427388</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4607,7 +4631,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4616,10 +4640,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855066</v>
+        <v>855074</v>
       </c>
       <c r="R40" t="n">
-        <v>7478180</v>
+        <v>7478164</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427356</v>
+        <v>124427347</v>
       </c>
       <c r="B41" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854977</v>
+        <v>855063</v>
       </c>
       <c r="R41" t="n">
-        <v>7478167</v>
+        <v>7478044</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427399</v>
+        <v>124427391</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,38 +4817,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855007</v>
+        <v>855091</v>
       </c>
       <c r="R42" t="n">
-        <v>7478357</v>
+        <v>7478207</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4865,6 +4893,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4883,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427389</v>
+        <v>124427399</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,42 +4924,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855110</v>
+        <v>855007</v>
       </c>
       <c r="R43" t="n">
-        <v>7478072</v>
+        <v>7478357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,7 +4996,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4990,7 +5014,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427345</v>
+        <v>124427346</v>
       </c>
       <c r="B44" t="n">
         <v>79927</v>
@@ -5030,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854967</v>
+        <v>855044</v>
       </c>
       <c r="R44" t="n">
-        <v>7478177</v>
+        <v>7478074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5092,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427388</v>
+        <v>124427401</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5104,42 +5128,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855074</v>
+        <v>855011</v>
       </c>
       <c r="R45" t="n">
-        <v>7478164</v>
+        <v>7478352</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5180,7 +5200,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5199,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427398</v>
+        <v>124427386</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5211,38 +5230,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855100</v>
+        <v>855066</v>
       </c>
       <c r="R46" t="n">
-        <v>7478058</v>
+        <v>7478180</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5283,6 +5306,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5301,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427352</v>
+        <v>124427356</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5313,42 +5337,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855059</v>
+        <v>854977</v>
       </c>
       <c r="R47" t="n">
-        <v>7478173</v>
+        <v>7478167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,7 +5409,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5408,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427387</v>
+        <v>124427369</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5420,42 +5439,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855102</v>
+        <v>854943</v>
       </c>
       <c r="R48" t="n">
-        <v>7478191</v>
+        <v>7478362</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5496,7 +5511,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5515,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427351</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5527,38 +5541,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>855056</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478165</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5599,6 +5617,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5617,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427346</v>
+        <v>124427389</v>
       </c>
       <c r="B50" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5629,38 +5648,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855044</v>
+        <v>855110</v>
       </c>
       <c r="R50" t="n">
-        <v>7478074</v>
+        <v>7478072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5701,6 +5724,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5719,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427406</v>
+        <v>124427393</v>
       </c>
       <c r="B51" t="n">
-        <v>91579</v>
+        <v>56714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5731,45 +5755,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>760</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855096</v>
+        <v>854990</v>
       </c>
       <c r="R51" t="n">
-        <v>7478199</v>
+        <v>7478363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5804,18 +5821,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5834,7 +5845,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427391</v>
+        <v>124427387</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -5869,7 +5880,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5878,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855091</v>
+        <v>855102</v>
       </c>
       <c r="R52" t="n">
-        <v>7478207</v>
+        <v>7478191</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5941,10 +5952,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427375</v>
+        <v>124427352</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,38 +5964,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854922</v>
+        <v>855059</v>
       </c>
       <c r="R53" t="n">
-        <v>7478323</v>
+        <v>7478173</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6028,21 +6043,6 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6059,10 +6059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427347</v>
+        <v>124427354</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6071,25 +6071,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855063</v>
+        <v>855018</v>
       </c>
       <c r="R54" t="n">
-        <v>7478044</v>
+        <v>7478119</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6161,10 +6161,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427393</v>
+        <v>124427398</v>
       </c>
       <c r="B55" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854990</v>
+        <v>855100</v>
       </c>
       <c r="R55" t="n">
-        <v>7478363</v>
+        <v>7478058</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855475</v>
+        <v>124855469</v>
       </c>
       <c r="B57" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,25 +6378,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854813</v>
+        <v>854979</v>
       </c>
       <c r="R57" t="n">
-        <v>7477923</v>
+        <v>7477885</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855417</v>
+        <v>124855466</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855202</v>
+        <v>854921</v>
       </c>
       <c r="R58" t="n">
-        <v>7477976</v>
+        <v>7478082</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6570,7 +6570,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855376</v>
+        <v>124855404</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854741</v>
+        <v>854832</v>
       </c>
       <c r="R59" t="n">
-        <v>7477958</v>
+        <v>7477880</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855536</v>
+        <v>124855244</v>
       </c>
       <c r="B60" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854869</v>
+        <v>855187</v>
       </c>
       <c r="R60" t="n">
-        <v>7477778</v>
+        <v>7478029</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6747,17 +6747,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6784,7 +6779,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855358</v>
+        <v>124855371</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6817,17 +6812,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854772</v>
+        <v>854845</v>
       </c>
       <c r="R61" t="n">
-        <v>7477881</v>
+        <v>7477869</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,11 +6859,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6892,10 +6886,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855244</v>
+        <v>124855467</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6904,25 +6898,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6932,10 +6926,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855187</v>
+        <v>855062</v>
       </c>
       <c r="R62" t="n">
-        <v>7478029</v>
+        <v>7478002</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6994,10 +6988,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124854791</v>
+        <v>124855500</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7006,38 +7000,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854840</v>
+        <v>854850</v>
       </c>
       <c r="R63" t="n">
-        <v>7477716</v>
+        <v>7477915</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,12 +7058,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7096,10 +7090,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855421</v>
+        <v>124855317</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7108,25 +7102,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,10 +7130,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854951</v>
+        <v>854783</v>
       </c>
       <c r="R64" t="n">
-        <v>7477899</v>
+        <v>7477935</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7198,10 +7192,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855389</v>
+        <v>124855232</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7210,42 +7204,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854906</v>
+        <v>855094</v>
       </c>
       <c r="R65" t="n">
-        <v>7477891</v>
+        <v>7477931</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7286,7 +7276,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7305,10 +7294,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855359</v>
+        <v>124855482</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7317,38 +7306,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854838</v>
+        <v>855134</v>
       </c>
       <c r="R66" t="n">
-        <v>7477840</v>
+        <v>7477890</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7383,18 +7372,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7413,10 +7396,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855277</v>
+        <v>124855474</v>
       </c>
       <c r="B67" t="n">
-        <v>79920</v>
+        <v>56714</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7425,25 +7408,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7436,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855068</v>
+        <v>855065</v>
       </c>
       <c r="R67" t="n">
-        <v>7478046</v>
+        <v>7478197</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855512</v>
+        <v>124855231</v>
       </c>
       <c r="B68" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7531,21 +7514,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7555,10 +7538,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854911</v>
+        <v>854954</v>
       </c>
       <c r="R68" t="n">
-        <v>7478164</v>
+        <v>7478125</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7617,10 +7600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855394</v>
+        <v>124855333</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7629,42 +7612,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854897</v>
+        <v>854924</v>
       </c>
       <c r="R69" t="n">
-        <v>7477846</v>
+        <v>7478087</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7705,7 +7684,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7724,7 +7702,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855423</v>
+        <v>124855420</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7764,10 +7742,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854915</v>
+        <v>855071</v>
       </c>
       <c r="R70" t="n">
-        <v>7477851</v>
+        <v>7477912</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7928,7 +7906,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855468</v>
+        <v>124855366</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7961,17 +7939,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855069</v>
+        <v>854807</v>
       </c>
       <c r="R72" t="n">
-        <v>7477999</v>
+        <v>7477926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8012,6 +7994,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8030,10 +8013,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855500</v>
+        <v>124855394</v>
       </c>
       <c r="B73" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8042,38 +8025,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854850</v>
+        <v>854897</v>
       </c>
       <c r="R73" t="n">
-        <v>7477915</v>
+        <v>7477846</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8114,6 +8101,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8132,10 +8120,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855328</v>
+        <v>124855421</v>
       </c>
       <c r="B74" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8144,38 +8132,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854802</v>
+        <v>854951</v>
       </c>
       <c r="R74" t="n">
-        <v>7477769</v>
+        <v>7477899</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,17 +8190,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8239,7 +8222,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855466</v>
+        <v>124855417</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8279,10 +8262,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854921</v>
+        <v>855202</v>
       </c>
       <c r="R75" t="n">
-        <v>7478082</v>
+        <v>7477976</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8341,10 +8324,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855380</v>
+        <v>124855277</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8353,25 +8336,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8381,10 +8364,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854745</v>
+        <v>855068</v>
       </c>
       <c r="R76" t="n">
-        <v>7477946</v>
+        <v>7478046</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8425,7 +8408,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8444,10 +8426,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855483</v>
+        <v>124855475</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8460,21 +8442,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8484,10 +8466,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855251</v>
+        <v>854813</v>
       </c>
       <c r="R77" t="n">
-        <v>7478036</v>
+        <v>7477923</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8546,10 +8528,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855333</v>
+        <v>124855464</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8558,25 +8540,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8586,10 +8568,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854924</v>
+        <v>854898</v>
       </c>
       <c r="R78" t="n">
-        <v>7478087</v>
+        <v>7478156</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8648,7 +8630,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855415</v>
+        <v>124855423</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8688,10 +8670,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854928</v>
+        <v>854915</v>
       </c>
       <c r="R79" t="n">
-        <v>7478107</v>
+        <v>7477851</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,10 +8732,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855250</v>
+        <v>124855390</v>
       </c>
       <c r="B80" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8762,38 +8744,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854814</v>
+        <v>854899</v>
       </c>
       <c r="R80" t="n">
-        <v>7477852</v>
+        <v>7477831</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8834,6 +8820,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8852,10 +8839,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855313</v>
+        <v>124855275</v>
       </c>
       <c r="B81" t="n">
-        <v>91299</v>
+        <v>92321</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8868,34 +8855,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854814</v>
+        <v>854889</v>
       </c>
       <c r="R81" t="n">
-        <v>7477852</v>
+        <v>7477847</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8954,10 +8941,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855240</v>
+        <v>124855250</v>
       </c>
       <c r="B82" t="n">
-        <v>105102</v>
+        <v>91012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8966,25 +8953,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8994,10 +8981,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854937</v>
+        <v>854814</v>
       </c>
       <c r="R82" t="n">
-        <v>7477782</v>
+        <v>7477852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9024,12 +9011,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9056,7 +9043,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855231</v>
+        <v>124855240</v>
       </c>
       <c r="B83" t="n">
         <v>105102</v>
@@ -9096,10 +9083,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854954</v>
+        <v>854937</v>
       </c>
       <c r="R83" t="n">
-        <v>7478125</v>
+        <v>7477782</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9126,12 +9113,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9158,7 +9145,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855366</v>
+        <v>124855380</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9191,21 +9178,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854807</v>
+        <v>854745</v>
       </c>
       <c r="R84" t="n">
-        <v>7477926</v>
+        <v>7477946</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,10 +9248,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855330</v>
+        <v>124855524</v>
       </c>
       <c r="B85" t="n">
-        <v>56725</v>
+        <v>79926</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9281,42 +9264,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102613</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854676</v>
+        <v>854793</v>
       </c>
       <c r="R85" t="n">
-        <v>7477840</v>
+        <v>7477805</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9343,17 +9318,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9380,10 +9350,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855257</v>
+        <v>124855389</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9392,38 +9362,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854894</v>
+        <v>854906</v>
       </c>
       <c r="R86" t="n">
-        <v>7477768</v>
+        <v>7477891</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,17 +9424,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9469,6 +9438,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9487,10 +9457,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855524</v>
+        <v>124855386</v>
       </c>
       <c r="B87" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9499,38 +9469,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854793</v>
+        <v>854810</v>
       </c>
       <c r="R87" t="n">
-        <v>7477805</v>
+        <v>7477930</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9557,12 +9531,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9571,6 +9545,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9589,10 +9564,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855420</v>
+        <v>124855536</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9601,25 +9576,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9629,10 +9604,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855071</v>
+        <v>854869</v>
       </c>
       <c r="R88" t="n">
-        <v>7477912</v>
+        <v>7477778</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9659,12 +9634,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9691,7 +9671,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855469</v>
+        <v>124854790</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9724,17 +9704,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854979</v>
+        <v>854766</v>
       </c>
       <c r="R89" t="n">
-        <v>7477885</v>
+        <v>7478012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9775,6 +9759,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9793,10 +9778,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855364</v>
+        <v>124855330</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9805,38 +9790,46 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855120</v>
+        <v>854676</v>
       </c>
       <c r="R90" t="n">
-        <v>7477887</v>
+        <v>7477840</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9873,7 +9866,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9882,7 +9875,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9901,7 +9893,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855404</v>
+        <v>124855381</v>
       </c>
       <c r="B91" t="n">
         <v>98101</v>
@@ -9934,21 +9926,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854832</v>
+        <v>854803</v>
       </c>
       <c r="R91" t="n">
-        <v>7477880</v>
+        <v>7477930</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10008,10 +9996,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855233</v>
+        <v>124855415</v>
       </c>
       <c r="B92" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10020,25 +10008,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10048,10 +10036,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855073</v>
+        <v>854928</v>
       </c>
       <c r="R92" t="n">
-        <v>7477920</v>
+        <v>7478107</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10110,7 +10098,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855390</v>
+        <v>124855401</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10145,7 +10133,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10154,10 +10142,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854899</v>
+        <v>854928</v>
       </c>
       <c r="R93" t="n">
-        <v>7477831</v>
+        <v>7477769</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10184,12 +10172,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10217,10 +10205,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855318</v>
+        <v>124855358</v>
       </c>
       <c r="B94" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10229,38 +10217,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854817</v>
+        <v>854772</v>
       </c>
       <c r="R94" t="n">
-        <v>7477931</v>
+        <v>7477881</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10295,12 +10283,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10319,10 +10313,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855275</v>
+        <v>124855512</v>
       </c>
       <c r="B95" t="n">
-        <v>92321</v>
+        <v>79926</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10331,38 +10325,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854889</v>
+        <v>854911</v>
       </c>
       <c r="R95" t="n">
-        <v>7477847</v>
+        <v>7478164</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10421,10 +10415,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124854790</v>
+        <v>124855257</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10433,42 +10427,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854766</v>
+        <v>854894</v>
       </c>
       <c r="R96" t="n">
-        <v>7478012</v>
+        <v>7477768</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10495,12 +10485,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10509,7 +10504,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10528,10 +10522,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855371</v>
+        <v>124854791</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10540,42 +10534,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854845</v>
+        <v>854840</v>
       </c>
       <c r="R97" t="n">
-        <v>7477869</v>
+        <v>7477716</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10602,12 +10592,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10616,7 +10606,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10635,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855474</v>
+        <v>124855416</v>
       </c>
       <c r="B98" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10647,25 +10636,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10675,10 +10664,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855065</v>
+        <v>855002</v>
       </c>
       <c r="R98" t="n">
-        <v>7478197</v>
+        <v>7478149</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10737,7 +10726,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855386</v>
+        <v>124855468</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -10770,21 +10759,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854810</v>
+        <v>855069</v>
       </c>
       <c r="R99" t="n">
-        <v>7477930</v>
+        <v>7477999</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10825,7 +10810,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10844,7 +10828,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855381</v>
+        <v>124855359</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10880,14 +10864,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854803</v>
+        <v>854838</v>
       </c>
       <c r="R100" t="n">
-        <v>7477930</v>
+        <v>7477840</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10920,6 +10904,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10947,10 +10936,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855316</v>
+        <v>124855376</v>
       </c>
       <c r="B101" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10959,38 +10948,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855019</v>
+        <v>854741</v>
       </c>
       <c r="R101" t="n">
-        <v>7477888</v>
+        <v>7477958</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11031,6 +11024,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11049,10 +11043,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855482</v>
+        <v>124855318</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11061,25 +11055,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11089,10 +11083,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855134</v>
+        <v>854817</v>
       </c>
       <c r="R102" t="n">
-        <v>7477890</v>
+        <v>7477931</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11151,10 +11145,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855232</v>
+        <v>124855483</v>
       </c>
       <c r="B103" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11163,25 +11157,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11191,10 +11185,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855094</v>
+        <v>855251</v>
       </c>
       <c r="R103" t="n">
-        <v>7477931</v>
+        <v>7478036</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11253,10 +11247,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855464</v>
+        <v>124855233</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11265,25 +11259,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11293,10 +11287,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854898</v>
+        <v>855073</v>
       </c>
       <c r="R104" t="n">
-        <v>7478156</v>
+        <v>7477920</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11355,10 +11349,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855418</v>
+        <v>124855328</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,38 +11361,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855131</v>
+        <v>854802</v>
       </c>
       <c r="R105" t="n">
-        <v>7477924</v>
+        <v>7477769</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11425,12 +11419,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11457,10 +11456,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855416</v>
+        <v>124855316</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11469,25 +11468,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11496,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855002</v>
+        <v>855019</v>
       </c>
       <c r="R106" t="n">
-        <v>7478149</v>
+        <v>7477888</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11559,10 +11558,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855317</v>
+        <v>124855364</v>
       </c>
       <c r="B107" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11571,38 +11570,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854783</v>
+        <v>855120</v>
       </c>
       <c r="R107" t="n">
-        <v>7477935</v>
+        <v>7477887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11637,12 +11636,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11661,7 +11666,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855467</v>
+        <v>124855418</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11701,10 +11706,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855062</v>
+        <v>855131</v>
       </c>
       <c r="R108" t="n">
-        <v>7478002</v>
+        <v>7477924</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11768,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855401</v>
+        <v>124855313</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11775,42 +11780,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854928</v>
+        <v>854814</v>
       </c>
       <c r="R109" t="n">
-        <v>7477769</v>
+        <v>7477852</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11837,12 +11838,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11851,7 +11852,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427345</v>
+        <v>124427406</v>
       </c>
       <c r="B36" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854967</v>
+        <v>855096</v>
       </c>
       <c r="R36" t="n">
-        <v>7478177</v>
+        <v>7478199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4237,12 +4244,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4379,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427406</v>
+        <v>124427393</v>
       </c>
       <c r="B38" t="n">
-        <v>91579</v>
+        <v>56714</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,45 +4404,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855096</v>
+        <v>854990</v>
       </c>
       <c r="R38" t="n">
-        <v>7478199</v>
+        <v>7478363</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,18 +4470,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427365</v>
+        <v>124427351</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4506,38 +4506,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854939</v>
+        <v>855056</v>
       </c>
       <c r="R39" t="n">
-        <v>7478324</v>
+        <v>7478165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4578,6 +4582,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4596,10 +4601,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427388</v>
+        <v>124427399</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4608,42 +4613,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855074</v>
+        <v>855007</v>
       </c>
       <c r="R40" t="n">
-        <v>7478164</v>
+        <v>7478357</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,7 +4685,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427391</v>
+        <v>124427398</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,42 +4817,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855091</v>
+        <v>855100</v>
       </c>
       <c r="R42" t="n">
-        <v>7478207</v>
+        <v>7478058</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,7 +4889,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4912,10 +4907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427399</v>
+        <v>124427356</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,20 +4919,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4948,14 +4943,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855007</v>
+        <v>854977</v>
       </c>
       <c r="R43" t="n">
-        <v>7478357</v>
+        <v>7478167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427346</v>
+        <v>124427369</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,38 +5021,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855044</v>
+        <v>854943</v>
       </c>
       <c r="R44" t="n">
-        <v>7478074</v>
+        <v>7478362</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B45" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,38 +5123,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R45" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,6 +5199,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427386</v>
+        <v>124427391</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855066</v>
+        <v>855091</v>
       </c>
       <c r="R46" t="n">
-        <v>7478180</v>
+        <v>7478207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427356</v>
+        <v>124427345</v>
       </c>
       <c r="B47" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,21 +5341,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854977</v>
+        <v>854967</v>
       </c>
       <c r="R47" t="n">
-        <v>7478167</v>
+        <v>7478177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427369</v>
+        <v>124427365</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854943</v>
+        <v>854939</v>
       </c>
       <c r="R48" t="n">
-        <v>7478362</v>
+        <v>7478324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427351</v>
+        <v>124427388</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5564,19 +5564,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855056</v>
+        <v>855074</v>
       </c>
       <c r="R49" t="n">
-        <v>7478165</v>
+        <v>7478164</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427389</v>
+        <v>124427401</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,42 +5648,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855110</v>
+        <v>855011</v>
       </c>
       <c r="R50" t="n">
-        <v>7478072</v>
+        <v>7478352</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5724,7 +5720,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5743,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B51" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5759,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R51" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5845,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427387</v>
+        <v>124427389</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -5880,7 +5875,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5889,10 +5884,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855102</v>
+        <v>855110</v>
       </c>
       <c r="R52" t="n">
-        <v>7478191</v>
+        <v>7478072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5952,10 +5947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5964,42 +5959,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R53" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6040,7 +6031,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6059,10 +6049,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427354</v>
+        <v>124427403</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6071,38 +6061,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855018</v>
+        <v>854946</v>
       </c>
       <c r="R54" t="n">
-        <v>7478119</v>
+        <v>7478367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,6 +6133,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6161,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427398</v>
+        <v>124427387</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6173,38 +6164,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855100</v>
+        <v>855102</v>
       </c>
       <c r="R55" t="n">
-        <v>7478058</v>
+        <v>7478191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6245,6 +6240,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6263,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427403</v>
+        <v>124427386</v>
       </c>
       <c r="B56" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6275,38 +6271,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854946</v>
+        <v>855066</v>
       </c>
       <c r="R56" t="n">
-        <v>7478367</v>
+        <v>7478180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855469</v>
+        <v>124854790</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6399,17 +6399,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854979</v>
+        <v>854766</v>
       </c>
       <c r="R57" t="n">
-        <v>7477885</v>
+        <v>7478012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,6 +6454,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6468,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855466</v>
+        <v>124855330</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6485,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854921</v>
+        <v>854676</v>
       </c>
       <c r="R58" t="n">
-        <v>7478082</v>
+        <v>7477840</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,6 +6557,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6570,7 +6588,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855404</v>
+        <v>124855401</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6605,7 +6623,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6614,10 +6632,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854832</v>
+        <v>854928</v>
       </c>
       <c r="R59" t="n">
-        <v>7477880</v>
+        <v>7477769</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,12 +6662,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6677,10 +6695,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855244</v>
+        <v>124855232</v>
       </c>
       <c r="B60" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,25 +6707,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6735,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855187</v>
+        <v>855094</v>
       </c>
       <c r="R60" t="n">
-        <v>7478029</v>
+        <v>7477931</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,7 +6797,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855371</v>
+        <v>124855418</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6812,21 +6830,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854845</v>
+        <v>855131</v>
       </c>
       <c r="R61" t="n">
-        <v>7477869</v>
+        <v>7477924</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6867,7 +6881,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6886,7 +6899,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855467</v>
+        <v>124855420</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -6926,10 +6939,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855062</v>
+        <v>855071</v>
       </c>
       <c r="R62" t="n">
-        <v>7478002</v>
+        <v>7477912</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6988,10 +7001,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855500</v>
+        <v>124855417</v>
       </c>
       <c r="B63" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7000,25 +7013,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7028,10 +7041,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854850</v>
+        <v>855202</v>
       </c>
       <c r="R63" t="n">
-        <v>7477915</v>
+        <v>7477976</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7090,10 +7103,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855317</v>
+        <v>124855389</v>
       </c>
       <c r="B64" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,38 +7115,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854783</v>
+        <v>854906</v>
       </c>
       <c r="R64" t="n">
-        <v>7477935</v>
+        <v>7477891</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7174,6 +7191,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7192,10 +7210,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855232</v>
+        <v>124855313</v>
       </c>
       <c r="B65" t="n">
-        <v>105102</v>
+        <v>91299</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7204,25 +7222,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7232,10 +7250,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855094</v>
+        <v>854814</v>
       </c>
       <c r="R65" t="n">
-        <v>7477931</v>
+        <v>7477852</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7294,10 +7312,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855482</v>
+        <v>124855231</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7306,25 +7324,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7334,10 +7352,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855134</v>
+        <v>854954</v>
       </c>
       <c r="R66" t="n">
-        <v>7477890</v>
+        <v>7478125</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7396,10 +7414,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855474</v>
+        <v>124855380</v>
       </c>
       <c r="B67" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7408,25 +7426,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7436,10 +7454,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855065</v>
+        <v>854745</v>
       </c>
       <c r="R67" t="n">
-        <v>7478197</v>
+        <v>7477946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7480,6 +7498,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7498,10 +7517,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855231</v>
+        <v>124855275</v>
       </c>
       <c r="B68" t="n">
-        <v>105102</v>
+        <v>92321</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7510,38 +7529,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854954</v>
+        <v>854889</v>
       </c>
       <c r="R68" t="n">
-        <v>7478125</v>
+        <v>7477847</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7600,10 +7619,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855333</v>
+        <v>124855316</v>
       </c>
       <c r="B69" t="n">
-        <v>79927</v>
+        <v>96985</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7616,21 +7635,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7640,10 +7659,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854924</v>
+        <v>855019</v>
       </c>
       <c r="R69" t="n">
-        <v>7478087</v>
+        <v>7477888</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7702,10 +7721,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855420</v>
+        <v>124855500</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7714,25 +7733,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7742,10 +7761,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855071</v>
+        <v>854850</v>
       </c>
       <c r="R70" t="n">
-        <v>7477912</v>
+        <v>7477915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7804,10 +7823,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855424</v>
+        <v>124855257</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7816,25 +7835,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7863,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854780</v>
+        <v>854894</v>
       </c>
       <c r="R71" t="n">
-        <v>7477939</v>
+        <v>7477768</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7874,12 +7893,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7906,10 +7930,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855366</v>
+        <v>124855524</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7918,42 +7942,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854807</v>
+        <v>854793</v>
       </c>
       <c r="R72" t="n">
-        <v>7477926</v>
+        <v>7477805</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7980,12 +8000,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7994,7 +8014,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8013,10 +8032,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855394</v>
+        <v>124855318</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8025,42 +8044,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854897</v>
+        <v>854817</v>
       </c>
       <c r="R73" t="n">
-        <v>7477846</v>
+        <v>7477931</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,7 +8116,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8120,10 +8134,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855421</v>
+        <v>124855482</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8132,25 +8146,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8160,10 +8174,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854951</v>
+        <v>855134</v>
       </c>
       <c r="R74" t="n">
-        <v>7477899</v>
+        <v>7477890</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8222,7 +8236,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855417</v>
+        <v>124855371</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8255,17 +8269,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855202</v>
+        <v>854845</v>
       </c>
       <c r="R75" t="n">
-        <v>7477976</v>
+        <v>7477869</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8306,6 +8324,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8324,10 +8343,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855277</v>
+        <v>124855466</v>
       </c>
       <c r="B76" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8336,25 +8355,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8364,10 +8383,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855068</v>
+        <v>854921</v>
       </c>
       <c r="R76" t="n">
-        <v>7478046</v>
+        <v>7478082</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8426,10 +8445,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855475</v>
+        <v>124855421</v>
       </c>
       <c r="B77" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8438,25 +8457,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8466,10 +8485,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854813</v>
+        <v>854951</v>
       </c>
       <c r="R77" t="n">
-        <v>7477923</v>
+        <v>7477899</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8528,7 +8547,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855464</v>
+        <v>124855381</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8568,10 +8587,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854898</v>
+        <v>854803</v>
       </c>
       <c r="R78" t="n">
-        <v>7478156</v>
+        <v>7477930</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8612,6 +8631,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8630,10 +8650,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855423</v>
+        <v>124855240</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8642,25 +8662,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8670,10 +8690,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854915</v>
+        <v>854937</v>
       </c>
       <c r="R79" t="n">
-        <v>7477851</v>
+        <v>7477782</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8700,12 +8720,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8732,10 +8752,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855390</v>
+        <v>124855277</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8744,42 +8764,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854899</v>
+        <v>855068</v>
       </c>
       <c r="R80" t="n">
-        <v>7477831</v>
+        <v>7478046</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8820,7 +8836,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8839,10 +8854,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855275</v>
+        <v>124855328</v>
       </c>
       <c r="B81" t="n">
-        <v>92321</v>
+        <v>56725</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8851,25 +8866,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>102613</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8879,10 +8894,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854889</v>
+        <v>854802</v>
       </c>
       <c r="R81" t="n">
-        <v>7477847</v>
+        <v>7477769</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8909,12 +8924,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8941,10 +8961,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855250</v>
+        <v>124855475</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8957,21 +8977,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8981,10 +9001,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854814</v>
+        <v>854813</v>
       </c>
       <c r="R82" t="n">
-        <v>7477852</v>
+        <v>7477923</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9043,10 +9063,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855240</v>
+        <v>124855366</v>
       </c>
       <c r="B83" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9055,38 +9075,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854937</v>
+        <v>854807</v>
       </c>
       <c r="R83" t="n">
-        <v>7477782</v>
+        <v>7477926</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9113,12 +9137,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9127,6 +9151,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9145,10 +9170,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855380</v>
+        <v>124855483</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9157,25 +9182,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9185,10 +9210,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854745</v>
+        <v>855251</v>
       </c>
       <c r="R84" t="n">
-        <v>7477946</v>
+        <v>7478036</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9229,7 +9254,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9248,10 +9272,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855524</v>
+        <v>124855536</v>
       </c>
       <c r="B85" t="n">
-        <v>79926</v>
+        <v>57529</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9260,25 +9284,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9288,10 +9312,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854793</v>
+        <v>854869</v>
       </c>
       <c r="R85" t="n">
-        <v>7477805</v>
+        <v>7477778</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9324,6 +9348,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9350,7 +9379,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855389</v>
+        <v>124855390</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9385,7 +9414,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9394,10 +9423,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854906</v>
+        <v>854899</v>
       </c>
       <c r="R86" t="n">
-        <v>7477891</v>
+        <v>7477831</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9457,7 +9486,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855386</v>
+        <v>124855394</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9492,7 +9521,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9501,10 +9530,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854810</v>
+        <v>854897</v>
       </c>
       <c r="R87" t="n">
-        <v>7477930</v>
+        <v>7477846</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9564,10 +9593,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855536</v>
+        <v>124855244</v>
       </c>
       <c r="B88" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9580,21 +9609,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9604,10 +9633,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854869</v>
+        <v>855187</v>
       </c>
       <c r="R88" t="n">
-        <v>7477778</v>
+        <v>7478029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9634,17 +9663,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9671,10 +9695,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124854790</v>
+        <v>124855233</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9683,42 +9707,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854766</v>
+        <v>855073</v>
       </c>
       <c r="R89" t="n">
-        <v>7478012</v>
+        <v>7477920</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9759,7 +9779,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9778,10 +9797,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855330</v>
+        <v>124855250</v>
       </c>
       <c r="B90" t="n">
-        <v>56725</v>
+        <v>91012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9790,46 +9809,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854676</v>
+        <v>854814</v>
       </c>
       <c r="R90" t="n">
-        <v>7477840</v>
+        <v>7477852</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9862,11 +9873,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9893,10 +9899,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855381</v>
+        <v>124855333</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9905,25 +9911,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9933,10 +9939,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854803</v>
+        <v>854924</v>
       </c>
       <c r="R91" t="n">
-        <v>7477930</v>
+        <v>7478087</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9977,7 +9983,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9996,10 +10001,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855415</v>
+        <v>124855474</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10008,25 +10013,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10036,10 +10041,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854928</v>
+        <v>855065</v>
       </c>
       <c r="R92" t="n">
-        <v>7478107</v>
+        <v>7478197</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10098,7 +10103,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855401</v>
+        <v>124855423</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10131,21 +10136,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854928</v>
+        <v>854915</v>
       </c>
       <c r="R93" t="n">
-        <v>7477769</v>
+        <v>7477851</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10172,12 +10173,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10186,7 +10187,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855358</v>
+        <v>124855404</v>
       </c>
       <c r="B94" t="n">
         <v>98101</v>
@@ -10238,17 +10238,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854772</v>
+        <v>854832</v>
       </c>
       <c r="R94" t="n">
-        <v>7477881</v>
+        <v>7477880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10281,11 +10285,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10313,10 +10312,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855512</v>
+        <v>124855468</v>
       </c>
       <c r="B95" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10325,25 +10324,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10353,10 +10352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854911</v>
+        <v>855069</v>
       </c>
       <c r="R95" t="n">
-        <v>7478164</v>
+        <v>7477999</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10415,10 +10414,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855257</v>
+        <v>124855358</v>
       </c>
       <c r="B96" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10427,38 +10426,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854894</v>
+        <v>854772</v>
       </c>
       <c r="R96" t="n">
-        <v>7477768</v>
+        <v>7477881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10485,17 +10484,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10504,6 +10503,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10624,7 +10624,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855416</v>
+        <v>124855424</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10664,10 +10664,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855002</v>
+        <v>854780</v>
       </c>
       <c r="R98" t="n">
-        <v>7478149</v>
+        <v>7477939</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10726,10 +10726,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855468</v>
+        <v>124855317</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10738,25 +10738,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10766,10 +10766,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855069</v>
+        <v>854783</v>
       </c>
       <c r="R99" t="n">
-        <v>7477999</v>
+        <v>7477935</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855359</v>
+        <v>124855376</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10861,17 +10861,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854838</v>
+        <v>854741</v>
       </c>
       <c r="R100" t="n">
-        <v>7477840</v>
+        <v>7477958</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10904,11 +10908,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10936,7 +10935,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855376</v>
+        <v>124855416</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10969,21 +10968,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854741</v>
+        <v>855002</v>
       </c>
       <c r="R101" t="n">
-        <v>7477958</v>
+        <v>7478149</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11024,7 +11019,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11043,10 +11037,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855318</v>
+        <v>124855415</v>
       </c>
       <c r="B102" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11055,25 +11049,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11083,10 +11077,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854817</v>
+        <v>854928</v>
       </c>
       <c r="R102" t="n">
-        <v>7477931</v>
+        <v>7478107</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11145,10 +11139,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855483</v>
+        <v>124855467</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11157,25 +11151,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11185,10 +11179,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855251</v>
+        <v>855062</v>
       </c>
       <c r="R103" t="n">
-        <v>7478036</v>
+        <v>7478002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11247,10 +11241,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855233</v>
+        <v>124855464</v>
       </c>
       <c r="B104" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11259,25 +11253,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11287,10 +11281,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855073</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477920</v>
+        <v>7478156</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11349,10 +11343,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855328</v>
+        <v>124855469</v>
       </c>
       <c r="B105" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11361,38 +11355,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854802</v>
+        <v>854979</v>
       </c>
       <c r="R105" t="n">
-        <v>7477769</v>
+        <v>7477885</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11419,17 +11413,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11456,10 +11445,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855316</v>
+        <v>124855386</v>
       </c>
       <c r="B106" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11468,38 +11457,42 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855019</v>
+        <v>854810</v>
       </c>
       <c r="R106" t="n">
-        <v>7477888</v>
+        <v>7477930</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11540,6 +11533,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11558,10 +11552,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855364</v>
+        <v>124855512</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11570,38 +11564,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>855120</v>
+        <v>854911</v>
       </c>
       <c r="R107" t="n">
-        <v>7477887</v>
+        <v>7478164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11636,18 +11630,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11666,7 +11654,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855418</v>
+        <v>124855364</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11702,14 +11690,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855131</v>
+        <v>855120</v>
       </c>
       <c r="R108" t="n">
-        <v>7477924</v>
+        <v>7477887</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11744,12 +11732,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11768,10 +11762,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855313</v>
+        <v>124855359</v>
       </c>
       <c r="B109" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11780,38 +11774,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854814</v>
+        <v>854838</v>
       </c>
       <c r="R109" t="n">
-        <v>7477852</v>
+        <v>7477840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11846,12 +11840,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5009,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427369</v>
+        <v>124427352</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,38 +5021,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854943</v>
+        <v>855059</v>
       </c>
       <c r="R44" t="n">
-        <v>7478362</v>
+        <v>7478173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,6 +5097,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5111,7 +5116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427352</v>
+        <v>124427391</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5146,19 +5151,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855059</v>
+        <v>855091</v>
       </c>
       <c r="R45" t="n">
-        <v>7478173</v>
+        <v>7478207</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427391</v>
+        <v>124427369</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,42 +5235,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855091</v>
+        <v>854943</v>
       </c>
       <c r="R46" t="n">
-        <v>7478207</v>
+        <v>7478362</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,7 +5307,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5840,10 +5840,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427389</v>
+        <v>124427346</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,42 +5852,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855110</v>
+        <v>855044</v>
       </c>
       <c r="R52" t="n">
-        <v>7478072</v>
+        <v>7478074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5928,7 +5924,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5947,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427346</v>
+        <v>124427403</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>79826</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5963,34 +5958,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855044</v>
+        <v>854946</v>
       </c>
       <c r="R53" t="n">
-        <v>7478074</v>
+        <v>7478367</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6031,6 +6026,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6049,10 +6045,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427403</v>
+        <v>124427389</v>
       </c>
       <c r="B54" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6061,38 +6057,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854946</v>
+        <v>855110</v>
       </c>
       <c r="R54" t="n">
-        <v>7478367</v>
+        <v>7478072</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855275</v>
+        <v>124855500</v>
       </c>
       <c r="B68" t="n">
-        <v>92321</v>
+        <v>79826</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7529,38 +7529,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>6457</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854889</v>
+        <v>854850</v>
       </c>
       <c r="R68" t="n">
-        <v>7477847</v>
+        <v>7477915</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855500</v>
+        <v>124855275</v>
       </c>
       <c r="B70" t="n">
-        <v>79826</v>
+        <v>92321</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7733,38 +7733,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6457</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854850</v>
+        <v>854889</v>
       </c>
       <c r="R70" t="n">
-        <v>7477915</v>
+        <v>7477847</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855524</v>
+        <v>124855482</v>
       </c>
       <c r="B72" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7942,20 +7942,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854793</v>
+        <v>855134</v>
       </c>
       <c r="R72" t="n">
-        <v>7477805</v>
+        <v>7477890</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8000,12 +8000,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8134,10 +8134,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855482</v>
+        <v>124855524</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8146,20 +8146,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855134</v>
+        <v>854793</v>
       </c>
       <c r="R74" t="n">
-        <v>7477890</v>
+        <v>7477805</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8236,7 +8236,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855371</v>
+        <v>124855466</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8269,21 +8269,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854845</v>
+        <v>854921</v>
       </c>
       <c r="R75" t="n">
-        <v>7477869</v>
+        <v>7478082</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8324,7 +8320,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8343,7 +8338,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855466</v>
+        <v>124855371</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8376,17 +8371,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854921</v>
+        <v>854845</v>
       </c>
       <c r="R76" t="n">
-        <v>7478082</v>
+        <v>7477869</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8427,6 +8426,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8752,10 +8752,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855277</v>
+        <v>124855328</v>
       </c>
       <c r="B80" t="n">
-        <v>79920</v>
+        <v>56725</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8768,34 +8768,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855068</v>
+        <v>854802</v>
       </c>
       <c r="R80" t="n">
-        <v>7478046</v>
+        <v>7477769</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8822,12 +8822,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8854,10 +8859,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855328</v>
+        <v>124855277</v>
       </c>
       <c r="B81" t="n">
-        <v>56725</v>
+        <v>79920</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8870,34 +8875,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854802</v>
+        <v>855068</v>
       </c>
       <c r="R81" t="n">
-        <v>7477769</v>
+        <v>7478046</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,17 +8929,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10205,10 +10205,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855404</v>
+        <v>124854791</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10217,42 +10217,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854832</v>
+        <v>854840</v>
       </c>
       <c r="R94" t="n">
-        <v>7477880</v>
+        <v>7477716</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10279,12 +10275,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10293,7 +10289,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10312,7 +10307,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855468</v>
+        <v>124855404</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10345,17 +10340,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855069</v>
+        <v>854832</v>
       </c>
       <c r="R95" t="n">
-        <v>7477999</v>
+        <v>7477880</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10396,6 +10395,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855358</v>
+        <v>124855468</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10450,14 +10450,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854772</v>
+        <v>855069</v>
       </c>
       <c r="R96" t="n">
-        <v>7477881</v>
+        <v>7477999</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10492,18 +10492,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10522,10 +10516,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124854791</v>
+        <v>124855358</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10534,25 +10528,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10562,10 +10556,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854840</v>
+        <v>854772</v>
       </c>
       <c r="R97" t="n">
-        <v>7477716</v>
+        <v>7477881</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10592,12 +10586,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10606,6 +10605,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5840,10 +5840,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427346</v>
+        <v>124427389</v>
       </c>
       <c r="B52" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,38 +5852,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855044</v>
+        <v>855110</v>
       </c>
       <c r="R52" t="n">
-        <v>7478074</v>
+        <v>7478072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5924,6 +5928,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5942,10 +5947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427403</v>
+        <v>124427346</v>
       </c>
       <c r="B53" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5958,34 +5963,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854946</v>
+        <v>855044</v>
       </c>
       <c r="R53" t="n">
-        <v>7478367</v>
+        <v>7478074</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6026,7 +6031,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6049,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427389</v>
+        <v>124427403</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6057,42 +6061,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855110</v>
+        <v>854946</v>
       </c>
       <c r="R54" t="n">
-        <v>7478072</v>
+        <v>7478367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855500</v>
+        <v>124855275</v>
       </c>
       <c r="B68" t="n">
-        <v>79826</v>
+        <v>92321</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7529,38 +7529,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6457</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854850</v>
+        <v>854889</v>
       </c>
       <c r="R68" t="n">
-        <v>7477915</v>
+        <v>7477847</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855275</v>
+        <v>124855500</v>
       </c>
       <c r="B70" t="n">
-        <v>92321</v>
+        <v>79826</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7733,38 +7733,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>6457</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854889</v>
+        <v>854850</v>
       </c>
       <c r="R70" t="n">
-        <v>7477847</v>
+        <v>7477915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8752,10 +8752,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855328</v>
+        <v>124855277</v>
       </c>
       <c r="B80" t="n">
-        <v>56725</v>
+        <v>79920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8768,34 +8768,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854802</v>
+        <v>855068</v>
       </c>
       <c r="R80" t="n">
-        <v>7477769</v>
+        <v>7478046</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8822,17 +8822,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8859,10 +8854,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855277</v>
+        <v>124855328</v>
       </c>
       <c r="B81" t="n">
-        <v>79920</v>
+        <v>56725</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8875,34 +8870,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855068</v>
+        <v>854802</v>
       </c>
       <c r="R81" t="n">
-        <v>7478046</v>
+        <v>7477769</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8929,12 +8924,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9170,10 +9170,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855483</v>
+        <v>124855244</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9186,21 +9186,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855251</v>
+        <v>855187</v>
       </c>
       <c r="R84" t="n">
-        <v>7478036</v>
+        <v>7478029</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9379,10 +9379,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855390</v>
+        <v>124855483</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9391,42 +9391,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854899</v>
+        <v>855251</v>
       </c>
       <c r="R86" t="n">
-        <v>7477831</v>
+        <v>7478036</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9467,7 +9463,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9593,10 +9588,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855244</v>
+        <v>124855233</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9605,25 +9600,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9633,10 +9628,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855187</v>
+        <v>855073</v>
       </c>
       <c r="R88" t="n">
-        <v>7478029</v>
+        <v>7477920</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9695,10 +9690,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855233</v>
+        <v>124855390</v>
       </c>
       <c r="B89" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9707,38 +9702,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855073</v>
+        <v>854899</v>
       </c>
       <c r="R89" t="n">
-        <v>7477920</v>
+        <v>7477831</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9779,6 +9778,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10205,10 +10205,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124854791</v>
+        <v>124855404</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10217,38 +10217,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854840</v>
+        <v>854832</v>
       </c>
       <c r="R94" t="n">
-        <v>7477716</v>
+        <v>7477880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10275,12 +10279,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10289,6 +10293,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10307,7 +10312,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855404</v>
+        <v>124855468</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10340,21 +10345,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854832</v>
+        <v>855069</v>
       </c>
       <c r="R95" t="n">
-        <v>7477880</v>
+        <v>7477999</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10395,7 +10396,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855468</v>
+        <v>124855358</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10450,14 +10450,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855069</v>
+        <v>854772</v>
       </c>
       <c r="R96" t="n">
-        <v>7477999</v>
+        <v>7477881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10492,12 +10492,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10516,10 +10522,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855358</v>
+        <v>124854791</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10528,25 +10534,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10556,10 +10562,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854772</v>
+        <v>854840</v>
       </c>
       <c r="R97" t="n">
-        <v>7477881</v>
+        <v>7477716</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10586,17 +10592,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10605,7 +10606,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11654,7 +11654,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855364</v>
+        <v>124855359</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855120</v>
+        <v>854838</v>
       </c>
       <c r="R108" t="n">
-        <v>7477887</v>
+        <v>7477840</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855359</v>
+        <v>124855364</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854838</v>
+        <v>855120</v>
       </c>
       <c r="R109" t="n">
-        <v>7477840</v>
+        <v>7477887</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427406</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,45 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855096</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478199</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,18 +4237,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427375</v>
+        <v>124427387</v>
       </c>
       <c r="B37" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,38 +4273,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854922</v>
+        <v>855102</v>
       </c>
       <c r="R37" t="n">
-        <v>7478323</v>
+        <v>7478191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,21 +4352,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4392,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427393</v>
+        <v>124427389</v>
       </c>
       <c r="B38" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4404,38 +4380,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854990</v>
+        <v>855110</v>
       </c>
       <c r="R38" t="n">
-        <v>7478363</v>
+        <v>7478072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,6 +4456,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427351</v>
+        <v>124427365</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4506,42 +4487,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855056</v>
+        <v>854939</v>
       </c>
       <c r="R39" t="n">
-        <v>7478165</v>
+        <v>7478324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4582,7 +4559,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4601,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427399</v>
+        <v>124427393</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4617,21 +4593,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4641,10 +4617,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855007</v>
+        <v>854990</v>
       </c>
       <c r="R40" t="n">
-        <v>7478357</v>
+        <v>7478363</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427347</v>
+        <v>124427352</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4715,38 +4691,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855063</v>
+        <v>855059</v>
       </c>
       <c r="R41" t="n">
-        <v>7478044</v>
+        <v>7478173</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4787,6 +4767,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4805,10 +4786,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427398</v>
+        <v>124427369</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,21 +4802,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4845,10 +4826,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855100</v>
+        <v>854943</v>
       </c>
       <c r="R42" t="n">
-        <v>7478058</v>
+        <v>7478362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4907,10 +4888,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427356</v>
+        <v>124427386</v>
       </c>
       <c r="B43" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4919,38 +4900,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854977</v>
+        <v>855066</v>
       </c>
       <c r="R43" t="n">
-        <v>7478167</v>
+        <v>7478180</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,6 +4976,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5009,10 +4995,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427352</v>
+        <v>124427403</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,42 +5007,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855059</v>
+        <v>854946</v>
       </c>
       <c r="R44" t="n">
-        <v>7478173</v>
+        <v>7478367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5098,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427391</v>
+        <v>124427406</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,38 +5114,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855091</v>
+        <v>855096</v>
       </c>
       <c r="R45" t="n">
-        <v>7478207</v>
+        <v>7478199</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,6 +5181,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5223,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427369</v>
+        <v>124427399</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5239,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5263,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854943</v>
+        <v>855007</v>
       </c>
       <c r="R46" t="n">
-        <v>7478362</v>
+        <v>7478357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5325,7 +5315,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427345</v>
+        <v>124427347</v>
       </c>
       <c r="B47" t="n">
         <v>79927</v>
@@ -5365,10 +5355,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854967</v>
+        <v>855063</v>
       </c>
       <c r="R47" t="n">
-        <v>7478177</v>
+        <v>7478044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427365</v>
+        <v>124427398</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854939</v>
+        <v>855100</v>
       </c>
       <c r="R48" t="n">
-        <v>7478324</v>
+        <v>7478058</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427388</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5541,42 +5531,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855074</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478164</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5617,7 +5603,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,38 +5633,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R50" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5738,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427354</v>
+        <v>124427388</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,38 +5735,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855018</v>
+        <v>855074</v>
       </c>
       <c r="R51" t="n">
-        <v>7478119</v>
+        <v>7478164</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5822,6 +5811,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5840,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -5875,7 +5865,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5884,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R52" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5947,7 +5937,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427346</v>
+        <v>124427345</v>
       </c>
       <c r="B53" t="n">
         <v>79927</v>
@@ -5987,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855044</v>
+        <v>854967</v>
       </c>
       <c r="R53" t="n">
-        <v>7478074</v>
+        <v>7478177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427403</v>
+        <v>124427375</v>
       </c>
       <c r="B54" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6089,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854946</v>
+        <v>854922</v>
       </c>
       <c r="R54" t="n">
-        <v>7478367</v>
+        <v>7478323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,6 +6126,21 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6152,7 +6157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427387</v>
+        <v>124427351</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6187,19 +6192,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855102</v>
+        <v>855056</v>
       </c>
       <c r="R55" t="n">
-        <v>7478191</v>
+        <v>7478165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6259,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427386</v>
+        <v>124427356</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,42 +6276,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855066</v>
+        <v>854977</v>
       </c>
       <c r="R56" t="n">
-        <v>7478180</v>
+        <v>7478167</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,7 +6348,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124854790</v>
+        <v>124855364</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6399,21 +6399,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854766</v>
+        <v>855120</v>
       </c>
       <c r="R57" t="n">
-        <v>7478012</v>
+        <v>7477887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6446,6 +6442,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6473,10 +6474,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855330</v>
+        <v>124855467</v>
       </c>
       <c r="B58" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6485,46 +6486,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854676</v>
+        <v>855062</v>
       </c>
       <c r="R58" t="n">
-        <v>7477840</v>
+        <v>7478002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6557,11 +6550,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6588,10 +6576,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855401</v>
+        <v>124855275</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6600,42 +6588,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854928</v>
+        <v>854889</v>
       </c>
       <c r="R59" t="n">
-        <v>7477769</v>
+        <v>7477847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6662,12 +6646,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6676,7 +6660,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6695,10 +6678,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855232</v>
+        <v>124855380</v>
       </c>
       <c r="B60" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6707,25 +6690,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6735,10 +6718,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855094</v>
+        <v>854745</v>
       </c>
       <c r="R60" t="n">
-        <v>7477931</v>
+        <v>7477946</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,6 +6762,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6797,7 +6781,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855418</v>
+        <v>124855415</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6837,10 +6821,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855131</v>
+        <v>854928</v>
       </c>
       <c r="R61" t="n">
-        <v>7477924</v>
+        <v>7478107</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6899,10 +6883,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855420</v>
+        <v>124855257</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6911,25 +6895,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6939,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855071</v>
+        <v>854894</v>
       </c>
       <c r="R62" t="n">
-        <v>7477912</v>
+        <v>7477768</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6969,12 +6953,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7001,7 +6990,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855417</v>
+        <v>124855416</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7041,10 +7030,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855202</v>
+        <v>855002</v>
       </c>
       <c r="R63" t="n">
-        <v>7477976</v>
+        <v>7478149</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,7 +7092,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855389</v>
+        <v>124855390</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7138,7 +7127,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7147,10 +7136,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854906</v>
+        <v>854899</v>
       </c>
       <c r="R64" t="n">
-        <v>7477891</v>
+        <v>7477831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7210,10 +7199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855313</v>
+        <v>124855250</v>
       </c>
       <c r="B65" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7226,21 +7215,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7312,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855231</v>
+        <v>124855404</v>
       </c>
       <c r="B66" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7324,38 +7313,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854954</v>
+        <v>854832</v>
       </c>
       <c r="R66" t="n">
-        <v>7478125</v>
+        <v>7477880</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7396,6 +7389,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7414,7 +7408,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855380</v>
+        <v>124855358</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7450,14 +7444,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854745</v>
+        <v>854772</v>
       </c>
       <c r="R67" t="n">
-        <v>7477946</v>
+        <v>7477881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,6 +7484,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7517,10 +7516,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855275</v>
+        <v>124855469</v>
       </c>
       <c r="B68" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7529,38 +7528,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854889</v>
+        <v>854979</v>
       </c>
       <c r="R68" t="n">
-        <v>7477847</v>
+        <v>7477885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7619,10 +7618,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855316</v>
+        <v>124855277</v>
       </c>
       <c r="B69" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7635,21 +7634,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7659,10 +7658,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855019</v>
+        <v>855068</v>
       </c>
       <c r="R69" t="n">
-        <v>7477888</v>
+        <v>7478046</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7721,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855500</v>
+        <v>124855333</v>
       </c>
       <c r="B70" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7737,21 +7736,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7761,10 +7760,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854850</v>
+        <v>854924</v>
       </c>
       <c r="R70" t="n">
-        <v>7477915</v>
+        <v>7478087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7823,10 +7822,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855257</v>
+        <v>124855475</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7839,16 +7838,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7863,10 +7862,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854894</v>
+        <v>854813</v>
       </c>
       <c r="R71" t="n">
-        <v>7477768</v>
+        <v>7477923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7893,17 +7892,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7930,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855482</v>
+        <v>124854790</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7942,38 +7936,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855134</v>
+        <v>854766</v>
       </c>
       <c r="R72" t="n">
-        <v>7477890</v>
+        <v>7478012</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8014,6 +8012,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8032,10 +8031,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855318</v>
+        <v>124855231</v>
       </c>
       <c r="B73" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8048,21 +8047,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8072,10 +8071,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854817</v>
+        <v>854954</v>
       </c>
       <c r="R73" t="n">
-        <v>7477931</v>
+        <v>7478125</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8236,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855466</v>
+        <v>124855328</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,38 +8247,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854921</v>
+        <v>854802</v>
       </c>
       <c r="R75" t="n">
-        <v>7478082</v>
+        <v>7477769</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8306,12 +8305,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8338,7 +8342,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855371</v>
+        <v>124855464</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8371,21 +8375,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854845</v>
+        <v>854898</v>
       </c>
       <c r="R76" t="n">
-        <v>7477869</v>
+        <v>7478156</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8426,7 +8426,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8445,7 +8444,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855421</v>
+        <v>124855359</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8481,14 +8480,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854951</v>
+        <v>854838</v>
       </c>
       <c r="R77" t="n">
-        <v>7477899</v>
+        <v>7477840</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8523,12 +8522,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8547,10 +8552,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855381</v>
+        <v>124855233</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8559,25 +8564,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8587,10 +8592,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854803</v>
+        <v>855073</v>
       </c>
       <c r="R78" t="n">
-        <v>7477930</v>
+        <v>7477920</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8631,7 +8636,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8650,10 +8654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855240</v>
+        <v>124855401</v>
       </c>
       <c r="B79" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8662,38 +8666,42 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854937</v>
+        <v>854928</v>
       </c>
       <c r="R79" t="n">
-        <v>7477782</v>
+        <v>7477769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8734,6 +8742,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8752,10 +8761,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855277</v>
+        <v>124855376</v>
       </c>
       <c r="B80" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8764,38 +8773,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855068</v>
+        <v>854741</v>
       </c>
       <c r="R80" t="n">
-        <v>7478046</v>
+        <v>7477958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8836,6 +8849,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8854,10 +8868,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855328</v>
+        <v>124855512</v>
       </c>
       <c r="B81" t="n">
-        <v>56725</v>
+        <v>79926</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8870,34 +8884,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102613</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854802</v>
+        <v>854911</v>
       </c>
       <c r="R81" t="n">
-        <v>7477769</v>
+        <v>7478164</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,17 +8938,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8961,10 +8970,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855475</v>
+        <v>124855381</v>
       </c>
       <c r="B82" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8973,25 +8982,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9001,10 +9010,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854813</v>
+        <v>854803</v>
       </c>
       <c r="R82" t="n">
-        <v>7477923</v>
+        <v>7477930</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,6 +9054,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9063,10 +9073,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855366</v>
+        <v>124855482</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9075,42 +9085,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854807</v>
+        <v>855134</v>
       </c>
       <c r="R83" t="n">
-        <v>7477926</v>
+        <v>7477890</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9151,7 +9157,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9170,10 +9175,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855244</v>
+        <v>124855330</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>56725</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9182,38 +9187,46 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855187</v>
+        <v>854676</v>
       </c>
       <c r="R84" t="n">
-        <v>7478029</v>
+        <v>7477840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9246,6 +9259,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9272,10 +9290,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855536</v>
+        <v>124855394</v>
       </c>
       <c r="B85" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9284,38 +9302,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854869</v>
+        <v>854897</v>
       </c>
       <c r="R85" t="n">
-        <v>7477778</v>
+        <v>7477846</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9342,17 +9364,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9361,6 +9378,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9379,10 +9397,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855483</v>
+        <v>124855500</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9391,25 +9409,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9419,10 +9437,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855251</v>
+        <v>854850</v>
       </c>
       <c r="R86" t="n">
-        <v>7478036</v>
+        <v>7477915</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9481,7 +9499,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855394</v>
+        <v>124855423</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9514,21 +9532,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854897</v>
+        <v>854915</v>
       </c>
       <c r="R87" t="n">
-        <v>7477846</v>
+        <v>7477851</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9569,7 +9583,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9588,10 +9601,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855233</v>
+        <v>124855318</v>
       </c>
       <c r="B88" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9604,21 +9617,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9628,10 +9641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855073</v>
+        <v>854817</v>
       </c>
       <c r="R88" t="n">
-        <v>7477920</v>
+        <v>7477931</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9690,7 +9703,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855390</v>
+        <v>124855417</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9723,21 +9736,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854899</v>
+        <v>855202</v>
       </c>
       <c r="R89" t="n">
-        <v>7477831</v>
+        <v>7477976</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9778,7 +9787,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9797,10 +9805,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855250</v>
+        <v>124855240</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9809,25 +9817,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9837,10 +9845,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854814</v>
+        <v>854937</v>
       </c>
       <c r="R90" t="n">
-        <v>7477852</v>
+        <v>7477782</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9867,12 +9875,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9899,10 +9907,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855333</v>
+        <v>124855366</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9911,38 +9919,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854924</v>
+        <v>854807</v>
       </c>
       <c r="R91" t="n">
-        <v>7478087</v>
+        <v>7477926</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9983,6 +9995,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10103,7 +10116,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855423</v>
+        <v>124855420</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10143,10 +10156,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854915</v>
+        <v>855071</v>
       </c>
       <c r="R93" t="n">
-        <v>7477851</v>
+        <v>7477912</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10205,7 +10218,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855404</v>
+        <v>124855424</v>
       </c>
       <c r="B94" t="n">
         <v>98101</v>
@@ -10238,21 +10251,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854832</v>
+        <v>854780</v>
       </c>
       <c r="R94" t="n">
-        <v>7477880</v>
+        <v>7477939</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10293,7 +10302,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10312,7 +10320,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855468</v>
+        <v>124855386</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10345,17 +10353,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855069</v>
+        <v>854810</v>
       </c>
       <c r="R95" t="n">
-        <v>7477999</v>
+        <v>7477930</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10396,6 +10408,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10414,10 +10427,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855358</v>
+        <v>124855483</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10426,38 +10439,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854772</v>
+        <v>855251</v>
       </c>
       <c r="R96" t="n">
-        <v>7477881</v>
+        <v>7478036</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10492,18 +10505,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10624,7 +10631,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855424</v>
+        <v>124855418</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10664,10 +10671,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854780</v>
+        <v>855131</v>
       </c>
       <c r="R98" t="n">
-        <v>7477939</v>
+        <v>7477924</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10726,10 +10733,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855317</v>
+        <v>124855232</v>
       </c>
       <c r="B99" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10742,21 +10749,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10766,10 +10773,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854783</v>
+        <v>855094</v>
       </c>
       <c r="R99" t="n">
-        <v>7477935</v>
+        <v>7477931</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10828,7 +10835,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855376</v>
+        <v>124855421</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10861,21 +10868,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854741</v>
+        <v>854951</v>
       </c>
       <c r="R100" t="n">
-        <v>7477958</v>
+        <v>7477899</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10916,7 +10919,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10935,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855416</v>
+        <v>124855536</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10947,25 +10949,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10975,10 +10977,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855002</v>
+        <v>854869</v>
       </c>
       <c r="R101" t="n">
-        <v>7478149</v>
+        <v>7477778</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11005,12 +11007,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11037,7 +11044,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855415</v>
+        <v>124855466</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11077,10 +11084,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854928</v>
+        <v>854921</v>
       </c>
       <c r="R102" t="n">
-        <v>7478107</v>
+        <v>7478082</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11139,7 +11146,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855467</v>
+        <v>124855389</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11172,17 +11179,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855062</v>
+        <v>854906</v>
       </c>
       <c r="R103" t="n">
-        <v>7478002</v>
+        <v>7477891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11223,6 +11234,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11241,10 +11253,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855464</v>
+        <v>124855317</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11253,25 +11265,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11281,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854898</v>
+        <v>854783</v>
       </c>
       <c r="R104" t="n">
-        <v>7478156</v>
+        <v>7477935</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11343,10 +11355,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855469</v>
+        <v>124855316</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11355,25 +11367,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11383,10 +11395,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854979</v>
+        <v>855019</v>
       </c>
       <c r="R105" t="n">
-        <v>7477885</v>
+        <v>7477888</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11445,7 +11457,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855386</v>
+        <v>124855468</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11478,21 +11490,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854810</v>
+        <v>855069</v>
       </c>
       <c r="R106" t="n">
-        <v>7477930</v>
+        <v>7477999</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11533,7 +11541,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11552,10 +11559,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855512</v>
+        <v>124855371</v>
       </c>
       <c r="B107" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11564,38 +11571,42 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854911</v>
+        <v>854845</v>
       </c>
       <c r="R107" t="n">
-        <v>7478164</v>
+        <v>7477869</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11636,6 +11647,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11654,10 +11666,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855359</v>
+        <v>124855244</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11666,38 +11678,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854838</v>
+        <v>855187</v>
       </c>
       <c r="R108" t="n">
-        <v>7477840</v>
+        <v>7478029</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11732,18 +11744,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11762,10 +11768,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855364</v>
+        <v>124855313</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11774,38 +11780,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855120</v>
+        <v>854814</v>
       </c>
       <c r="R109" t="n">
-        <v>7477887</v>
+        <v>7477852</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11840,18 +11846,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,7 +4266,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427387</v>
+        <v>124427388</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4305,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855102</v>
+        <v>855074</v>
       </c>
       <c r="R37" t="n">
-        <v>7478191</v>
+        <v>7478164</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,10 +4480,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427365</v>
+        <v>124427345</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4487,38 +4492,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854939</v>
+        <v>854967</v>
       </c>
       <c r="R39" t="n">
-        <v>7478324</v>
+        <v>7478177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4577,10 +4582,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427393</v>
+        <v>124427406</v>
       </c>
       <c r="B40" t="n">
-        <v>56714</v>
+        <v>91579</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4589,38 +4594,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854990</v>
+        <v>855096</v>
       </c>
       <c r="R40" t="n">
-        <v>7478363</v>
+        <v>7478199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4655,12 +4667,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4679,10 +4697,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427352</v>
+        <v>124427365</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,42 +4709,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855059</v>
+        <v>854939</v>
       </c>
       <c r="R41" t="n">
-        <v>7478173</v>
+        <v>7478324</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4767,7 +4781,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4786,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427369</v>
+        <v>124427354</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4802,34 +4815,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854943</v>
+        <v>855018</v>
       </c>
       <c r="R42" t="n">
-        <v>7478362</v>
+        <v>7478119</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4995,10 +5008,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427403</v>
+        <v>124427356</v>
       </c>
       <c r="B44" t="n">
-        <v>79826</v>
+        <v>79926</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,34 +5024,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854946</v>
+        <v>854977</v>
       </c>
       <c r="R44" t="n">
-        <v>7478367</v>
+        <v>7478167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5092,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5098,10 +5110,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427406</v>
+        <v>124427347</v>
       </c>
       <c r="B45" t="n">
-        <v>91579</v>
+        <v>79927</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5110,45 +5122,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855096</v>
+        <v>855063</v>
       </c>
       <c r="R45" t="n">
-        <v>7478199</v>
+        <v>7478044</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,18 +5188,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5213,10 +5212,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427399</v>
+        <v>124427375</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5225,25 +5224,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5253,10 +5252,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855007</v>
+        <v>854922</v>
       </c>
       <c r="R46" t="n">
-        <v>7478357</v>
+        <v>7478323</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,8 +5296,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5315,10 +5330,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427347</v>
+        <v>124427401</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5327,38 +5342,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855063</v>
+        <v>855011</v>
       </c>
       <c r="R47" t="n">
-        <v>7478044</v>
+        <v>7478352</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,10 +5432,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427398</v>
+        <v>124427403</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5429,25 +5444,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5457,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855100</v>
+        <v>854946</v>
       </c>
       <c r="R48" t="n">
-        <v>7478058</v>
+        <v>7478367</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5501,6 +5516,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5519,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427393</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,34 +5551,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>854990</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478363</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427388</v>
+        <v>124427398</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5735,42 +5751,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855074</v>
+        <v>855100</v>
       </c>
       <c r="R51" t="n">
-        <v>7478164</v>
+        <v>7478058</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,7 +5823,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5937,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427345</v>
+        <v>124427399</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5949,38 +5960,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854967</v>
+        <v>855007</v>
       </c>
       <c r="R53" t="n">
-        <v>7478177</v>
+        <v>7478357</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427375</v>
+        <v>124427369</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,25 +6062,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6079,10 +6090,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854922</v>
+        <v>854943</v>
       </c>
       <c r="R54" t="n">
-        <v>7478323</v>
+        <v>7478362</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6123,24 +6134,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6264,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427356</v>
+        <v>124427387</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,38 +6271,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854977</v>
+        <v>855102</v>
       </c>
       <c r="R56" t="n">
-        <v>7478167</v>
+        <v>7478191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,6 +6347,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855364</v>
+        <v>124855257</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855120</v>
+        <v>854894</v>
       </c>
       <c r="R57" t="n">
-        <v>7477887</v>
+        <v>7477768</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6436,17 +6436,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6455,7 +6455,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855467</v>
+        <v>124855330</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6486,38 +6485,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855062</v>
+        <v>854676</v>
       </c>
       <c r="R58" t="n">
-        <v>7478002</v>
+        <v>7477840</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6550,6 +6557,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6576,10 +6588,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855275</v>
+        <v>124855474</v>
       </c>
       <c r="B59" t="n">
-        <v>92321</v>
+        <v>56714</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6592,34 +6604,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854889</v>
+        <v>855065</v>
       </c>
       <c r="R59" t="n">
-        <v>7477847</v>
+        <v>7478197</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6678,7 +6690,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855380</v>
+        <v>124855416</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6718,10 +6730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854745</v>
+        <v>855002</v>
       </c>
       <c r="R60" t="n">
-        <v>7477946</v>
+        <v>7478149</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6762,7 +6774,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6781,7 +6792,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855415</v>
+        <v>124855401</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6814,7 +6825,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
@@ -6824,7 +6839,7 @@
         <v>854928</v>
       </c>
       <c r="R61" t="n">
-        <v>7478107</v>
+        <v>7477769</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,12 +6866,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6865,6 +6880,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6883,10 +6899,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855257</v>
+        <v>124855420</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6895,25 +6911,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6939,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854894</v>
+        <v>855071</v>
       </c>
       <c r="R62" t="n">
-        <v>7477768</v>
+        <v>7477912</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6953,17 +6969,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6990,10 +7001,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855416</v>
+        <v>124855275</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7002,38 +7013,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855002</v>
+        <v>854889</v>
       </c>
       <c r="R63" t="n">
-        <v>7478149</v>
+        <v>7477847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7092,7 +7103,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855390</v>
+        <v>124855468</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7125,21 +7136,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854899</v>
+        <v>855069</v>
       </c>
       <c r="R64" t="n">
-        <v>7477831</v>
+        <v>7477999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,7 +7187,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7199,10 +7205,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855250</v>
+        <v>124855464</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7211,25 +7217,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7239,10 +7245,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854814</v>
+        <v>854898</v>
       </c>
       <c r="R65" t="n">
-        <v>7477852</v>
+        <v>7478156</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,7 +7307,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855404</v>
+        <v>124855423</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7334,21 +7340,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854832</v>
+        <v>854915</v>
       </c>
       <c r="R66" t="n">
-        <v>7477880</v>
+        <v>7477851</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,7 +7391,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7408,7 +7409,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855358</v>
+        <v>124855424</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7444,14 +7445,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854772</v>
+        <v>854780</v>
       </c>
       <c r="R67" t="n">
-        <v>7477881</v>
+        <v>7477939</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,18 +7487,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7516,10 +7511,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855469</v>
+        <v>124855512</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7528,25 +7523,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854979</v>
+        <v>854911</v>
       </c>
       <c r="R68" t="n">
-        <v>7477885</v>
+        <v>7478164</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7618,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855277</v>
+        <v>124855390</v>
       </c>
       <c r="B69" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7630,38 +7625,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855068</v>
+        <v>854899</v>
       </c>
       <c r="R69" t="n">
-        <v>7478046</v>
+        <v>7477831</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7702,6 +7701,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855333</v>
+        <v>124855244</v>
       </c>
       <c r="B70" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7732,25 +7732,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854924</v>
+        <v>855187</v>
       </c>
       <c r="R70" t="n">
-        <v>7478087</v>
+        <v>7478029</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855475</v>
+        <v>124855317</v>
       </c>
       <c r="B71" t="n">
-        <v>56714</v>
+        <v>96985</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7834,25 +7834,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854813</v>
+        <v>854783</v>
       </c>
       <c r="R71" t="n">
-        <v>7477923</v>
+        <v>7477935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124854790</v>
+        <v>124855233</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7936,42 +7936,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854766</v>
+        <v>855073</v>
       </c>
       <c r="R72" t="n">
-        <v>7478012</v>
+        <v>7477920</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8012,7 +8008,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8031,10 +8026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855231</v>
+        <v>124855466</v>
       </c>
       <c r="B73" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8043,25 +8038,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8071,10 +8066,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854954</v>
+        <v>854921</v>
       </c>
       <c r="R73" t="n">
-        <v>7478125</v>
+        <v>7478082</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8133,10 +8128,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855524</v>
+        <v>124855366</v>
       </c>
       <c r="B74" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8145,38 +8140,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854793</v>
+        <v>854807</v>
       </c>
       <c r="R74" t="n">
-        <v>7477805</v>
+        <v>7477926</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8203,12 +8202,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8217,6 +8216,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8235,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855328</v>
+        <v>124855500</v>
       </c>
       <c r="B75" t="n">
-        <v>56725</v>
+        <v>79826</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8251,34 +8251,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102613</v>
+        <v>6457</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854802</v>
+        <v>854850</v>
       </c>
       <c r="R75" t="n">
-        <v>7477769</v>
+        <v>7477915</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8305,17 +8305,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8342,10 +8337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855464</v>
+        <v>124855232</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8354,25 +8349,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8382,10 +8377,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854898</v>
+        <v>855094</v>
       </c>
       <c r="R76" t="n">
-        <v>7478156</v>
+        <v>7477931</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8444,10 +8439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855359</v>
+        <v>124855524</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8456,38 +8451,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854838</v>
+        <v>854793</v>
       </c>
       <c r="R77" t="n">
-        <v>7477840</v>
+        <v>7477805</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8514,17 +8509,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8533,7 +8523,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8541,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855233</v>
+        <v>124855333</v>
       </c>
       <c r="B78" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8568,21 +8557,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8592,10 +8581,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855073</v>
+        <v>854924</v>
       </c>
       <c r="R78" t="n">
-        <v>7477920</v>
+        <v>7478087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8654,7 +8643,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855401</v>
+        <v>124855418</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8687,21 +8676,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854928</v>
+        <v>855131</v>
       </c>
       <c r="R79" t="n">
-        <v>7477769</v>
+        <v>7477924</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8728,12 +8713,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8742,7 +8727,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8761,7 +8745,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855376</v>
+        <v>124855415</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8794,21 +8778,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854741</v>
+        <v>854928</v>
       </c>
       <c r="R80" t="n">
-        <v>7477958</v>
+        <v>7478107</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8849,7 +8829,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8868,10 +8847,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855512</v>
+        <v>124855359</v>
       </c>
       <c r="B81" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8880,38 +8859,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854911</v>
+        <v>854838</v>
       </c>
       <c r="R81" t="n">
-        <v>7478164</v>
+        <v>7477840</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8946,12 +8925,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8970,7 +8955,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855381</v>
+        <v>124855386</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -9003,14 +8988,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854803</v>
+        <v>854810</v>
       </c>
       <c r="R82" t="n">
         <v>7477930</v>
@@ -9175,10 +9164,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855330</v>
+        <v>124855277</v>
       </c>
       <c r="B84" t="n">
-        <v>56725</v>
+        <v>79920</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9191,42 +9180,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854676</v>
+        <v>855068</v>
       </c>
       <c r="R84" t="n">
-        <v>7477840</v>
+        <v>7478046</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9259,11 +9240,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9290,7 +9266,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855394</v>
+        <v>124855469</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9323,21 +9299,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854897</v>
+        <v>854979</v>
       </c>
       <c r="R85" t="n">
-        <v>7477846</v>
+        <v>7477885</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9378,7 +9350,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9397,10 +9368,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855500</v>
+        <v>124855417</v>
       </c>
       <c r="B86" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9409,25 +9380,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9437,10 +9408,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854850</v>
+        <v>855202</v>
       </c>
       <c r="R86" t="n">
-        <v>7477915</v>
+        <v>7477976</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9499,10 +9470,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855423</v>
+        <v>124855231</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9511,25 +9482,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9539,10 +9510,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854915</v>
+        <v>854954</v>
       </c>
       <c r="R87" t="n">
-        <v>7477851</v>
+        <v>7478125</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,10 +9572,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855318</v>
+        <v>124855250</v>
       </c>
       <c r="B88" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9613,25 +9584,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9641,10 +9612,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854817</v>
+        <v>854814</v>
       </c>
       <c r="R88" t="n">
-        <v>7477931</v>
+        <v>7477852</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9703,10 +9674,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855417</v>
+        <v>124855475</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9715,25 +9686,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9743,10 +9714,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855202</v>
+        <v>854813</v>
       </c>
       <c r="R89" t="n">
-        <v>7477976</v>
+        <v>7477923</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9805,10 +9776,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855240</v>
+        <v>124855421</v>
       </c>
       <c r="B90" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9817,25 +9788,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9845,10 +9816,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854937</v>
+        <v>854951</v>
       </c>
       <c r="R90" t="n">
-        <v>7477782</v>
+        <v>7477899</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9875,12 +9846,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9907,10 +9878,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855366</v>
+        <v>124855318</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9919,42 +9890,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854807</v>
+        <v>854817</v>
       </c>
       <c r="R91" t="n">
-        <v>7477926</v>
+        <v>7477931</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9995,7 +9962,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10014,10 +9980,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855474</v>
+        <v>124855240</v>
       </c>
       <c r="B92" t="n">
-        <v>56714</v>
+        <v>105102</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10026,25 +9992,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10054,10 +10020,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855065</v>
+        <v>854937</v>
       </c>
       <c r="R92" t="n">
-        <v>7478197</v>
+        <v>7477782</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10084,12 +10050,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10116,10 +10082,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855420</v>
+        <v>124855316</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10128,25 +10094,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10156,10 +10122,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855071</v>
+        <v>855019</v>
       </c>
       <c r="R93" t="n">
-        <v>7477912</v>
+        <v>7477888</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10218,10 +10184,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855424</v>
+        <v>124855313</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10230,25 +10196,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10258,10 +10224,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854780</v>
+        <v>854814</v>
       </c>
       <c r="R94" t="n">
-        <v>7477939</v>
+        <v>7477852</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10320,10 +10286,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855386</v>
+        <v>124855328</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10332,42 +10298,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854810</v>
+        <v>854802</v>
       </c>
       <c r="R95" t="n">
-        <v>7477930</v>
+        <v>7477769</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10394,12 +10356,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10408,7 +10375,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10427,10 +10393,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855483</v>
+        <v>124855380</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10439,25 +10405,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10467,10 +10433,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855251</v>
+        <v>854745</v>
       </c>
       <c r="R96" t="n">
-        <v>7478036</v>
+        <v>7477946</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10511,6 +10477,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10529,10 +10496,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124854791</v>
+        <v>124855381</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10541,38 +10508,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854840</v>
+        <v>854803</v>
       </c>
       <c r="R97" t="n">
-        <v>7477716</v>
+        <v>7477930</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10599,12 +10566,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10613,6 +10580,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10631,10 +10599,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855418</v>
+        <v>124855536</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10643,25 +10611,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10671,10 +10639,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855131</v>
+        <v>854869</v>
       </c>
       <c r="R98" t="n">
-        <v>7477924</v>
+        <v>7477778</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10701,12 +10669,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10733,10 +10706,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855232</v>
+        <v>124854790</v>
       </c>
       <c r="B99" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10745,38 +10718,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855094</v>
+        <v>854766</v>
       </c>
       <c r="R99" t="n">
-        <v>7477931</v>
+        <v>7478012</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10817,6 +10794,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10835,7 +10813,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855421</v>
+        <v>124855467</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10875,10 +10853,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854951</v>
+        <v>855062</v>
       </c>
       <c r="R100" t="n">
-        <v>7477899</v>
+        <v>7478002</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10937,10 +10915,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855536</v>
+        <v>124854791</v>
       </c>
       <c r="B101" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10953,34 +10931,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854869</v>
+        <v>854840</v>
       </c>
       <c r="R101" t="n">
-        <v>7477778</v>
+        <v>7477716</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11013,11 +10991,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11044,10 +11017,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855466</v>
+        <v>124855483</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11056,25 +11029,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11084,10 +11057,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854921</v>
+        <v>855251</v>
       </c>
       <c r="R102" t="n">
-        <v>7478082</v>
+        <v>7478036</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11146,7 +11119,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855389</v>
+        <v>124855371</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11181,7 +11154,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11190,10 +11163,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854906</v>
+        <v>854845</v>
       </c>
       <c r="R103" t="n">
-        <v>7477891</v>
+        <v>7477869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11253,10 +11226,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855317</v>
+        <v>124855376</v>
       </c>
       <c r="B104" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11265,38 +11238,42 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854783</v>
+        <v>854741</v>
       </c>
       <c r="R104" t="n">
-        <v>7477935</v>
+        <v>7477958</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11337,6 +11314,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11355,10 +11333,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855316</v>
+        <v>124855394</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,38 +11345,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855019</v>
+        <v>854897</v>
       </c>
       <c r="R105" t="n">
-        <v>7477888</v>
+        <v>7477846</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11439,6 +11421,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11457,7 +11440,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855468</v>
+        <v>124855364</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11493,14 +11476,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855069</v>
+        <v>855120</v>
       </c>
       <c r="R106" t="n">
-        <v>7477999</v>
+        <v>7477887</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11535,12 +11518,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11559,7 +11548,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855371</v>
+        <v>124855389</v>
       </c>
       <c r="B107" t="n">
         <v>98101</v>
@@ -11594,7 +11583,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11603,10 +11592,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854845</v>
+        <v>854906</v>
       </c>
       <c r="R107" t="n">
-        <v>7477869</v>
+        <v>7477891</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11666,10 +11655,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855244</v>
+        <v>124855358</v>
       </c>
       <c r="B108" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11678,38 +11667,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855187</v>
+        <v>854772</v>
       </c>
       <c r="R108" t="n">
-        <v>7478029</v>
+        <v>7477881</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11744,12 +11733,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11768,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855313</v>
+        <v>124855404</v>
       </c>
       <c r="B109" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11780,38 +11775,42 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854814</v>
+        <v>854832</v>
       </c>
       <c r="R109" t="n">
-        <v>7477852</v>
+        <v>7477880</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11852,6 +11851,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427352</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855059</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478173</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427388</v>
+        <v>124427356</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,42 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855074</v>
+        <v>854977</v>
       </c>
       <c r="R37" t="n">
-        <v>7478164</v>
+        <v>7478167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4354,7 +4345,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4373,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427389</v>
+        <v>124427347</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4385,42 +4375,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855110</v>
+        <v>855063</v>
       </c>
       <c r="R38" t="n">
-        <v>7478072</v>
+        <v>7478044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,7 +4447,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4480,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427345</v>
+        <v>124427352</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4492,38 +4477,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854967</v>
+        <v>855059</v>
       </c>
       <c r="R39" t="n">
-        <v>7478177</v>
+        <v>7478173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4564,6 +4553,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4582,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427406</v>
+        <v>124427354</v>
       </c>
       <c r="B40" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4594,45 +4584,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855096</v>
+        <v>855018</v>
       </c>
       <c r="R40" t="n">
-        <v>7478199</v>
+        <v>7478119</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,18 +4650,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4697,10 +4674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427365</v>
+        <v>124427393</v>
       </c>
       <c r="B41" t="n">
-        <v>79428</v>
+        <v>56714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4713,21 +4690,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4737,10 +4714,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854939</v>
+        <v>854990</v>
       </c>
       <c r="R41" t="n">
-        <v>7478324</v>
+        <v>7478363</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,10 +4776,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427354</v>
+        <v>124427351</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,38 +4788,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855018</v>
+        <v>855056</v>
       </c>
       <c r="R42" t="n">
-        <v>7478119</v>
+        <v>7478165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,6 +4864,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4901,10 +4883,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427386</v>
+        <v>124427345</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,42 +4895,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855066</v>
+        <v>854967</v>
       </c>
       <c r="R43" t="n">
-        <v>7478180</v>
+        <v>7478177</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4967,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,10 +4985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427356</v>
+        <v>124427386</v>
       </c>
       <c r="B44" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5020,38 +4997,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854977</v>
+        <v>855066</v>
       </c>
       <c r="R44" t="n">
-        <v>7478167</v>
+        <v>7478180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5092,6 +5073,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5110,10 +5092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427347</v>
+        <v>124427399</v>
       </c>
       <c r="B45" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5122,38 +5104,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855063</v>
+        <v>855007</v>
       </c>
       <c r="R45" t="n">
-        <v>7478044</v>
+        <v>7478357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5212,10 +5194,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427375</v>
+        <v>124427406</v>
       </c>
       <c r="B46" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5224,38 +5206,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854922</v>
+        <v>855096</v>
       </c>
       <c r="R46" t="n">
-        <v>7478323</v>
+        <v>7478199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,6 +5279,11 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5299,21 +5293,6 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5330,10 +5309,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427401</v>
+        <v>124427387</v>
       </c>
       <c r="B47" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5342,38 +5321,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855011</v>
+        <v>855102</v>
       </c>
       <c r="R47" t="n">
-        <v>7478352</v>
+        <v>7478191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5414,6 +5397,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5432,10 +5416,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427403</v>
+        <v>124427365</v>
       </c>
       <c r="B48" t="n">
-        <v>79826</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,25 +5428,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5456,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854946</v>
+        <v>854939</v>
       </c>
       <c r="R48" t="n">
-        <v>7478367</v>
+        <v>7478324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5516,7 +5500,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427393</v>
+        <v>124427391</v>
       </c>
       <c r="B49" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5547,38 +5530,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854990</v>
+        <v>855091</v>
       </c>
       <c r="R49" t="n">
-        <v>7478363</v>
+        <v>7478207</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,6 +5606,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5637,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427346</v>
+        <v>124427389</v>
       </c>
       <c r="B50" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5649,38 +5637,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855044</v>
+        <v>855110</v>
       </c>
       <c r="R50" t="n">
-        <v>7478074</v>
+        <v>7478072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5721,6 +5713,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5739,10 +5732,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427398</v>
+        <v>124427388</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5751,38 +5744,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855100</v>
+        <v>855074</v>
       </c>
       <c r="R51" t="n">
-        <v>7478058</v>
+        <v>7478164</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5823,6 +5820,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5839,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427391</v>
+        <v>124427403</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,42 +5851,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855091</v>
+        <v>854946</v>
       </c>
       <c r="R52" t="n">
-        <v>7478207</v>
+        <v>7478367</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427399</v>
+        <v>124427369</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5964,21 +5958,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5988,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855007</v>
+        <v>854943</v>
       </c>
       <c r="R53" t="n">
-        <v>7478357</v>
+        <v>7478362</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6050,10 +6044,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427369</v>
+        <v>124427375</v>
       </c>
       <c r="B54" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6062,25 +6056,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6090,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854943</v>
+        <v>854922</v>
       </c>
       <c r="R54" t="n">
-        <v>7478362</v>
+        <v>7478323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6134,8 +6128,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6152,10 +6162,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427351</v>
+        <v>124427346</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,42 +6174,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855056</v>
+        <v>855044</v>
       </c>
       <c r="R55" t="n">
-        <v>7478165</v>
+        <v>7478074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,7 +6246,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6259,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427387</v>
+        <v>124427398</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,42 +6276,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855102</v>
+        <v>855100</v>
       </c>
       <c r="R56" t="n">
-        <v>7478191</v>
+        <v>7478058</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,7 +6348,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855257</v>
+        <v>124855359</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854894</v>
+        <v>854838</v>
       </c>
       <c r="R57" t="n">
-        <v>7477768</v>
+        <v>7477840</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6436,17 +6436,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6455,6 +6455,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6473,10 +6474,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855330</v>
+        <v>124855313</v>
       </c>
       <c r="B58" t="n">
-        <v>56725</v>
+        <v>91299</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6485,46 +6486,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102613</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854676</v>
+        <v>854814</v>
       </c>
       <c r="R58" t="n">
-        <v>7477840</v>
+        <v>7477852</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6557,11 +6550,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6588,10 +6576,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855474</v>
+        <v>124855329</v>
       </c>
       <c r="B59" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6600,20 +6588,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6624,14 +6612,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855065</v>
+        <v>854676</v>
       </c>
       <c r="R59" t="n">
-        <v>7478197</v>
+        <v>7477840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6658,12 +6646,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6690,10 +6683,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855416</v>
+        <v>124855512</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6702,25 +6695,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6730,10 +6723,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855002</v>
+        <v>854911</v>
       </c>
       <c r="R60" t="n">
-        <v>7478149</v>
+        <v>7478164</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6792,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855401</v>
+        <v>124855474</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6804,42 +6797,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854928</v>
+        <v>855065</v>
       </c>
       <c r="R61" t="n">
-        <v>7477769</v>
+        <v>7478197</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6866,12 +6855,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6880,7 +6869,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6899,7 +6887,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855420</v>
+        <v>124855394</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -6932,17 +6920,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855071</v>
+        <v>854897</v>
       </c>
       <c r="R62" t="n">
-        <v>7477912</v>
+        <v>7477846</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,6 +6975,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7001,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855275</v>
+        <v>124855421</v>
       </c>
       <c r="B63" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7013,38 +7006,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854889</v>
+        <v>854951</v>
       </c>
       <c r="R63" t="n">
-        <v>7477847</v>
+        <v>7477899</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,7 +7096,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855468</v>
+        <v>124855464</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7143,10 +7136,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855069</v>
+        <v>854898</v>
       </c>
       <c r="R64" t="n">
-        <v>7477999</v>
+        <v>7478156</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7205,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855464</v>
+        <v>124855257</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7217,25 +7210,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7245,10 +7238,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854898</v>
+        <v>854894</v>
       </c>
       <c r="R65" t="n">
-        <v>7478156</v>
+        <v>7477768</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7275,12 +7268,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7307,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855423</v>
+        <v>124855316</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7319,25 +7317,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7347,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854915</v>
+        <v>855019</v>
       </c>
       <c r="R66" t="n">
-        <v>7477851</v>
+        <v>7477888</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7409,7 +7407,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855424</v>
+        <v>124855381</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7449,10 +7447,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854780</v>
+        <v>854803</v>
       </c>
       <c r="R67" t="n">
-        <v>7477939</v>
+        <v>7477930</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7493,6 +7491,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7511,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855512</v>
+        <v>124855469</v>
       </c>
       <c r="B68" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7523,25 +7522,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7551,10 +7550,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854911</v>
+        <v>854979</v>
       </c>
       <c r="R68" t="n">
-        <v>7478164</v>
+        <v>7477885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,10 +7612,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855390</v>
+        <v>124855275</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7625,42 +7624,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854899</v>
+        <v>854889</v>
       </c>
       <c r="R69" t="n">
-        <v>7477831</v>
+        <v>7477847</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7701,7 +7696,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7720,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855244</v>
+        <v>124855277</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7732,25 +7726,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7760,10 +7754,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855187</v>
+        <v>855068</v>
       </c>
       <c r="R70" t="n">
-        <v>7478029</v>
+        <v>7478046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7822,10 +7816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855317</v>
+        <v>124855328</v>
       </c>
       <c r="B71" t="n">
-        <v>96985</v>
+        <v>56725</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7838,34 +7832,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854783</v>
+        <v>854802</v>
       </c>
       <c r="R71" t="n">
-        <v>7477935</v>
+        <v>7477769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,12 +7886,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7924,10 +7923,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855233</v>
+        <v>124855418</v>
       </c>
       <c r="B72" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7936,25 +7935,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7964,10 +7963,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855073</v>
+        <v>855131</v>
       </c>
       <c r="R72" t="n">
-        <v>7477920</v>
+        <v>7477924</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8026,7 +8025,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855466</v>
+        <v>124854790</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8059,17 +8058,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854921</v>
+        <v>854766</v>
       </c>
       <c r="R73" t="n">
-        <v>7478082</v>
+        <v>7478012</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8110,6 +8113,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8128,10 +8132,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855366</v>
+        <v>124855483</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8140,42 +8144,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854807</v>
+        <v>855251</v>
       </c>
       <c r="R74" t="n">
-        <v>7477926</v>
+        <v>7478036</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,7 +8216,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8235,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855500</v>
+        <v>124855401</v>
       </c>
       <c r="B75" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8247,38 +8246,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854850</v>
+        <v>854928</v>
       </c>
       <c r="R75" t="n">
-        <v>7477915</v>
+        <v>7477769</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8305,12 +8308,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8319,6 +8322,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8337,10 +8341,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855232</v>
+        <v>124855358</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8349,38 +8353,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855094</v>
+        <v>854772</v>
       </c>
       <c r="R76" t="n">
-        <v>7477931</v>
+        <v>7477881</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8415,12 +8419,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8439,10 +8449,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855524</v>
+        <v>124855376</v>
       </c>
       <c r="B77" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8451,38 +8461,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854793</v>
+        <v>854741</v>
       </c>
       <c r="R77" t="n">
-        <v>7477805</v>
+        <v>7477958</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8509,12 +8523,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8523,6 +8537,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8541,10 +8556,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855333</v>
+        <v>124855250</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8553,25 +8568,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8581,10 +8596,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854924</v>
+        <v>854814</v>
       </c>
       <c r="R78" t="n">
-        <v>7478087</v>
+        <v>7477852</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8643,7 +8658,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855418</v>
+        <v>124855424</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8683,10 +8698,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855131</v>
+        <v>854780</v>
       </c>
       <c r="R79" t="n">
-        <v>7477924</v>
+        <v>7477939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8745,7 +8760,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855415</v>
+        <v>124855364</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8781,14 +8796,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854928</v>
+        <v>855120</v>
       </c>
       <c r="R80" t="n">
-        <v>7478107</v>
+        <v>7477887</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8823,12 +8838,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8847,10 +8868,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855359</v>
+        <v>124855500</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8859,38 +8880,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854838</v>
+        <v>854850</v>
       </c>
       <c r="R81" t="n">
-        <v>7477840</v>
+        <v>7477915</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8925,18 +8946,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8955,10 +8970,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855386</v>
+        <v>124855244</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8967,42 +8982,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854810</v>
+        <v>855187</v>
       </c>
       <c r="R82" t="n">
-        <v>7477930</v>
+        <v>7478029</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9043,7 +9054,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9062,10 +9072,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855482</v>
+        <v>124855416</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9074,25 +9084,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9102,10 +9112,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855134</v>
+        <v>855002</v>
       </c>
       <c r="R83" t="n">
-        <v>7477890</v>
+        <v>7478149</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9164,10 +9174,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855277</v>
+        <v>124855380</v>
       </c>
       <c r="B84" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9176,25 +9186,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9204,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855068</v>
+        <v>854745</v>
       </c>
       <c r="R84" t="n">
-        <v>7478046</v>
+        <v>7477946</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9248,6 +9258,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9266,10 +9277,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855469</v>
+        <v>124855318</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9278,25 +9289,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9306,10 +9317,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854979</v>
+        <v>854817</v>
       </c>
       <c r="R85" t="n">
-        <v>7477885</v>
+        <v>7477931</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9368,7 +9379,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855417</v>
+        <v>124855467</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9408,10 +9419,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855202</v>
+        <v>855062</v>
       </c>
       <c r="R86" t="n">
-        <v>7477976</v>
+        <v>7478002</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9470,10 +9481,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855231</v>
+        <v>124855404</v>
       </c>
       <c r="B87" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9482,38 +9493,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854954</v>
+        <v>854832</v>
       </c>
       <c r="R87" t="n">
-        <v>7478125</v>
+        <v>7477880</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9554,6 +9569,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9572,10 +9588,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855250</v>
+        <v>124855233</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9584,25 +9600,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9612,10 +9628,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854814</v>
+        <v>855073</v>
       </c>
       <c r="R88" t="n">
-        <v>7477852</v>
+        <v>7477920</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9674,10 +9690,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855475</v>
+        <v>124855232</v>
       </c>
       <c r="B89" t="n">
-        <v>56714</v>
+        <v>105102</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9686,25 +9702,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9714,10 +9730,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854813</v>
+        <v>855094</v>
       </c>
       <c r="R89" t="n">
-        <v>7477923</v>
+        <v>7477931</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9776,10 +9792,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855421</v>
+        <v>124855475</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9788,25 +9804,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9816,10 +9832,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854951</v>
+        <v>854813</v>
       </c>
       <c r="R90" t="n">
-        <v>7477899</v>
+        <v>7477923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9878,10 +9894,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855318</v>
+        <v>124855482</v>
       </c>
       <c r="B91" t="n">
-        <v>96985</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9890,25 +9906,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9918,10 +9934,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854817</v>
+        <v>855134</v>
       </c>
       <c r="R91" t="n">
-        <v>7477931</v>
+        <v>7477890</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9980,10 +9996,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855240</v>
+        <v>124855390</v>
       </c>
       <c r="B92" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9992,38 +10008,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854937</v>
+        <v>854899</v>
       </c>
       <c r="R92" t="n">
-        <v>7477782</v>
+        <v>7477831</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10050,12 +10070,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10064,6 +10084,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10082,10 +10103,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855316</v>
+        <v>124855231</v>
       </c>
       <c r="B93" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10098,21 +10119,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10122,10 +10143,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855019</v>
+        <v>854954</v>
       </c>
       <c r="R93" t="n">
-        <v>7477888</v>
+        <v>7478125</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10184,10 +10205,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855313</v>
+        <v>124855386</v>
       </c>
       <c r="B94" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10196,38 +10217,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854814</v>
+        <v>854810</v>
       </c>
       <c r="R94" t="n">
-        <v>7477852</v>
+        <v>7477930</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10268,6 +10293,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10286,10 +10312,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855328</v>
+        <v>124855524</v>
       </c>
       <c r="B95" t="n">
-        <v>56725</v>
+        <v>79926</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10302,34 +10328,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102613</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854802</v>
+        <v>854793</v>
       </c>
       <c r="R95" t="n">
-        <v>7477769</v>
+        <v>7477805</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10362,11 +10388,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10393,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855380</v>
+        <v>124855371</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10426,17 +10447,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854745</v>
+        <v>854845</v>
       </c>
       <c r="R96" t="n">
-        <v>7477946</v>
+        <v>7477869</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10496,7 +10521,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855381</v>
+        <v>124855423</v>
       </c>
       <c r="B97" t="n">
         <v>98101</v>
@@ -10536,10 +10561,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854803</v>
+        <v>854915</v>
       </c>
       <c r="R97" t="n">
-        <v>7477930</v>
+        <v>7477851</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10580,7 +10605,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10599,10 +10623,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855536</v>
+        <v>124855389</v>
       </c>
       <c r="B98" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10611,38 +10635,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854869</v>
+        <v>854906</v>
       </c>
       <c r="R98" t="n">
-        <v>7477778</v>
+        <v>7477891</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10669,17 +10697,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10688,6 +10711,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10706,7 +10730,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124854790</v>
+        <v>124855366</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -10741,19 +10765,19 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>167</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854766</v>
+        <v>854807</v>
       </c>
       <c r="R99" t="n">
-        <v>7478012</v>
+        <v>7477926</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10813,10 +10837,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855467</v>
+        <v>124855536</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10825,25 +10849,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10853,10 +10877,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855062</v>
+        <v>854869</v>
       </c>
       <c r="R100" t="n">
-        <v>7478002</v>
+        <v>7477778</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10883,12 +10907,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11017,10 +11046,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855483</v>
+        <v>124855333</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11029,25 +11058,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11057,10 +11086,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855251</v>
+        <v>854924</v>
       </c>
       <c r="R102" t="n">
-        <v>7478036</v>
+        <v>7478087</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11119,7 +11148,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855371</v>
+        <v>124855415</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11152,21 +11181,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854845</v>
+        <v>854928</v>
       </c>
       <c r="R103" t="n">
-        <v>7477869</v>
+        <v>7478107</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11207,7 +11232,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11226,7 +11250,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855376</v>
+        <v>124855420</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11259,21 +11283,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854741</v>
+        <v>855071</v>
       </c>
       <c r="R104" t="n">
-        <v>7477958</v>
+        <v>7477912</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11314,7 +11334,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11333,10 +11352,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855394</v>
+        <v>124855240</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11345,42 +11364,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854897</v>
+        <v>854937</v>
       </c>
       <c r="R105" t="n">
-        <v>7477846</v>
+        <v>7477782</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11407,12 +11422,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11421,7 +11436,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11440,7 +11454,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855364</v>
+        <v>124855417</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11476,14 +11490,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855120</v>
+        <v>855202</v>
       </c>
       <c r="R106" t="n">
-        <v>7477887</v>
+        <v>7477976</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11518,18 +11532,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11548,10 +11556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855389</v>
+        <v>124855317</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11560,42 +11568,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854906</v>
+        <v>854783</v>
       </c>
       <c r="R107" t="n">
-        <v>7477891</v>
+        <v>7477935</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11636,7 +11640,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11655,7 +11658,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855358</v>
+        <v>124855466</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11691,14 +11694,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854772</v>
+        <v>854921</v>
       </c>
       <c r="R108" t="n">
-        <v>7477881</v>
+        <v>7478082</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11733,18 +11736,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11763,7 +11760,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855404</v>
+        <v>124855468</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11796,21 +11793,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854832</v>
+        <v>855069</v>
       </c>
       <c r="R109" t="n">
-        <v>7477880</v>
+        <v>7477999</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11851,7 +11844,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855359</v>
+        <v>124855313</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854838</v>
+        <v>854814</v>
       </c>
       <c r="R57" t="n">
-        <v>7477840</v>
+        <v>7477852</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6444,18 +6444,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855313</v>
+        <v>124855359</v>
       </c>
       <c r="B58" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6486,38 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854814</v>
+        <v>854838</v>
       </c>
       <c r="R58" t="n">
-        <v>7477852</v>
+        <v>7477840</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,12 +6546,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8132,10 +8132,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855483</v>
+        <v>124855401</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8144,38 +8144,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855251</v>
+        <v>854928</v>
       </c>
       <c r="R74" t="n">
-        <v>7478036</v>
+        <v>7477769</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,12 +8206,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8216,6 +8220,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8234,7 +8239,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855401</v>
+        <v>124855358</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8267,21 +8272,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854928</v>
+        <v>854772</v>
       </c>
       <c r="R75" t="n">
-        <v>7477769</v>
+        <v>7477881</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8308,12 +8309,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8341,7 +8347,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855358</v>
+        <v>124855376</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8374,17 +8380,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854772</v>
+        <v>854741</v>
       </c>
       <c r="R76" t="n">
-        <v>7477881</v>
+        <v>7477958</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8417,11 +8427,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8449,10 +8454,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855376</v>
+        <v>124855483</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8461,42 +8466,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854741</v>
+        <v>855251</v>
       </c>
       <c r="R77" t="n">
-        <v>7477958</v>
+        <v>7478036</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8537,7 +8538,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427356</v>
+        <v>124427406</v>
       </c>
       <c r="B37" t="n">
-        <v>79926</v>
+        <v>91579</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,38 +4278,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854977</v>
+        <v>855096</v>
       </c>
       <c r="R37" t="n">
-        <v>7478167</v>
+        <v>7478199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4339,12 +4351,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427347</v>
+        <v>124427401</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4393,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855063</v>
+        <v>855011</v>
       </c>
       <c r="R38" t="n">
-        <v>7478044</v>
+        <v>7478352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,10 +4483,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,42 +4495,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R39" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4585,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427354</v>
+        <v>124427356</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,20 +4597,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4612,10 +4625,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855018</v>
+        <v>854977</v>
       </c>
       <c r="R40" t="n">
-        <v>7478119</v>
+        <v>7478167</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,10 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427393</v>
+        <v>124427375</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4686,25 +4699,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4714,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854990</v>
+        <v>854922</v>
       </c>
       <c r="R41" t="n">
-        <v>7478363</v>
+        <v>7478323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,8 +4771,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4776,7 +4805,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427351</v>
+        <v>124427389</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4811,19 +4840,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855056</v>
+        <v>855110</v>
       </c>
       <c r="R42" t="n">
-        <v>7478165</v>
+        <v>7478072</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427345</v>
+        <v>124427399</v>
       </c>
       <c r="B43" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,38 +4924,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854967</v>
+        <v>855007</v>
       </c>
       <c r="R43" t="n">
-        <v>7478177</v>
+        <v>7478357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427386</v>
+        <v>124427347</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,42 +5026,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855066</v>
+        <v>855063</v>
       </c>
       <c r="R44" t="n">
-        <v>7478180</v>
+        <v>7478044</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5073,7 +5098,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5092,7 +5116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427399</v>
+        <v>124427398</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5132,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855007</v>
+        <v>855100</v>
       </c>
       <c r="R45" t="n">
-        <v>7478357</v>
+        <v>7478058</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5194,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427406</v>
+        <v>124427387</v>
       </c>
       <c r="B46" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5210,41 +5234,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855096</v>
+        <v>855102</v>
       </c>
       <c r="R46" t="n">
-        <v>7478199</v>
+        <v>7478191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,11 +5298,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5309,7 +5325,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427387</v>
+        <v>124427388</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5344,7 +5360,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5353,10 +5369,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855102</v>
+        <v>855074</v>
       </c>
       <c r="R47" t="n">
-        <v>7478191</v>
+        <v>7478164</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5518,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427391</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,42 +5546,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855091</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478207</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5606,7 +5618,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5625,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427389</v>
+        <v>124427369</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,42 +5648,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855110</v>
+        <v>854943</v>
       </c>
       <c r="R50" t="n">
-        <v>7478072</v>
+        <v>7478362</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,7 +5720,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5732,7 +5738,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427388</v>
+        <v>124427386</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -5767,7 +5773,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5776,10 +5782,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855074</v>
+        <v>855066</v>
       </c>
       <c r="R51" t="n">
-        <v>7478164</v>
+        <v>7478180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5839,10 +5845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427403</v>
+        <v>124427345</v>
       </c>
       <c r="B52" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5855,34 +5861,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854946</v>
+        <v>854967</v>
       </c>
       <c r="R52" t="n">
-        <v>7478367</v>
+        <v>7478177</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5923,7 +5929,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5942,10 +5947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427369</v>
+        <v>124427403</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>79826</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,25 +5959,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854943</v>
+        <v>854946</v>
       </c>
       <c r="R53" t="n">
-        <v>7478362</v>
+        <v>7478367</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6026,6 +6031,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427375</v>
+        <v>124427391</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6056,38 +6062,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854922</v>
+        <v>855091</v>
       </c>
       <c r="R54" t="n">
-        <v>7478323</v>
+        <v>7478207</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,21 +6141,6 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6162,10 +6157,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427346</v>
+        <v>124427393</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6174,38 +6169,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855044</v>
+        <v>854990</v>
       </c>
       <c r="R55" t="n">
-        <v>7478074</v>
+        <v>7478363</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427398</v>
+        <v>124427351</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6276,38 +6271,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855100</v>
+        <v>855056</v>
       </c>
       <c r="R56" t="n">
-        <v>7478058</v>
+        <v>7478165</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,6 +6347,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855313</v>
+        <v>124855371</v>
       </c>
       <c r="B57" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6378,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854814</v>
+        <v>854845</v>
       </c>
       <c r="R57" t="n">
-        <v>7477852</v>
+        <v>7477869</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,6 +6454,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6468,7 +6473,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855359</v>
+        <v>124855468</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6504,14 +6509,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854838</v>
+        <v>855069</v>
       </c>
       <c r="R58" t="n">
-        <v>7477840</v>
+        <v>7477999</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6546,18 +6551,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6576,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855329</v>
+        <v>124855313</v>
       </c>
       <c r="B59" t="n">
-        <v>56725</v>
+        <v>91299</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6588,38 +6587,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102613</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854676</v>
+        <v>854814</v>
       </c>
       <c r="R59" t="n">
-        <v>7477840</v>
+        <v>7477852</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,17 +6645,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6683,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855512</v>
+        <v>124855475</v>
       </c>
       <c r="B60" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6695,25 +6689,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6723,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854911</v>
+        <v>854813</v>
       </c>
       <c r="R60" t="n">
-        <v>7478164</v>
+        <v>7477923</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6887,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855394</v>
+        <v>124855536</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6899,42 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854897</v>
+        <v>854869</v>
       </c>
       <c r="R62" t="n">
-        <v>7477846</v>
+        <v>7477778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,12 +6951,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6975,7 +6970,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6988,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855421</v>
+        <v>124855275</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7006,38 +7000,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854951</v>
+        <v>854889</v>
       </c>
       <c r="R63" t="n">
-        <v>7477899</v>
+        <v>7477847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7096,7 +7090,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855464</v>
+        <v>124855390</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7129,17 +7123,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854898</v>
+        <v>854899</v>
       </c>
       <c r="R64" t="n">
-        <v>7478156</v>
+        <v>7477831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,6 +7178,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7198,10 +7197,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855257</v>
+        <v>124855416</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7210,25 +7209,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7238,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854894</v>
+        <v>855002</v>
       </c>
       <c r="R65" t="n">
-        <v>7477768</v>
+        <v>7478149</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7268,17 +7267,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7305,10 +7299,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855316</v>
+        <v>124855404</v>
       </c>
       <c r="B66" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7317,38 +7311,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855019</v>
+        <v>854832</v>
       </c>
       <c r="R66" t="n">
-        <v>7477888</v>
+        <v>7477880</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,6 +7387,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7406,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855381</v>
+        <v>124855366</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7440,17 +7439,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854803</v>
+        <v>854807</v>
       </c>
       <c r="R67" t="n">
-        <v>7477930</v>
+        <v>7477926</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7510,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855469</v>
+        <v>124855317</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7522,25 +7525,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7550,10 +7553,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854979</v>
+        <v>854783</v>
       </c>
       <c r="R68" t="n">
-        <v>7477885</v>
+        <v>7477935</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855275</v>
+        <v>124855250</v>
       </c>
       <c r="B69" t="n">
-        <v>92321</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7628,34 +7631,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854889</v>
+        <v>854814</v>
       </c>
       <c r="R69" t="n">
-        <v>7477847</v>
+        <v>7477852</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7714,10 +7717,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855277</v>
+        <v>124855394</v>
       </c>
       <c r="B70" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,38 +7729,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855068</v>
+        <v>854897</v>
       </c>
       <c r="R70" t="n">
-        <v>7478046</v>
+        <v>7477846</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7798,6 +7805,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7816,10 +7824,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855328</v>
+        <v>124855389</v>
       </c>
       <c r="B71" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7828,38 +7836,42 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854802</v>
+        <v>854906</v>
       </c>
       <c r="R71" t="n">
-        <v>7477769</v>
+        <v>7477891</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7886,17 +7898,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7905,6 +7912,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7923,7 +7931,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855418</v>
+        <v>124855420</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7963,10 +7971,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855131</v>
+        <v>855071</v>
       </c>
       <c r="R72" t="n">
-        <v>7477924</v>
+        <v>7477912</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8025,10 +8033,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124854790</v>
+        <v>124855240</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8037,42 +8045,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854766</v>
+        <v>854937</v>
       </c>
       <c r="R73" t="n">
-        <v>7478012</v>
+        <v>7477782</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,12 +8103,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8113,7 +8117,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8132,10 +8135,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855401</v>
+        <v>124855329</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8144,42 +8147,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854928</v>
+        <v>854676</v>
       </c>
       <c r="R74" t="n">
-        <v>7477769</v>
+        <v>7477840</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8214,13 +8213,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8239,7 +8242,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855358</v>
+        <v>124855464</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8275,14 +8278,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854772</v>
+        <v>854898</v>
       </c>
       <c r="R75" t="n">
-        <v>7477881</v>
+        <v>7478156</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,18 +8320,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8347,7 +8344,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855376</v>
+        <v>124854790</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8382,19 +8379,19 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854741</v>
+        <v>854766</v>
       </c>
       <c r="R76" t="n">
-        <v>7477958</v>
+        <v>7478012</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8454,10 +8451,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855483</v>
+        <v>124855364</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8466,38 +8463,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855251</v>
+        <v>855120</v>
       </c>
       <c r="R77" t="n">
-        <v>7478036</v>
+        <v>7477887</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8532,12 +8529,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8556,10 +8559,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855250</v>
+        <v>124855424</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8568,25 +8571,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8596,10 +8599,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854814</v>
+        <v>854780</v>
       </c>
       <c r="R78" t="n">
-        <v>7477852</v>
+        <v>7477939</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8658,10 +8661,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855424</v>
+        <v>124855333</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8670,25 +8673,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8698,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854780</v>
+        <v>854924</v>
       </c>
       <c r="R79" t="n">
-        <v>7477939</v>
+        <v>7478087</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8760,7 +8763,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855364</v>
+        <v>124855376</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8793,17 +8796,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855120</v>
+        <v>854741</v>
       </c>
       <c r="R80" t="n">
-        <v>7477887</v>
+        <v>7477958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8836,11 +8843,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8868,10 +8870,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855500</v>
+        <v>124855469</v>
       </c>
       <c r="B81" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8880,25 +8882,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8908,10 +8910,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854850</v>
+        <v>854979</v>
       </c>
       <c r="R81" t="n">
-        <v>7477915</v>
+        <v>7477885</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8970,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855244</v>
+        <v>124855380</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8982,25 +8984,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9010,10 +9012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855187</v>
+        <v>854745</v>
       </c>
       <c r="R82" t="n">
-        <v>7478029</v>
+        <v>7477946</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9054,6 +9056,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9072,7 +9075,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855416</v>
+        <v>124855423</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9112,10 +9115,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855002</v>
+        <v>854915</v>
       </c>
       <c r="R83" t="n">
-        <v>7478149</v>
+        <v>7477851</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9174,10 +9177,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855380</v>
+        <v>124855232</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9186,25 +9189,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9217,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854745</v>
+        <v>855094</v>
       </c>
       <c r="R84" t="n">
-        <v>7477946</v>
+        <v>7477931</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9258,7 +9261,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9277,10 +9279,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855318</v>
+        <v>124855467</v>
       </c>
       <c r="B85" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9289,25 +9291,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9317,10 +9319,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854817</v>
+        <v>855062</v>
       </c>
       <c r="R85" t="n">
-        <v>7477931</v>
+        <v>7478002</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9379,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855467</v>
+        <v>124855244</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9391,25 +9393,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9419,10 +9421,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855062</v>
+        <v>855187</v>
       </c>
       <c r="R86" t="n">
-        <v>7478002</v>
+        <v>7478029</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9481,7 +9483,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855404</v>
+        <v>124855417</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9514,21 +9516,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854832</v>
+        <v>855202</v>
       </c>
       <c r="R87" t="n">
-        <v>7477880</v>
+        <v>7477976</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9569,7 +9567,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9588,10 +9585,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855233</v>
+        <v>124855483</v>
       </c>
       <c r="B88" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9600,25 +9597,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9628,10 +9625,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855073</v>
+        <v>855251</v>
       </c>
       <c r="R88" t="n">
-        <v>7477920</v>
+        <v>7478036</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9690,7 +9687,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855232</v>
+        <v>124855233</v>
       </c>
       <c r="B89" t="n">
         <v>105102</v>
@@ -9730,10 +9727,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855094</v>
+        <v>855073</v>
       </c>
       <c r="R89" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9792,10 +9789,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855475</v>
+        <v>124855524</v>
       </c>
       <c r="B90" t="n">
-        <v>56714</v>
+        <v>79926</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9804,25 +9801,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9832,10 +9829,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854813</v>
+        <v>854793</v>
       </c>
       <c r="R90" t="n">
-        <v>7477923</v>
+        <v>7477805</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9862,12 +9859,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9996,10 +9993,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855390</v>
+        <v>124854791</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10008,42 +10005,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854899</v>
+        <v>854840</v>
       </c>
       <c r="R92" t="n">
-        <v>7477831</v>
+        <v>7477716</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10070,12 +10063,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10084,7 +10077,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10103,10 +10095,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855231</v>
+        <v>124855418</v>
       </c>
       <c r="B93" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10115,25 +10107,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10143,10 +10135,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854954</v>
+        <v>855131</v>
       </c>
       <c r="R93" t="n">
-        <v>7478125</v>
+        <v>7477924</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10205,7 +10197,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855386</v>
+        <v>124855381</v>
       </c>
       <c r="B94" t="n">
         <v>98101</v>
@@ -10238,18 +10230,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854810</v>
+        <v>854803</v>
       </c>
       <c r="R94" t="n">
         <v>7477930</v>
@@ -10312,10 +10300,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855524</v>
+        <v>124855500</v>
       </c>
       <c r="B95" t="n">
-        <v>79926</v>
+        <v>79826</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10328,21 +10316,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10352,10 +10340,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854793</v>
+        <v>854850</v>
       </c>
       <c r="R95" t="n">
-        <v>7477805</v>
+        <v>7477915</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10382,12 +10370,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10414,10 +10402,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855371</v>
+        <v>124855512</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10426,42 +10414,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854845</v>
+        <v>854911</v>
       </c>
       <c r="R96" t="n">
-        <v>7477869</v>
+        <v>7478164</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10502,7 +10486,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10521,10 +10504,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855423</v>
+        <v>124855328</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10533,38 +10516,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854915</v>
+        <v>854802</v>
       </c>
       <c r="R97" t="n">
-        <v>7477851</v>
+        <v>7477769</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10591,12 +10574,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10623,7 +10611,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855389</v>
+        <v>124855401</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10658,7 +10646,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10667,10 +10655,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854906</v>
+        <v>854928</v>
       </c>
       <c r="R98" t="n">
-        <v>7477891</v>
+        <v>7477769</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10697,12 +10685,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10730,10 +10718,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855366</v>
+        <v>124855257</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10742,42 +10730,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854807</v>
+        <v>854894</v>
       </c>
       <c r="R99" t="n">
-        <v>7477926</v>
+        <v>7477768</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10804,12 +10788,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10818,7 +10807,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10837,10 +10825,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855536</v>
+        <v>124855421</v>
       </c>
       <c r="B100" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10849,25 +10837,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10877,10 +10865,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854869</v>
+        <v>854951</v>
       </c>
       <c r="R100" t="n">
-        <v>7477778</v>
+        <v>7477899</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10907,17 +10895,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10944,10 +10927,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124854791</v>
+        <v>124855358</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10956,25 +10939,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10984,10 +10967,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854840</v>
+        <v>854772</v>
       </c>
       <c r="R101" t="n">
-        <v>7477716</v>
+        <v>7477881</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11014,12 +10997,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11028,6 +11016,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11046,10 +11035,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855333</v>
+        <v>124855386</v>
       </c>
       <c r="B102" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11058,38 +11047,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854924</v>
+        <v>854810</v>
       </c>
       <c r="R102" t="n">
-        <v>7478087</v>
+        <v>7477930</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11130,6 +11123,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11148,7 +11142,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855415</v>
+        <v>124855466</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11188,10 +11182,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854928</v>
+        <v>854921</v>
       </c>
       <c r="R103" t="n">
-        <v>7478107</v>
+        <v>7478082</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11250,7 +11244,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855420</v>
+        <v>124855415</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11290,10 +11284,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855071</v>
+        <v>854928</v>
       </c>
       <c r="R104" t="n">
-        <v>7477912</v>
+        <v>7478107</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11352,10 +11346,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855240</v>
+        <v>124855316</v>
       </c>
       <c r="B105" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11368,21 +11362,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11392,10 +11386,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854937</v>
+        <v>855019</v>
       </c>
       <c r="R105" t="n">
-        <v>7477782</v>
+        <v>7477888</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11422,12 +11416,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11454,10 +11448,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855417</v>
+        <v>124855318</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11466,25 +11460,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11494,10 +11488,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855202</v>
+        <v>854817</v>
       </c>
       <c r="R106" t="n">
-        <v>7477976</v>
+        <v>7477931</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11556,10 +11550,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855317</v>
+        <v>124855277</v>
       </c>
       <c r="B107" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11572,21 +11566,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11590,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854783</v>
+        <v>855068</v>
       </c>
       <c r="R107" t="n">
-        <v>7477935</v>
+        <v>7478046</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11658,10 +11652,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855466</v>
+        <v>124855231</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11670,25 +11664,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11698,10 +11692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854921</v>
+        <v>854954</v>
       </c>
       <c r="R108" t="n">
-        <v>7478082</v>
+        <v>7478125</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11760,7 +11754,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855468</v>
+        <v>124855359</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11796,14 +11790,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855069</v>
+        <v>854838</v>
       </c>
       <c r="R109" t="n">
-        <v>7477999</v>
+        <v>7477840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11838,12 +11832,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427391</v>
+        <v>124427393</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6062,42 +6062,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855091</v>
+        <v>854990</v>
       </c>
       <c r="R54" t="n">
-        <v>7478207</v>
+        <v>7478363</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6138,7 +6134,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6157,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427393</v>
+        <v>124427391</v>
       </c>
       <c r="B55" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6169,38 +6164,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854990</v>
+        <v>855091</v>
       </c>
       <c r="R55" t="n">
-        <v>7478363</v>
+        <v>7478207</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6241,6 +6240,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7090,10 +7090,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855390</v>
+        <v>124855250</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,42 +7102,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854899</v>
+        <v>854814</v>
       </c>
       <c r="R64" t="n">
-        <v>7477831</v>
+        <v>7477852</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7178,7 +7174,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7197,7 +7192,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855416</v>
+        <v>124855390</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7230,17 +7225,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855002</v>
+        <v>854899</v>
       </c>
       <c r="R65" t="n">
-        <v>7478149</v>
+        <v>7477831</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7281,6 +7280,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7299,7 +7299,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855404</v>
+        <v>124855416</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7332,21 +7332,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854832</v>
+        <v>855002</v>
       </c>
       <c r="R66" t="n">
-        <v>7477880</v>
+        <v>7478149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7387,7 +7383,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7406,7 +7401,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855366</v>
+        <v>124855404</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7441,7 +7436,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7450,10 +7445,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854807</v>
+        <v>854832</v>
       </c>
       <c r="R67" t="n">
-        <v>7477926</v>
+        <v>7477880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7513,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855317</v>
+        <v>124855366</v>
       </c>
       <c r="B68" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7525,38 +7520,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854783</v>
+        <v>854807</v>
       </c>
       <c r="R68" t="n">
-        <v>7477935</v>
+        <v>7477926</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7597,6 +7596,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7615,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855250</v>
+        <v>124855317</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,25 +7627,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854814</v>
+        <v>854783</v>
       </c>
       <c r="R69" t="n">
-        <v>7477852</v>
+        <v>7477935</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855394</v>
+        <v>124855240</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7729,42 +7729,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854897</v>
+        <v>854937</v>
       </c>
       <c r="R70" t="n">
-        <v>7477846</v>
+        <v>7477782</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7791,12 +7787,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7805,7 +7801,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7824,7 +7819,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855389</v>
+        <v>124855394</v>
       </c>
       <c r="B71" t="n">
         <v>98101</v>
@@ -7859,7 +7854,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854906</v>
+        <v>854897</v>
       </c>
       <c r="R71" t="n">
-        <v>7477891</v>
+        <v>7477846</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7931,7 +7926,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855420</v>
+        <v>124855389</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7964,17 +7959,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855071</v>
+        <v>854906</v>
       </c>
       <c r="R72" t="n">
-        <v>7477912</v>
+        <v>7477891</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8015,6 +8014,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855240</v>
+        <v>124855420</v>
       </c>
       <c r="B73" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8045,25 +8045,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854937</v>
+        <v>855071</v>
       </c>
       <c r="R73" t="n">
-        <v>7477782</v>
+        <v>7477912</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8451,10 +8451,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855364</v>
+        <v>124855333</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8463,38 +8463,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855120</v>
+        <v>854924</v>
       </c>
       <c r="R77" t="n">
-        <v>7477887</v>
+        <v>7478087</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8529,18 +8529,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8559,7 +8553,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855424</v>
+        <v>124855364</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8595,14 +8589,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854780</v>
+        <v>855120</v>
       </c>
       <c r="R78" t="n">
-        <v>7477939</v>
+        <v>7477887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8637,12 +8631,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8661,10 +8661,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855333</v>
+        <v>124855424</v>
       </c>
       <c r="B79" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8673,25 +8673,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854924</v>
+        <v>854780</v>
       </c>
       <c r="R79" t="n">
-        <v>7478087</v>
+        <v>7477939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855469</v>
+        <v>124855423</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854979</v>
+        <v>854915</v>
       </c>
       <c r="R81" t="n">
-        <v>7477885</v>
+        <v>7477851</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855380</v>
+        <v>124855469</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854745</v>
+        <v>854979</v>
       </c>
       <c r="R82" t="n">
-        <v>7477946</v>
+        <v>7477885</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9056,7 +9056,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9075,7 +9074,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855423</v>
+        <v>124855380</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9115,10 +9114,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854915</v>
+        <v>854745</v>
       </c>
       <c r="R83" t="n">
-        <v>7477851</v>
+        <v>7477946</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,6 +9158,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10825,7 +10825,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855421</v>
+        <v>124855358</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10861,14 +10861,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854951</v>
+        <v>854772</v>
       </c>
       <c r="R100" t="n">
-        <v>7477899</v>
+        <v>7477881</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10903,12 +10903,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10927,7 +10933,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855358</v>
+        <v>124855421</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10963,14 +10969,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854772</v>
+        <v>854951</v>
       </c>
       <c r="R101" t="n">
-        <v>7477881</v>
+        <v>7477899</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11005,18 +11011,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855316</v>
+        <v>124855318</v>
       </c>
       <c r="B105" t="n">
         <v>96985</v>
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855019</v>
+        <v>854817</v>
       </c>
       <c r="R105" t="n">
-        <v>7477888</v>
+        <v>7477931</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855318</v>
+        <v>124855316</v>
       </c>
       <c r="B106" t="n">
         <v>96985</v>
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854817</v>
+        <v>855019</v>
       </c>
       <c r="R106" t="n">
-        <v>7477931</v>
+        <v>7477888</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11652,10 +11652,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855231</v>
+        <v>124855359</v>
       </c>
       <c r="B108" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11664,38 +11664,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854954</v>
+        <v>854838</v>
       </c>
       <c r="R108" t="n">
-        <v>7478125</v>
+        <v>7477840</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11730,12 +11730,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11754,10 +11760,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855359</v>
+        <v>124855231</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11766,38 +11772,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854838</v>
+        <v>854954</v>
       </c>
       <c r="R109" t="n">
-        <v>7477840</v>
+        <v>7478125</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11832,18 +11838,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427352</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855059</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478173</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427406</v>
+        <v>124427354</v>
       </c>
       <c r="B37" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,45 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855096</v>
+        <v>855018</v>
       </c>
       <c r="R37" t="n">
-        <v>7478199</v>
+        <v>7478119</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,18 +4339,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4381,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427375</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,25 +4375,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4421,10 +4403,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>854922</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,8 +4447,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4483,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427346</v>
+        <v>124427399</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,38 +4493,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855044</v>
+        <v>855007</v>
       </c>
       <c r="R39" t="n">
-        <v>7478074</v>
+        <v>7478357</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,10 +4583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427356</v>
+        <v>124427393</v>
       </c>
       <c r="B40" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,38 +4595,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854977</v>
+        <v>854990</v>
       </c>
       <c r="R40" t="n">
-        <v>7478167</v>
+        <v>7478363</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4687,7 +4685,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427375</v>
+        <v>124427345</v>
       </c>
       <c r="B41" t="n">
         <v>79927</v>
@@ -4723,14 +4721,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854922</v>
+        <v>854967</v>
       </c>
       <c r="R41" t="n">
-        <v>7478323</v>
+        <v>7478177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,24 +4769,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4805,10 +4787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427389</v>
+        <v>124427398</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,42 +4799,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855110</v>
+        <v>855100</v>
       </c>
       <c r="R42" t="n">
-        <v>7478072</v>
+        <v>7478058</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,7 +4871,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4912,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427399</v>
+        <v>124427406</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,38 +4901,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855007</v>
+        <v>855096</v>
       </c>
       <c r="R43" t="n">
-        <v>7478357</v>
+        <v>7478199</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,12 +4974,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427347</v>
+        <v>124427403</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>79826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,34 +5020,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855063</v>
+        <v>854946</v>
       </c>
       <c r="R44" t="n">
-        <v>7478044</v>
+        <v>7478367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5098,6 +5088,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5116,10 +5107,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427398</v>
+        <v>124427365</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,21 +5123,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5147,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855100</v>
+        <v>854939</v>
       </c>
       <c r="R45" t="n">
-        <v>7478058</v>
+        <v>7478324</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,7 +5209,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427387</v>
+        <v>124427391</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5253,7 +5244,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5262,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855102</v>
+        <v>855091</v>
       </c>
       <c r="R46" t="n">
-        <v>7478191</v>
+        <v>7478207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,10 +5423,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427365</v>
+        <v>124427386</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,38 +5435,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854939</v>
+        <v>855066</v>
       </c>
       <c r="R48" t="n">
-        <v>7478324</v>
+        <v>7478180</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5516,6 +5511,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5534,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427389</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,38 +5542,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>855110</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5618,6 +5618,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427386</v>
+        <v>124427347</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,42 +5751,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855066</v>
+        <v>855063</v>
       </c>
       <c r="R51" t="n">
-        <v>7478180</v>
+        <v>7478044</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5826,7 +5823,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5845,7 +5841,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427345</v>
+        <v>124427346</v>
       </c>
       <c r="B52" t="n">
         <v>79927</v>
@@ -5885,10 +5881,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854967</v>
+        <v>855044</v>
       </c>
       <c r="R52" t="n">
-        <v>7478177</v>
+        <v>7478074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5947,10 +5943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427403</v>
+        <v>124427352</v>
       </c>
       <c r="B53" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5959,38 +5955,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854946</v>
+        <v>855059</v>
       </c>
       <c r="R53" t="n">
-        <v>7478367</v>
+        <v>7478173</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427393</v>
+        <v>124427356</v>
       </c>
       <c r="B54" t="n">
-        <v>56714</v>
+        <v>79926</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6062,38 +6062,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854990</v>
+        <v>854977</v>
       </c>
       <c r="R54" t="n">
-        <v>7478363</v>
+        <v>7478167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427391</v>
+        <v>124427351</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6187,19 +6187,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855091</v>
+        <v>855056</v>
       </c>
       <c r="R55" t="n">
-        <v>7478207</v>
+        <v>7478165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427351</v>
+        <v>124427387</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6294,19 +6294,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855056</v>
+        <v>855102</v>
       </c>
       <c r="R56" t="n">
-        <v>7478165</v>
+        <v>7478191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855371</v>
+        <v>124855318</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,42 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854845</v>
+        <v>854817</v>
       </c>
       <c r="R57" t="n">
-        <v>7477869</v>
+        <v>7477931</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6454,7 +6450,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6473,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855468</v>
+        <v>124854791</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6485,38 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855069</v>
+        <v>854840</v>
       </c>
       <c r="R58" t="n">
-        <v>7477999</v>
+        <v>7477716</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6543,12 +6538,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6575,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855313</v>
+        <v>124855482</v>
       </c>
       <c r="B59" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6591,21 +6586,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854814</v>
+        <v>855134</v>
       </c>
       <c r="R59" t="n">
-        <v>7477852</v>
+        <v>7477890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855475</v>
+        <v>124855420</v>
       </c>
       <c r="B60" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,25 +6684,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854813</v>
+        <v>855071</v>
       </c>
       <c r="R60" t="n">
-        <v>7477923</v>
+        <v>7477912</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855474</v>
+        <v>124855415</v>
       </c>
       <c r="B61" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6791,25 +6786,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855065</v>
+        <v>854928</v>
       </c>
       <c r="R61" t="n">
-        <v>7478197</v>
+        <v>7478107</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6876,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855536</v>
+        <v>124855358</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6888,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854869</v>
+        <v>854772</v>
       </c>
       <c r="R62" t="n">
-        <v>7477778</v>
+        <v>7477881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,17 +6946,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6970,6 +6965,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6988,10 +6984,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855275</v>
+        <v>124855316</v>
       </c>
       <c r="B63" t="n">
-        <v>92321</v>
+        <v>96985</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7000,38 +6996,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854889</v>
+        <v>855019</v>
       </c>
       <c r="R63" t="n">
-        <v>7477847</v>
+        <v>7477888</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7090,10 +7086,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855250</v>
+        <v>124855330</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>56725</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,38 +7098,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854814</v>
+        <v>854676</v>
       </c>
       <c r="R64" t="n">
-        <v>7477852</v>
+        <v>7477840</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,6 +7170,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7192,10 +7201,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855390</v>
+        <v>124855328</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7204,42 +7213,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854899</v>
+        <v>854802</v>
       </c>
       <c r="R65" t="n">
-        <v>7477831</v>
+        <v>7477769</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7266,12 +7271,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7280,7 +7290,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7401,7 +7410,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855404</v>
+        <v>124855381</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7434,21 +7443,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854832</v>
+        <v>854803</v>
       </c>
       <c r="R67" t="n">
-        <v>7477880</v>
+        <v>7477930</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,7 +7513,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855366</v>
+        <v>124855389</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7543,7 +7548,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7552,10 +7557,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854807</v>
+        <v>854906</v>
       </c>
       <c r="R68" t="n">
-        <v>7477926</v>
+        <v>7477891</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7615,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855317</v>
+        <v>124855376</v>
       </c>
       <c r="B69" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,38 +7632,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854783</v>
+        <v>854741</v>
       </c>
       <c r="R69" t="n">
-        <v>7477935</v>
+        <v>7477958</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7699,6 +7708,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7717,10 +7727,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855240</v>
+        <v>124855359</v>
       </c>
       <c r="B70" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7729,38 +7739,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854937</v>
+        <v>854838</v>
       </c>
       <c r="R70" t="n">
-        <v>7477782</v>
+        <v>7477840</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7787,12 +7797,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7801,6 +7816,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7819,10 +7835,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855394</v>
+        <v>124855244</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7831,42 +7847,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854897</v>
+        <v>855187</v>
       </c>
       <c r="R71" t="n">
-        <v>7477846</v>
+        <v>7478029</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7907,7 +7919,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7926,7 +7937,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855389</v>
+        <v>124855394</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7961,7 +7972,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7970,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854906</v>
+        <v>854897</v>
       </c>
       <c r="R72" t="n">
-        <v>7477891</v>
+        <v>7477846</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8033,7 +8044,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855420</v>
+        <v>124855380</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8073,10 +8084,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855071</v>
+        <v>854745</v>
       </c>
       <c r="R73" t="n">
-        <v>7477912</v>
+        <v>7477946</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8117,6 +8128,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8135,10 +8147,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855329</v>
+        <v>124855464</v>
       </c>
       <c r="B74" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8147,38 +8159,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854676</v>
+        <v>854898</v>
       </c>
       <c r="R74" t="n">
-        <v>7477840</v>
+        <v>7478156</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8205,17 +8217,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8242,7 +8249,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855464</v>
+        <v>124855386</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8275,17 +8282,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854898</v>
+        <v>854810</v>
       </c>
       <c r="R75" t="n">
-        <v>7478156</v>
+        <v>7477930</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,6 +8337,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8344,10 +8356,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124854790</v>
+        <v>124855232</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8356,42 +8368,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854766</v>
+        <v>855094</v>
       </c>
       <c r="R76" t="n">
-        <v>7478012</v>
+        <v>7477931</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8432,7 +8440,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8451,10 +8458,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855333</v>
+        <v>124855483</v>
       </c>
       <c r="B77" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8463,25 +8470,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8498,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854924</v>
+        <v>855251</v>
       </c>
       <c r="R77" t="n">
-        <v>7478087</v>
+        <v>7478036</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8553,7 +8560,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855364</v>
+        <v>124855390</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8586,17 +8593,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855120</v>
+        <v>854899</v>
       </c>
       <c r="R78" t="n">
-        <v>7477887</v>
+        <v>7477831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8629,11 +8640,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8661,7 +8667,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855424</v>
+        <v>124855468</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8701,10 +8707,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854780</v>
+        <v>855069</v>
       </c>
       <c r="R79" t="n">
-        <v>7477939</v>
+        <v>7477999</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8763,10 +8769,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855376</v>
+        <v>124855277</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8775,42 +8781,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854741</v>
+        <v>855068</v>
       </c>
       <c r="R80" t="n">
-        <v>7477958</v>
+        <v>7478046</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8851,7 +8853,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8870,10 +8871,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855423</v>
+        <v>124855231</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8882,25 +8883,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8910,10 +8911,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854915</v>
+        <v>854954</v>
       </c>
       <c r="R81" t="n">
-        <v>7477851</v>
+        <v>7478125</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8972,7 +8973,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855469</v>
+        <v>124854790</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -9005,17 +9006,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854979</v>
+        <v>854766</v>
       </c>
       <c r="R82" t="n">
-        <v>7477885</v>
+        <v>7478012</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9056,6 +9061,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9074,7 +9080,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855380</v>
+        <v>124855469</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9114,10 +9120,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854745</v>
+        <v>854979</v>
       </c>
       <c r="R83" t="n">
-        <v>7477946</v>
+        <v>7477885</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9164,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9177,10 +9182,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855232</v>
+        <v>124855466</v>
       </c>
       <c r="B84" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9189,25 +9194,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9217,10 +9222,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855094</v>
+        <v>854921</v>
       </c>
       <c r="R84" t="n">
-        <v>7477931</v>
+        <v>7478082</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9279,7 +9284,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855467</v>
+        <v>124855404</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9312,17 +9317,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855062</v>
+        <v>854832</v>
       </c>
       <c r="R85" t="n">
-        <v>7478002</v>
+        <v>7477880</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9363,6 +9372,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9381,10 +9391,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855244</v>
+        <v>124855366</v>
       </c>
       <c r="B86" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9393,38 +9403,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855187</v>
+        <v>854807</v>
       </c>
       <c r="R86" t="n">
-        <v>7478029</v>
+        <v>7477926</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9465,6 +9479,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9483,10 +9498,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855417</v>
+        <v>124855250</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9495,25 +9510,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9523,10 +9538,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855202</v>
+        <v>854814</v>
       </c>
       <c r="R87" t="n">
-        <v>7477976</v>
+        <v>7477852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9585,10 +9600,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855483</v>
+        <v>124855475</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9601,21 +9616,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9625,10 +9640,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855251</v>
+        <v>854813</v>
       </c>
       <c r="R88" t="n">
-        <v>7478036</v>
+        <v>7477923</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9687,7 +9702,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855233</v>
+        <v>124855240</v>
       </c>
       <c r="B89" t="n">
         <v>105102</v>
@@ -9727,10 +9742,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855073</v>
+        <v>854937</v>
       </c>
       <c r="R89" t="n">
-        <v>7477920</v>
+        <v>7477782</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9757,12 +9772,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9789,10 +9804,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855524</v>
+        <v>124855333</v>
       </c>
       <c r="B90" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9805,21 +9820,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9829,10 +9844,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854793</v>
+        <v>854924</v>
       </c>
       <c r="R90" t="n">
-        <v>7477805</v>
+        <v>7478087</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9859,12 +9874,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9891,10 +9906,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855482</v>
+        <v>124855418</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9903,25 +9918,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9931,10 +9946,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855134</v>
+        <v>855131</v>
       </c>
       <c r="R91" t="n">
-        <v>7477890</v>
+        <v>7477924</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9993,10 +10008,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124854791</v>
+        <v>124855275</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>92321</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10009,21 +10024,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10033,10 +10048,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854840</v>
+        <v>854889</v>
       </c>
       <c r="R92" t="n">
-        <v>7477716</v>
+        <v>7477847</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10063,12 +10078,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10095,10 +10110,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855418</v>
+        <v>124855536</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10107,25 +10122,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10135,10 +10150,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855131</v>
+        <v>854869</v>
       </c>
       <c r="R93" t="n">
-        <v>7477924</v>
+        <v>7477778</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10165,12 +10180,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10197,10 +10217,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855381</v>
+        <v>124855317</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10209,25 +10229,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10237,10 +10257,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854803</v>
+        <v>854783</v>
       </c>
       <c r="R94" t="n">
-        <v>7477930</v>
+        <v>7477935</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10281,7 +10301,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10300,10 +10319,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855500</v>
+        <v>124855421</v>
       </c>
       <c r="B95" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10312,25 +10331,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10340,10 +10359,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854850</v>
+        <v>854951</v>
       </c>
       <c r="R95" t="n">
-        <v>7477915</v>
+        <v>7477899</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10402,10 +10421,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855512</v>
+        <v>124855364</v>
       </c>
       <c r="B96" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10414,38 +10433,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854911</v>
+        <v>855120</v>
       </c>
       <c r="R96" t="n">
-        <v>7478164</v>
+        <v>7477887</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10480,12 +10499,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10504,10 +10529,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855328</v>
+        <v>124855512</v>
       </c>
       <c r="B97" t="n">
-        <v>56725</v>
+        <v>79926</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10520,34 +10545,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102613</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854802</v>
+        <v>854911</v>
       </c>
       <c r="R97" t="n">
-        <v>7477769</v>
+        <v>7478164</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10574,17 +10599,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10611,10 +10631,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855401</v>
+        <v>124855257</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10623,42 +10643,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854928</v>
+        <v>854894</v>
       </c>
       <c r="R98" t="n">
-        <v>7477769</v>
+        <v>7477768</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10693,13 +10709,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10718,10 +10738,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855257</v>
+        <v>124855371</v>
       </c>
       <c r="B99" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10730,38 +10750,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854894</v>
+        <v>854845</v>
       </c>
       <c r="R99" t="n">
-        <v>7477768</v>
+        <v>7477869</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10788,17 +10812,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10807,6 +10826,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10825,10 +10845,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855358</v>
+        <v>124855474</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10837,38 +10857,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854772</v>
+        <v>855065</v>
       </c>
       <c r="R100" t="n">
-        <v>7477881</v>
+        <v>7478197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10903,18 +10923,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10933,7 +10947,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855421</v>
+        <v>124855401</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10966,17 +10980,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854951</v>
+        <v>854928</v>
       </c>
       <c r="R101" t="n">
-        <v>7477899</v>
+        <v>7477769</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11003,12 +11021,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11017,6 +11035,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11035,7 +11054,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855386</v>
+        <v>124855467</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11068,21 +11087,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854810</v>
+        <v>855062</v>
       </c>
       <c r="R102" t="n">
-        <v>7477930</v>
+        <v>7478002</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,7 +11138,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11142,7 +11156,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855466</v>
+        <v>124855424</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11182,10 +11196,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854921</v>
+        <v>854780</v>
       </c>
       <c r="R103" t="n">
-        <v>7478082</v>
+        <v>7477939</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11244,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855415</v>
+        <v>124855423</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11284,10 +11298,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854928</v>
+        <v>854915</v>
       </c>
       <c r="R104" t="n">
-        <v>7478107</v>
+        <v>7477851</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11346,10 +11360,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855318</v>
+        <v>124855233</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11362,21 +11376,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11386,10 +11400,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854817</v>
+        <v>855073</v>
       </c>
       <c r="R105" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11448,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855316</v>
+        <v>124855313</v>
       </c>
       <c r="B106" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11460,25 +11474,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11488,10 +11502,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855019</v>
+        <v>854814</v>
       </c>
       <c r="R106" t="n">
-        <v>7477888</v>
+        <v>7477852</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11550,10 +11564,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855277</v>
+        <v>124855500</v>
       </c>
       <c r="B107" t="n">
-        <v>79920</v>
+        <v>79826</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11566,21 +11580,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11590,10 +11604,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>855068</v>
+        <v>854850</v>
       </c>
       <c r="R107" t="n">
-        <v>7478046</v>
+        <v>7477915</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11652,10 +11666,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855359</v>
+        <v>124855524</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11664,38 +11678,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854838</v>
+        <v>854793</v>
       </c>
       <c r="R108" t="n">
-        <v>7477840</v>
+        <v>7477805</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11722,17 +11736,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11741,7 +11750,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11760,10 +11768,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855231</v>
+        <v>124855417</v>
       </c>
       <c r="B109" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11772,25 +11780,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11808,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854954</v>
+        <v>855202</v>
       </c>
       <c r="R109" t="n">
-        <v>7478125</v>
+        <v>7477976</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427369</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>57793</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>854943</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427354</v>
+        <v>124427393</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>56828</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,34 +4277,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855018</v>
+        <v>854990</v>
       </c>
       <c r="R37" t="n">
-        <v>7478119</v>
+        <v>7478363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427375</v>
+        <v>124427386</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4375,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854922</v>
+        <v>855066</v>
       </c>
       <c r="R38" t="n">
-        <v>7478323</v>
+        <v>7478180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,21 +4454,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4481,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427399</v>
+        <v>124427401</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>82737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4497,21 +4486,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4510,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855007</v>
+        <v>855011</v>
       </c>
       <c r="R39" t="n">
-        <v>7478357</v>
+        <v>7478352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4583,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427393</v>
+        <v>124427346</v>
       </c>
       <c r="B40" t="n">
-        <v>56714</v>
+        <v>80064</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,38 +4584,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854990</v>
+        <v>855044</v>
       </c>
       <c r="R40" t="n">
-        <v>7478363</v>
+        <v>7478074</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,10 +4674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427345</v>
+        <v>124427347</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,10 +4714,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854967</v>
+        <v>855063</v>
       </c>
       <c r="R41" t="n">
-        <v>7478177</v>
+        <v>7478044</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4787,10 +4776,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427398</v>
+        <v>124427387</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4799,38 +4788,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855100</v>
+        <v>855102</v>
       </c>
       <c r="R42" t="n">
-        <v>7478058</v>
+        <v>7478191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4864,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4892,7 +4886,7 @@
         <v>124427406</v>
       </c>
       <c r="B43" t="n">
-        <v>91579</v>
+        <v>91737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5004,10 +4998,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427403</v>
+        <v>124427398</v>
       </c>
       <c r="B44" t="n">
-        <v>79826</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5016,25 +5010,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5044,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854946</v>
+        <v>855100</v>
       </c>
       <c r="R44" t="n">
-        <v>7478367</v>
+        <v>7478058</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5088,7 +5082,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5107,10 +5100,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427365</v>
+        <v>124427356</v>
       </c>
       <c r="B45" t="n">
-        <v>79428</v>
+        <v>80063</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5119,38 +5112,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854939</v>
+        <v>854977</v>
       </c>
       <c r="R45" t="n">
-        <v>7478324</v>
+        <v>7478167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,10 +5202,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427391</v>
+        <v>124427365</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79565</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5221,42 +5214,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855091</v>
+        <v>854939</v>
       </c>
       <c r="R46" t="n">
-        <v>7478207</v>
+        <v>7478324</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,7 +5286,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5319,7 +5307,7 @@
         <v>124427388</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5423,10 +5411,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427386</v>
+        <v>124427389</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5458,7 +5446,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5467,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855066</v>
+        <v>855110</v>
       </c>
       <c r="R48" t="n">
-        <v>7478180</v>
+        <v>7478072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427389</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5542,42 +5530,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855110</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478072</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5618,7 +5602,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5637,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427369</v>
+        <v>124427352</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5649,38 +5632,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854943</v>
+        <v>855059</v>
       </c>
       <c r="R50" t="n">
-        <v>7478362</v>
+        <v>7478173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5721,6 +5708,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5739,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427347</v>
+        <v>124427391</v>
       </c>
       <c r="B51" t="n">
-        <v>79927</v>
+        <v>98269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5751,38 +5739,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R51" t="n">
-        <v>7478044</v>
+        <v>7478207</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5823,6 +5815,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427346</v>
+        <v>124427375</v>
       </c>
       <c r="B52" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5877,14 +5870,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855044</v>
+        <v>854922</v>
       </c>
       <c r="R52" t="n">
-        <v>7478074</v>
+        <v>7478323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,8 +5918,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -5943,10 +5952,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427352</v>
+        <v>124427351</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5978,7 +5987,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5987,10 +5996,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855059</v>
+        <v>855056</v>
       </c>
       <c r="R53" t="n">
-        <v>7478173</v>
+        <v>7478165</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6050,10 +6059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427356</v>
+        <v>124427399</v>
       </c>
       <c r="B54" t="n">
-        <v>79926</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6062,20 +6071,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6086,14 +6095,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854977</v>
+        <v>855007</v>
       </c>
       <c r="R54" t="n">
-        <v>7478167</v>
+        <v>7478357</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6152,10 +6161,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427351</v>
+        <v>124427345</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>80064</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,42 +6173,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855056</v>
+        <v>854967</v>
       </c>
       <c r="R55" t="n">
-        <v>7478165</v>
+        <v>7478177</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6240,7 +6245,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6259,10 +6263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427387</v>
+        <v>124427403</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79963</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,42 +6275,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855102</v>
+        <v>854946</v>
       </c>
       <c r="R56" t="n">
-        <v>7478191</v>
+        <v>7478367</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855318</v>
+        <v>124855475</v>
       </c>
       <c r="B57" t="n">
-        <v>96985</v>
+        <v>56828</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,25 +6378,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854817</v>
+        <v>854813</v>
       </c>
       <c r="R57" t="n">
-        <v>7477931</v>
+        <v>7477923</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124854791</v>
+        <v>124855423</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854840</v>
+        <v>854915</v>
       </c>
       <c r="R58" t="n">
-        <v>7477716</v>
+        <v>7477851</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6538,12 +6538,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855482</v>
+        <v>124854791</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6606,14 +6606,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855134</v>
+        <v>854840</v>
       </c>
       <c r="R59" t="n">
-        <v>7477890</v>
+        <v>7477716</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6672,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855420</v>
+        <v>124855328</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>56839</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,38 +6684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855071</v>
+        <v>854802</v>
       </c>
       <c r="R60" t="n">
-        <v>7477912</v>
+        <v>7477769</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6742,12 +6742,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6774,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855415</v>
+        <v>124855420</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854928</v>
+        <v>855071</v>
       </c>
       <c r="R61" t="n">
-        <v>7478107</v>
+        <v>7477912</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855358</v>
+        <v>124855233</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>105278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6888,38 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854772</v>
+        <v>855073</v>
       </c>
       <c r="R62" t="n">
-        <v>7477881</v>
+        <v>7477920</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6954,18 +6959,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6984,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855316</v>
+        <v>124855330</v>
       </c>
       <c r="B63" t="n">
-        <v>96985</v>
+        <v>56839</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7000,34 +6999,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855019</v>
+        <v>854676</v>
       </c>
       <c r="R63" t="n">
-        <v>7477888</v>
+        <v>7477840</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7060,6 +7067,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7086,10 +7098,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855330</v>
+        <v>124855316</v>
       </c>
       <c r="B64" t="n">
-        <v>56725</v>
+        <v>97153</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,42 +7114,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102613</v>
+        <v>221941</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854676</v>
+        <v>855019</v>
       </c>
       <c r="R64" t="n">
-        <v>7477840</v>
+        <v>7477888</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7170,11 +7174,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7201,10 +7200,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855328</v>
+        <v>124855483</v>
       </c>
       <c r="B65" t="n">
-        <v>56725</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7213,38 +7212,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854802</v>
+        <v>855251</v>
       </c>
       <c r="R65" t="n">
-        <v>7477769</v>
+        <v>7478036</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7271,17 +7270,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7308,10 +7302,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855416</v>
+        <v>124855232</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>105278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7320,25 +7314,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7348,10 +7342,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855002</v>
+        <v>855094</v>
       </c>
       <c r="R66" t="n">
-        <v>7478149</v>
+        <v>7477931</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7410,10 +7404,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855381</v>
+        <v>124855386</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7443,14 +7437,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854803</v>
+        <v>854810</v>
       </c>
       <c r="R67" t="n">
         <v>7477930</v>
@@ -7513,10 +7511,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855389</v>
+        <v>124855466</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7546,21 +7544,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854906</v>
+        <v>854921</v>
       </c>
       <c r="R68" t="n">
-        <v>7477891</v>
+        <v>7478082</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7601,7 +7595,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7620,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855376</v>
+        <v>124855464</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7653,21 +7646,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854741</v>
+        <v>854898</v>
       </c>
       <c r="R69" t="n">
-        <v>7477958</v>
+        <v>7478156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7708,7 +7697,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7727,10 +7715,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855359</v>
+        <v>124855390</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7760,17 +7748,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854838</v>
+        <v>854899</v>
       </c>
       <c r="R70" t="n">
-        <v>7477840</v>
+        <v>7477831</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7803,11 +7795,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7835,10 +7822,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855244</v>
+        <v>124855512</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>80063</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7847,25 +7834,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7875,10 +7862,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855187</v>
+        <v>854911</v>
       </c>
       <c r="R71" t="n">
-        <v>7478029</v>
+        <v>7478164</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7937,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855394</v>
+        <v>124855424</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7970,21 +7957,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854897</v>
+        <v>854780</v>
       </c>
       <c r="R72" t="n">
-        <v>7477846</v>
+        <v>7477939</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8025,7 +8008,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8044,10 +8026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855380</v>
+        <v>124855381</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8084,10 +8066,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854745</v>
+        <v>854803</v>
       </c>
       <c r="R73" t="n">
-        <v>7477946</v>
+        <v>7477930</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8147,10 +8129,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855464</v>
+        <v>124855358</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8183,14 +8165,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854898</v>
+        <v>854772</v>
       </c>
       <c r="R74" t="n">
-        <v>7478156</v>
+        <v>7477881</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,12 +8207,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8249,10 +8237,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855386</v>
+        <v>124855524</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>80063</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8261,42 +8249,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854810</v>
+        <v>854793</v>
       </c>
       <c r="R75" t="n">
-        <v>7477930</v>
+        <v>7477805</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8323,12 +8307,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8337,7 +8321,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8356,10 +8339,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855232</v>
+        <v>124855257</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>57635</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8368,25 +8351,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8396,10 +8379,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855094</v>
+        <v>854894</v>
       </c>
       <c r="R76" t="n">
-        <v>7477931</v>
+        <v>7477768</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8426,12 +8409,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8458,10 +8446,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855483</v>
+        <v>124855359</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8470,38 +8458,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855251</v>
+        <v>854838</v>
       </c>
       <c r="R77" t="n">
-        <v>7478036</v>
+        <v>7477840</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8536,12 +8524,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8560,10 +8554,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855390</v>
+        <v>124855418</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8593,21 +8587,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854899</v>
+        <v>855131</v>
       </c>
       <c r="R78" t="n">
-        <v>7477831</v>
+        <v>7477924</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8648,7 +8638,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8667,10 +8656,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855468</v>
+        <v>124855401</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8700,17 +8689,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855069</v>
+        <v>854928</v>
       </c>
       <c r="R79" t="n">
-        <v>7477999</v>
+        <v>7477769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8737,12 +8730,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8751,6 +8744,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8769,10 +8763,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855277</v>
+        <v>124855417</v>
       </c>
       <c r="B80" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8781,25 +8775,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8809,10 +8803,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855068</v>
+        <v>855202</v>
       </c>
       <c r="R80" t="n">
-        <v>7478046</v>
+        <v>7477976</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8871,10 +8865,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855231</v>
+        <v>124855240</v>
       </c>
       <c r="B81" t="n">
-        <v>105102</v>
+        <v>105278</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8911,10 +8905,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854954</v>
+        <v>854937</v>
       </c>
       <c r="R81" t="n">
-        <v>7478125</v>
+        <v>7477782</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8941,12 +8935,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8973,10 +8967,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124854790</v>
+        <v>124855244</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8985,42 +8979,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854766</v>
+        <v>855187</v>
       </c>
       <c r="R82" t="n">
-        <v>7478012</v>
+        <v>7478029</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9061,7 +9051,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9080,10 +9069,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855469</v>
+        <v>124855275</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>92476</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9092,38 +9081,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854979</v>
+        <v>854889</v>
       </c>
       <c r="R83" t="n">
-        <v>7477885</v>
+        <v>7477847</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9182,10 +9171,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855466</v>
+        <v>124855317</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>97153</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9194,25 +9183,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9222,10 +9211,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854921</v>
+        <v>854783</v>
       </c>
       <c r="R84" t="n">
-        <v>7478082</v>
+        <v>7477935</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9284,10 +9273,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855404</v>
+        <v>124855364</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9317,21 +9306,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854832</v>
+        <v>855120</v>
       </c>
       <c r="R85" t="n">
-        <v>7477880</v>
+        <v>7477887</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9364,6 +9349,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9391,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855366</v>
+        <v>124855404</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9426,7 +9416,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9435,10 +9425,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854807</v>
+        <v>854832</v>
       </c>
       <c r="R86" t="n">
-        <v>7477926</v>
+        <v>7477880</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9498,10 +9488,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855250</v>
+        <v>124855366</v>
       </c>
       <c r="B87" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9510,38 +9500,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854814</v>
+        <v>854807</v>
       </c>
       <c r="R87" t="n">
-        <v>7477852</v>
+        <v>7477926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9582,6 +9576,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9600,10 +9595,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855475</v>
+        <v>124855250</v>
       </c>
       <c r="B88" t="n">
-        <v>56714</v>
+        <v>91166</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9616,21 +9611,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9640,10 +9635,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854813</v>
+        <v>854814</v>
       </c>
       <c r="R88" t="n">
-        <v>7477923</v>
+        <v>7477852</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9702,10 +9697,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855240</v>
+        <v>124855482</v>
       </c>
       <c r="B89" t="n">
-        <v>105102</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9714,25 +9709,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9742,10 +9737,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854937</v>
+        <v>855134</v>
       </c>
       <c r="R89" t="n">
-        <v>7477782</v>
+        <v>7477890</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9772,12 +9767,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9804,10 +9799,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855333</v>
+        <v>124855416</v>
       </c>
       <c r="B90" t="n">
-        <v>79927</v>
+        <v>98269</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9816,25 +9811,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9844,10 +9839,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854924</v>
+        <v>855002</v>
       </c>
       <c r="R90" t="n">
-        <v>7478087</v>
+        <v>7478149</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9906,10 +9901,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855418</v>
+        <v>124854790</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9939,17 +9934,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855131</v>
+        <v>854766</v>
       </c>
       <c r="R91" t="n">
-        <v>7477924</v>
+        <v>7478012</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9990,6 +9989,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855275</v>
+        <v>124855389</v>
       </c>
       <c r="B92" t="n">
-        <v>92321</v>
+        <v>98269</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10020,38 +10020,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854889</v>
+        <v>854906</v>
       </c>
       <c r="R92" t="n">
-        <v>7477847</v>
+        <v>7477891</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10092,6 +10096,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10110,10 +10115,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855536</v>
+        <v>124855318</v>
       </c>
       <c r="B93" t="n">
-        <v>57529</v>
+        <v>97153</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10122,25 +10127,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10150,10 +10155,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854869</v>
+        <v>854817</v>
       </c>
       <c r="R93" t="n">
-        <v>7477778</v>
+        <v>7477931</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10180,17 +10185,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10217,10 +10217,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855317</v>
+        <v>124855380</v>
       </c>
       <c r="B94" t="n">
-        <v>96985</v>
+        <v>98269</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10229,25 +10229,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854783</v>
+        <v>854745</v>
       </c>
       <c r="R94" t="n">
-        <v>7477935</v>
+        <v>7477946</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10301,6 +10301,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10319,10 +10320,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855421</v>
+        <v>124855376</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10352,17 +10353,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854951</v>
+        <v>854741</v>
       </c>
       <c r="R95" t="n">
-        <v>7477899</v>
+        <v>7477958</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10403,6 +10408,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10421,10 +10427,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855364</v>
+        <v>124855313</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10433,38 +10439,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855120</v>
+        <v>854814</v>
       </c>
       <c r="R96" t="n">
-        <v>7477887</v>
+        <v>7477852</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10499,18 +10505,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10529,10 +10529,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855512</v>
+        <v>124855415</v>
       </c>
       <c r="B97" t="n">
-        <v>79926</v>
+        <v>98269</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10541,25 +10541,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10569,10 +10569,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854911</v>
+        <v>854928</v>
       </c>
       <c r="R97" t="n">
-        <v>7478164</v>
+        <v>7478107</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855257</v>
+        <v>124855277</v>
       </c>
       <c r="B98" t="n">
-        <v>57513</v>
+        <v>80057</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10643,25 +10643,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854894</v>
+        <v>855068</v>
       </c>
       <c r="R98" t="n">
-        <v>7477768</v>
+        <v>7478046</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10701,17 +10701,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10741,7 +10736,7 @@
         <v>124855371</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10845,10 +10840,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855474</v>
+        <v>124855421</v>
       </c>
       <c r="B100" t="n">
-        <v>56714</v>
+        <v>98269</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10857,25 +10852,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10885,10 +10880,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855065</v>
+        <v>854951</v>
       </c>
       <c r="R100" t="n">
-        <v>7478197</v>
+        <v>7477899</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10947,10 +10942,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855401</v>
+        <v>124855394</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10982,7 +10977,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10991,10 +10986,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854928</v>
+        <v>854897</v>
       </c>
       <c r="R101" t="n">
-        <v>7477769</v>
+        <v>7477846</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11021,12 +11016,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11054,10 +11049,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855467</v>
+        <v>124855536</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11066,25 +11061,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11094,10 +11089,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855062</v>
+        <v>854869</v>
       </c>
       <c r="R102" t="n">
-        <v>7478002</v>
+        <v>7477778</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11124,12 +11119,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11156,10 +11156,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855424</v>
+        <v>124855467</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854780</v>
+        <v>855062</v>
       </c>
       <c r="R103" t="n">
-        <v>7477939</v>
+        <v>7478002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855423</v>
+        <v>124855333</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>80064</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11270,25 +11270,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854915</v>
+        <v>854924</v>
       </c>
       <c r="R104" t="n">
-        <v>7477851</v>
+        <v>7478087</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11360,10 +11360,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855233</v>
+        <v>124855474</v>
       </c>
       <c r="B105" t="n">
-        <v>105102</v>
+        <v>56828</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11372,25 +11372,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855073</v>
+        <v>855065</v>
       </c>
       <c r="R105" t="n">
-        <v>7477920</v>
+        <v>7478197</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855313</v>
+        <v>124855500</v>
       </c>
       <c r="B106" t="n">
-        <v>91299</v>
+        <v>79963</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11474,25 +11474,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854814</v>
+        <v>854850</v>
       </c>
       <c r="R106" t="n">
-        <v>7477852</v>
+        <v>7477915</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11564,10 +11564,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855500</v>
+        <v>124855231</v>
       </c>
       <c r="B107" t="n">
-        <v>79826</v>
+        <v>105278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11580,21 +11580,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6457</v>
+        <v>221725</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854850</v>
+        <v>854954</v>
       </c>
       <c r="R107" t="n">
-        <v>7477915</v>
+        <v>7478125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855524</v>
+        <v>124855469</v>
       </c>
       <c r="B108" t="n">
-        <v>79926</v>
+        <v>98269</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11678,25 +11678,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854793</v>
+        <v>854979</v>
       </c>
       <c r="R108" t="n">
-        <v>7477805</v>
+        <v>7477885</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11768,10 +11768,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855417</v>
+        <v>124855468</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11808,10 +11808,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855202</v>
+        <v>855069</v>
       </c>
       <c r="R109" t="n">
-        <v>7477976</v>
+        <v>7477999</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B39" t="n">
-        <v>82737</v>
+        <v>80064</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4482,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R39" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427346</v>
+        <v>124427401</v>
       </c>
       <c r="B40" t="n">
-        <v>80064</v>
+        <v>82737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,38 +4584,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855044</v>
+        <v>855011</v>
       </c>
       <c r="R40" t="n">
-        <v>7478074</v>
+        <v>7478352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855244</v>
+        <v>124855275</v>
       </c>
       <c r="B82" t="n">
-        <v>91166</v>
+        <v>92476</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8983,34 +8983,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855187</v>
+        <v>854889</v>
       </c>
       <c r="R82" t="n">
-        <v>7478029</v>
+        <v>7477847</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855275</v>
+        <v>124855364</v>
       </c>
       <c r="B83" t="n">
-        <v>92476</v>
+        <v>98269</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854889</v>
+        <v>855120</v>
       </c>
       <c r="R83" t="n">
-        <v>7477847</v>
+        <v>7477887</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9147,12 +9147,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9171,10 +9177,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855317</v>
+        <v>124855404</v>
       </c>
       <c r="B84" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9183,38 +9189,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854783</v>
+        <v>854832</v>
       </c>
       <c r="R84" t="n">
-        <v>7477935</v>
+        <v>7477880</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9255,6 +9265,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9273,7 +9284,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855364</v>
+        <v>124855366</v>
       </c>
       <c r="B85" t="n">
         <v>98269</v>
@@ -9306,17 +9317,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855120</v>
+        <v>854807</v>
       </c>
       <c r="R85" t="n">
-        <v>7477887</v>
+        <v>7477926</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9349,11 +9364,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9381,10 +9391,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855404</v>
+        <v>124855244</v>
       </c>
       <c r="B86" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9393,42 +9403,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854832</v>
+        <v>855187</v>
       </c>
       <c r="R86" t="n">
-        <v>7477880</v>
+        <v>7478029</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9469,7 +9475,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9488,10 +9493,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855366</v>
+        <v>124855317</v>
       </c>
       <c r="B87" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9500,42 +9505,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854807</v>
+        <v>854783</v>
       </c>
       <c r="R87" t="n">
-        <v>7477926</v>
+        <v>7477935</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9576,7 +9577,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9595,10 +9595,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855250</v>
+        <v>124855482</v>
       </c>
       <c r="B88" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9611,21 +9611,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9635,10 +9635,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854814</v>
+        <v>855134</v>
       </c>
       <c r="R88" t="n">
-        <v>7477852</v>
+        <v>7477890</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855482</v>
+        <v>124855416</v>
       </c>
       <c r="B89" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9709,25 +9709,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855134</v>
+        <v>855002</v>
       </c>
       <c r="R89" t="n">
-        <v>7477890</v>
+        <v>7478149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9799,7 +9799,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855416</v>
+        <v>124854790</v>
       </c>
       <c r="B90" t="n">
         <v>98269</v>
@@ -9832,17 +9832,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855002</v>
+        <v>854766</v>
       </c>
       <c r="R90" t="n">
-        <v>7478149</v>
+        <v>7478012</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9883,6 +9887,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9901,7 +9906,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124854790</v>
+        <v>124855389</v>
       </c>
       <c r="B91" t="n">
         <v>98269</v>
@@ -9936,19 +9941,19 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854766</v>
+        <v>854906</v>
       </c>
       <c r="R91" t="n">
-        <v>7478012</v>
+        <v>7477891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10008,10 +10013,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855389</v>
+        <v>124855250</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10020,42 +10025,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854906</v>
+        <v>854814</v>
       </c>
       <c r="R92" t="n">
-        <v>7477891</v>
+        <v>7477852</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10096,7 +10097,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11156,10 +11156,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855467</v>
+        <v>124855333</v>
       </c>
       <c r="B103" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11168,25 +11168,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855062</v>
+        <v>854924</v>
       </c>
       <c r="R103" t="n">
-        <v>7478002</v>
+        <v>7478087</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855333</v>
+        <v>124855474</v>
       </c>
       <c r="B104" t="n">
-        <v>80064</v>
+        <v>56828</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11270,25 +11270,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854924</v>
+        <v>855065</v>
       </c>
       <c r="R104" t="n">
-        <v>7478087</v>
+        <v>7478197</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11360,10 +11360,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855474</v>
+        <v>124855467</v>
       </c>
       <c r="B105" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11372,25 +11372,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855065</v>
+        <v>855062</v>
       </c>
       <c r="R105" t="n">
-        <v>7478197</v>
+        <v>7478002</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427369</v>
+        <v>124427351</v>
       </c>
       <c r="B36" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854943</v>
+        <v>855056</v>
       </c>
       <c r="R36" t="n">
-        <v>7478362</v>
+        <v>7478165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B37" t="n">
-        <v>56828</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,34 +4282,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R37" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427386</v>
+        <v>124427389</v>
       </c>
       <c r="B38" t="n">
         <v>98269</v>
@@ -4398,7 +4403,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4407,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855066</v>
+        <v>855110</v>
       </c>
       <c r="R38" t="n">
-        <v>7478180</v>
+        <v>7478072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427346</v>
+        <v>124427369</v>
       </c>
       <c r="B39" t="n">
-        <v>80064</v>
+        <v>57793</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4487,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855044</v>
+        <v>854943</v>
       </c>
       <c r="R39" t="n">
-        <v>7478074</v>
+        <v>7478362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B40" t="n">
-        <v>82737</v>
+        <v>80064</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,38 +4589,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R40" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,7 +4679,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427347</v>
+        <v>124427375</v>
       </c>
       <c r="B41" t="n">
         <v>80064</v>
@@ -4710,14 +4715,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855063</v>
+        <v>854922</v>
       </c>
       <c r="R41" t="n">
-        <v>7478044</v>
+        <v>7478323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,8 +4763,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4776,10 +4797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427387</v>
+        <v>124427356</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4788,42 +4809,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855102</v>
+        <v>854977</v>
       </c>
       <c r="R42" t="n">
-        <v>7478191</v>
+        <v>7478167</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,7 +4881,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4883,10 +4899,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427406</v>
+        <v>124427391</v>
       </c>
       <c r="B43" t="n">
-        <v>91737</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4899,41 +4915,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855096</v>
+        <v>855091</v>
       </c>
       <c r="R43" t="n">
-        <v>7478199</v>
+        <v>7478207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4966,11 +4979,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4998,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427398</v>
+        <v>124427388</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5010,38 +5018,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855100</v>
+        <v>855074</v>
       </c>
       <c r="R44" t="n">
-        <v>7478058</v>
+        <v>7478164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5082,6 +5094,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5100,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427356</v>
+        <v>124427401</v>
       </c>
       <c r="B45" t="n">
-        <v>80063</v>
+        <v>82737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5112,38 +5125,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854977</v>
+        <v>855011</v>
       </c>
       <c r="R45" t="n">
-        <v>7478167</v>
+        <v>7478352</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427365</v>
+        <v>124427393</v>
       </c>
       <c r="B46" t="n">
-        <v>79565</v>
+        <v>56828</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5218,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5242,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854939</v>
+        <v>854990</v>
       </c>
       <c r="R46" t="n">
-        <v>7478324</v>
+        <v>7478363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5304,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427388</v>
+        <v>124427403</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>79963</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5316,42 +5329,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855074</v>
+        <v>854946</v>
       </c>
       <c r="R47" t="n">
-        <v>7478164</v>
+        <v>7478367</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5411,7 +5420,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427389</v>
+        <v>124427352</v>
       </c>
       <c r="B48" t="n">
         <v>98269</v>
@@ -5446,19 +5455,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855110</v>
+        <v>855059</v>
       </c>
       <c r="R48" t="n">
-        <v>7478072</v>
+        <v>7478173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,10 +5527,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427347</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
+        <v>80064</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,25 +5539,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5558,10 +5567,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>855063</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478044</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5620,10 +5629,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427352</v>
+        <v>124427365</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,42 +5641,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855059</v>
+        <v>854939</v>
       </c>
       <c r="R50" t="n">
-        <v>7478173</v>
+        <v>7478324</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,7 +5713,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5727,7 +5731,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427391</v>
+        <v>124427386</v>
       </c>
       <c r="B51" t="n">
         <v>98269</v>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5771,10 +5775,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855091</v>
+        <v>855066</v>
       </c>
       <c r="R51" t="n">
-        <v>7478207</v>
+        <v>7478180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5834,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427375</v>
+        <v>124427399</v>
       </c>
       <c r="B52" t="n">
-        <v>80064</v>
+        <v>78947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,25 +5850,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5874,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854922</v>
+        <v>855007</v>
       </c>
       <c r="R52" t="n">
-        <v>7478323</v>
+        <v>7478357</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5918,24 +5922,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -5952,10 +5940,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427351</v>
+        <v>124427398</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5964,42 +5952,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855056</v>
+        <v>855100</v>
       </c>
       <c r="R53" t="n">
-        <v>7478165</v>
+        <v>7478058</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6040,7 +6024,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6059,10 +6042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427399</v>
+        <v>124427387</v>
       </c>
       <c r="B54" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6071,38 +6054,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855007</v>
+        <v>855102</v>
       </c>
       <c r="R54" t="n">
-        <v>7478357</v>
+        <v>7478191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,6 +6130,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6161,10 +6149,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427345</v>
+        <v>124427406</v>
       </c>
       <c r="B55" t="n">
-        <v>80064</v>
+        <v>91737</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6173,38 +6161,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854967</v>
+        <v>855096</v>
       </c>
       <c r="R55" t="n">
-        <v>7478177</v>
+        <v>7478199</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6239,12 +6234,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6263,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427403</v>
+        <v>124427345</v>
       </c>
       <c r="B56" t="n">
-        <v>79963</v>
+        <v>80064</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6279,34 +6280,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854946</v>
+        <v>854967</v>
       </c>
       <c r="R56" t="n">
-        <v>7478367</v>
+        <v>7478177</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,7 +6348,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124855475</v>
+        <v>124855464</v>
       </c>
       <c r="B57" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,25 +6378,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854813</v>
+        <v>854898</v>
       </c>
       <c r="R57" t="n">
-        <v>7477923</v>
+        <v>7478156</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124855423</v>
+        <v>124855328</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>56839</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854915</v>
+        <v>854802</v>
       </c>
       <c r="R58" t="n">
-        <v>7477851</v>
+        <v>7477769</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6538,12 +6538,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6570,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124854791</v>
+        <v>124855277</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6587,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854840</v>
+        <v>855068</v>
       </c>
       <c r="R59" t="n">
-        <v>7477716</v>
+        <v>7478046</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6640,12 +6645,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6672,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855328</v>
+        <v>124855358</v>
       </c>
       <c r="B60" t="n">
-        <v>56839</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,25 +6689,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6712,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854802</v>
+        <v>854772</v>
       </c>
       <c r="R60" t="n">
-        <v>7477769</v>
+        <v>7477881</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6742,17 +6747,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6761,6 +6766,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6779,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855420</v>
+        <v>124855240</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6791,25 +6797,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6819,10 +6825,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855071</v>
+        <v>854937</v>
       </c>
       <c r="R61" t="n">
-        <v>7477912</v>
+        <v>7477782</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6849,12 +6855,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6881,10 +6887,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855233</v>
+        <v>124854791</v>
       </c>
       <c r="B62" t="n">
-        <v>105278</v>
+        <v>78947</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6899,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855073</v>
+        <v>854840</v>
       </c>
       <c r="R62" t="n">
-        <v>7477920</v>
+        <v>7477716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,12 +6957,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6983,10 +6989,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855330</v>
+        <v>124855401</v>
       </c>
       <c r="B63" t="n">
-        <v>56839</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6995,46 +7001,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854676</v>
+        <v>854928</v>
       </c>
       <c r="R63" t="n">
-        <v>7477840</v>
+        <v>7477769</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7061,17 +7063,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Spillning med blindtarmstömning.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7080,6 +7077,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7098,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855316</v>
+        <v>124855376</v>
       </c>
       <c r="B64" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7110,38 +7108,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855019</v>
+        <v>854741</v>
       </c>
       <c r="R64" t="n">
-        <v>7477888</v>
+        <v>7477958</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7182,6 +7184,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7200,10 +7203,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855483</v>
+        <v>124855415</v>
       </c>
       <c r="B65" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7212,25 +7215,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7240,10 +7243,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855251</v>
+        <v>854928</v>
       </c>
       <c r="R65" t="n">
-        <v>7478036</v>
+        <v>7478107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855232</v>
+        <v>124855231</v>
       </c>
       <c r="B66" t="n">
         <v>105278</v>
@@ -7342,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855094</v>
+        <v>854954</v>
       </c>
       <c r="R66" t="n">
-        <v>7477931</v>
+        <v>7478125</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7404,10 +7407,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855386</v>
+        <v>124855233</v>
       </c>
       <c r="B67" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7416,42 +7419,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854810</v>
+        <v>855073</v>
       </c>
       <c r="R67" t="n">
-        <v>7477930</v>
+        <v>7477920</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7492,7 +7491,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7511,7 +7509,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855466</v>
+        <v>124855469</v>
       </c>
       <c r="B68" t="n">
         <v>98269</v>
@@ -7551,10 +7549,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854921</v>
+        <v>854979</v>
       </c>
       <c r="R68" t="n">
-        <v>7478082</v>
+        <v>7477885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855464</v>
+        <v>124855244</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7625,25 +7623,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7653,10 +7651,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854898</v>
+        <v>855187</v>
       </c>
       <c r="R69" t="n">
-        <v>7478156</v>
+        <v>7478029</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7715,7 +7713,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855390</v>
+        <v>124855467</v>
       </c>
       <c r="B70" t="n">
         <v>98269</v>
@@ -7748,21 +7746,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854899</v>
+        <v>855062</v>
       </c>
       <c r="R70" t="n">
-        <v>7477831</v>
+        <v>7478002</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7803,7 +7797,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7822,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855512</v>
+        <v>124855394</v>
       </c>
       <c r="B71" t="n">
-        <v>80063</v>
+        <v>98269</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7834,38 +7827,42 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854911</v>
+        <v>854897</v>
       </c>
       <c r="R71" t="n">
-        <v>7478164</v>
+        <v>7477846</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,6 +7903,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8026,7 +8024,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855381</v>
+        <v>124855423</v>
       </c>
       <c r="B73" t="n">
         <v>98269</v>
@@ -8066,10 +8064,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854803</v>
+        <v>854915</v>
       </c>
       <c r="R73" t="n">
-        <v>7477930</v>
+        <v>7477851</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8110,7 +8108,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8129,7 +8126,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855358</v>
+        <v>124855386</v>
       </c>
       <c r="B74" t="n">
         <v>98269</v>
@@ -8162,17 +8159,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854772</v>
+        <v>854810</v>
       </c>
       <c r="R74" t="n">
-        <v>7477881</v>
+        <v>7477930</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8205,11 +8206,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8237,10 +8233,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855524</v>
+        <v>124855329</v>
       </c>
       <c r="B75" t="n">
-        <v>80063</v>
+        <v>56839</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8253,34 +8249,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>102613</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854793</v>
+        <v>854676</v>
       </c>
       <c r="R75" t="n">
-        <v>7477805</v>
+        <v>7477840</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8313,6 +8309,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8339,10 +8340,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855257</v>
+        <v>124855275</v>
       </c>
       <c r="B76" t="n">
-        <v>57635</v>
+        <v>92476</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8355,34 +8356,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854894</v>
+        <v>854889</v>
       </c>
       <c r="R76" t="n">
-        <v>7477768</v>
+        <v>7477847</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8409,17 +8410,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8446,10 +8442,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855359</v>
+        <v>124855318</v>
       </c>
       <c r="B77" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8458,38 +8454,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854838</v>
+        <v>854817</v>
       </c>
       <c r="R77" t="n">
-        <v>7477840</v>
+        <v>7477931</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8524,18 +8520,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8554,10 +8544,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855418</v>
+        <v>124855232</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8566,25 +8556,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8594,10 +8584,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855131</v>
+        <v>855094</v>
       </c>
       <c r="R78" t="n">
-        <v>7477924</v>
+        <v>7477931</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8656,10 +8646,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855401</v>
+        <v>124855536</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8668,42 +8658,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854928</v>
+        <v>854869</v>
       </c>
       <c r="R79" t="n">
-        <v>7477769</v>
+        <v>7477778</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8738,13 +8724,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8763,7 +8753,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855417</v>
+        <v>124855421</v>
       </c>
       <c r="B80" t="n">
         <v>98269</v>
@@ -8803,10 +8793,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855202</v>
+        <v>854951</v>
       </c>
       <c r="R80" t="n">
-        <v>7477976</v>
+        <v>7477899</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8865,10 +8855,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855240</v>
+        <v>124855466</v>
       </c>
       <c r="B81" t="n">
-        <v>105278</v>
+        <v>98269</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8877,25 +8867,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8905,10 +8895,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854937</v>
+        <v>854921</v>
       </c>
       <c r="R81" t="n">
-        <v>7477782</v>
+        <v>7478082</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8935,12 +8925,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8967,10 +8957,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855275</v>
+        <v>124855404</v>
       </c>
       <c r="B82" t="n">
-        <v>92476</v>
+        <v>98269</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8979,38 +8969,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854889</v>
+        <v>854832</v>
       </c>
       <c r="R82" t="n">
-        <v>7477847</v>
+        <v>7477880</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,6 +9045,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9069,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855364</v>
+        <v>124855482</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9081,38 +9076,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855120</v>
+        <v>855134</v>
       </c>
       <c r="R83" t="n">
-        <v>7477887</v>
+        <v>7477890</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9147,18 +9142,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9177,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855404</v>
+        <v>124855313</v>
       </c>
       <c r="B84" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9189,42 +9178,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854832</v>
+        <v>854814</v>
       </c>
       <c r="R84" t="n">
-        <v>7477880</v>
+        <v>7477852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9250,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9284,7 +9268,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855366</v>
+        <v>124855389</v>
       </c>
       <c r="B85" t="n">
         <v>98269</v>
@@ -9319,7 +9303,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9328,10 +9312,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854807</v>
+        <v>854906</v>
       </c>
       <c r="R85" t="n">
-        <v>7477926</v>
+        <v>7477891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9391,10 +9375,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855244</v>
+        <v>124855371</v>
       </c>
       <c r="B86" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9403,38 +9387,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855187</v>
+        <v>854845</v>
       </c>
       <c r="R86" t="n">
-        <v>7478029</v>
+        <v>7477869</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9475,6 +9463,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9493,10 +9482,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855317</v>
+        <v>124855500</v>
       </c>
       <c r="B87" t="n">
-        <v>97153</v>
+        <v>79963</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9509,21 +9498,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>6457</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9533,10 +9522,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854783</v>
+        <v>854850</v>
       </c>
       <c r="R87" t="n">
-        <v>7477935</v>
+        <v>7477915</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9595,10 +9584,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855482</v>
+        <v>124855524</v>
       </c>
       <c r="B88" t="n">
-        <v>78947</v>
+        <v>80063</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9607,20 +9596,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9635,10 +9624,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855134</v>
+        <v>854793</v>
       </c>
       <c r="R88" t="n">
-        <v>7477890</v>
+        <v>7477805</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9665,12 +9654,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9697,10 +9686,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855416</v>
+        <v>124855333</v>
       </c>
       <c r="B89" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9709,25 +9698,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9737,10 +9726,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855002</v>
+        <v>854924</v>
       </c>
       <c r="R89" t="n">
-        <v>7478149</v>
+        <v>7478087</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9799,7 +9788,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124854790</v>
+        <v>124855417</v>
       </c>
       <c r="B90" t="n">
         <v>98269</v>
@@ -9832,21 +9821,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854766</v>
+        <v>855202</v>
       </c>
       <c r="R90" t="n">
-        <v>7478012</v>
+        <v>7477976</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9887,7 +9872,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9906,10 +9890,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855389</v>
+        <v>124855512</v>
       </c>
       <c r="B91" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9918,42 +9902,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854906</v>
+        <v>854911</v>
       </c>
       <c r="R91" t="n">
-        <v>7477891</v>
+        <v>7478164</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9994,7 +9974,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10013,10 +9992,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855250</v>
+        <v>124855257</v>
       </c>
       <c r="B92" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10029,21 +10008,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10053,10 +10032,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854814</v>
+        <v>854894</v>
       </c>
       <c r="R92" t="n">
-        <v>7477852</v>
+        <v>7477768</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10083,12 +10062,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10115,10 +10099,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855318</v>
+        <v>124855364</v>
       </c>
       <c r="B93" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10127,38 +10111,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854817</v>
+        <v>855120</v>
       </c>
       <c r="R93" t="n">
-        <v>7477931</v>
+        <v>7477887</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10193,12 +10177,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10217,7 +10207,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855380</v>
+        <v>124855420</v>
       </c>
       <c r="B94" t="n">
         <v>98269</v>
@@ -10257,10 +10247,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854745</v>
+        <v>855071</v>
       </c>
       <c r="R94" t="n">
-        <v>7477946</v>
+        <v>7477912</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10301,7 +10291,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10320,7 +10309,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855376</v>
+        <v>124855468</v>
       </c>
       <c r="B95" t="n">
         <v>98269</v>
@@ -10353,21 +10342,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854741</v>
+        <v>855069</v>
       </c>
       <c r="R95" t="n">
-        <v>7477958</v>
+        <v>7477999</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10408,7 +10393,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10427,10 +10411,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855313</v>
+        <v>124855475</v>
       </c>
       <c r="B96" t="n">
-        <v>91459</v>
+        <v>56828</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10443,21 +10427,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10467,10 +10451,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854814</v>
+        <v>854813</v>
       </c>
       <c r="R96" t="n">
-        <v>7477852</v>
+        <v>7477923</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10529,10 +10513,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855415</v>
+        <v>124855483</v>
       </c>
       <c r="B97" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10541,25 +10525,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10569,10 +10553,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854928</v>
+        <v>855251</v>
       </c>
       <c r="R97" t="n">
-        <v>7478107</v>
+        <v>7478036</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10631,10 +10615,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855277</v>
+        <v>124855359</v>
       </c>
       <c r="B98" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10643,38 +10627,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855068</v>
+        <v>854838</v>
       </c>
       <c r="R98" t="n">
-        <v>7478046</v>
+        <v>7477840</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10709,12 +10693,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10733,7 +10723,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855371</v>
+        <v>124855390</v>
       </c>
       <c r="B99" t="n">
         <v>98269</v>
@@ -10768,7 +10758,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10777,10 +10767,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854845</v>
+        <v>854899</v>
       </c>
       <c r="R99" t="n">
-        <v>7477869</v>
+        <v>7477831</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10840,7 +10830,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855421</v>
+        <v>124855381</v>
       </c>
       <c r="B100" t="n">
         <v>98269</v>
@@ -10880,10 +10870,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854951</v>
+        <v>854803</v>
       </c>
       <c r="R100" t="n">
-        <v>7477899</v>
+        <v>7477930</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10924,6 +10914,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10942,10 +10933,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855394</v>
+        <v>124855316</v>
       </c>
       <c r="B101" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10954,42 +10945,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854897</v>
+        <v>855019</v>
       </c>
       <c r="R101" t="n">
-        <v>7477846</v>
+        <v>7477888</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11030,7 +11017,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11049,10 +11035,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855536</v>
+        <v>124855416</v>
       </c>
       <c r="B102" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11061,25 +11047,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11089,10 +11075,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854869</v>
+        <v>855002</v>
       </c>
       <c r="R102" t="n">
-        <v>7477778</v>
+        <v>7478149</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11119,17 +11105,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11156,10 +11137,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855333</v>
+        <v>124855366</v>
       </c>
       <c r="B103" t="n">
-        <v>80064</v>
+        <v>98269</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11168,38 +11149,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854924</v>
+        <v>854807</v>
       </c>
       <c r="R103" t="n">
-        <v>7478087</v>
+        <v>7477926</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11240,6 +11225,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11258,10 +11244,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855474</v>
+        <v>124855317</v>
       </c>
       <c r="B104" t="n">
-        <v>56828</v>
+        <v>97153</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11270,25 +11256,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11298,10 +11284,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855065</v>
+        <v>854783</v>
       </c>
       <c r="R104" t="n">
-        <v>7478197</v>
+        <v>7477935</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11360,7 +11346,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855467</v>
+        <v>124855418</v>
       </c>
       <c r="B105" t="n">
         <v>98269</v>
@@ -11400,10 +11386,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855062</v>
+        <v>855131</v>
       </c>
       <c r="R105" t="n">
-        <v>7478002</v>
+        <v>7477924</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11462,10 +11448,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855500</v>
+        <v>124854790</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>98269</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11474,38 +11460,42 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854850</v>
+        <v>854766</v>
       </c>
       <c r="R106" t="n">
-        <v>7477915</v>
+        <v>7478012</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11546,6 +11536,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11564,10 +11555,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855231</v>
+        <v>124855250</v>
       </c>
       <c r="B107" t="n">
-        <v>105278</v>
+        <v>91166</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11576,25 +11567,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11604,10 +11595,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854954</v>
+        <v>854814</v>
       </c>
       <c r="R107" t="n">
-        <v>7478125</v>
+        <v>7477852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11666,7 +11657,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855469</v>
+        <v>124855380</v>
       </c>
       <c r="B108" t="n">
         <v>98269</v>
@@ -11706,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854979</v>
+        <v>854745</v>
       </c>
       <c r="R108" t="n">
-        <v>7477885</v>
+        <v>7477946</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11750,6 +11741,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11768,10 +11760,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855468</v>
+        <v>124855474</v>
       </c>
       <c r="B109" t="n">
-        <v>98269</v>
+        <v>56828</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11780,25 +11772,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11808,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855069</v>
+        <v>855065</v>
       </c>
       <c r="R109" t="n">
-        <v>7477999</v>
+        <v>7478197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427354</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>855018</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478119</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427354</v>
+        <v>124427351</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,38 +4273,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855018</v>
+        <v>855056</v>
       </c>
       <c r="R37" t="n">
-        <v>7478119</v>
+        <v>7478165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4349,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427356</v>
+        <v>124427391</v>
       </c>
       <c r="B42" t="n">
-        <v>80063</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4809,38 +4809,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854977</v>
+        <v>855091</v>
       </c>
       <c r="R42" t="n">
-        <v>7478167</v>
+        <v>7478207</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,6 +4885,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4904,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427391</v>
+        <v>124427388</v>
       </c>
       <c r="B43" t="n">
         <v>98269</v>
@@ -4934,7 +4939,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855091</v>
+        <v>855074</v>
       </c>
       <c r="R43" t="n">
-        <v>7478207</v>
+        <v>7478164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5011,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427388</v>
+        <v>124427356</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5018,42 +5023,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855074</v>
+        <v>854977</v>
       </c>
       <c r="R44" t="n">
-        <v>7478164</v>
+        <v>7478167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5094,7 +5095,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427393</v>
+        <v>124427403</v>
       </c>
       <c r="B46" t="n">
-        <v>56828</v>
+        <v>79963</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5227,25 +5227,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854990</v>
+        <v>854946</v>
       </c>
       <c r="R46" t="n">
-        <v>7478363</v>
+        <v>7478367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5299,6 +5299,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5317,10 +5318,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427403</v>
+        <v>124427393</v>
       </c>
       <c r="B47" t="n">
-        <v>79963</v>
+        <v>56828</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,25 +5330,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5358,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854946</v>
+        <v>854990</v>
       </c>
       <c r="R47" t="n">
-        <v>7478367</v>
+        <v>7478363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5401,7 +5402,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -9064,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855482</v>
+        <v>124855313</v>
       </c>
       <c r="B83" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855134</v>
+        <v>854814</v>
       </c>
       <c r="R83" t="n">
-        <v>7477890</v>
+        <v>7477852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9166,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855313</v>
+        <v>124855482</v>
       </c>
       <c r="B84" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9182,21 +9182,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854814</v>
+        <v>855134</v>
       </c>
       <c r="R84" t="n">
-        <v>7477852</v>
+        <v>7477890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855317</v>
+        <v>124855418</v>
       </c>
       <c r="B104" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11256,25 +11256,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854783</v>
+        <v>855131</v>
       </c>
       <c r="R104" t="n">
-        <v>7477935</v>
+        <v>7477924</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855418</v>
+        <v>124854790</v>
       </c>
       <c r="B105" t="n">
         <v>98269</v>
@@ -11379,17 +11379,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855131</v>
+        <v>854766</v>
       </c>
       <c r="R105" t="n">
-        <v>7477924</v>
+        <v>7478012</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11430,6 +11434,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11448,10 +11453,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124854790</v>
+        <v>124855317</v>
       </c>
       <c r="B106" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11460,42 +11465,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854766</v>
+        <v>854783</v>
       </c>
       <c r="R106" t="n">
-        <v>7478012</v>
+        <v>7477935</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11536,7 +11537,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855277</v>
+        <v>124855358</v>
       </c>
       <c r="B59" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6587,38 +6587,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855068</v>
+        <v>854772</v>
       </c>
       <c r="R59" t="n">
-        <v>7478046</v>
+        <v>7477881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6653,12 +6653,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6677,10 +6683,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855358</v>
+        <v>124855240</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,38 +6695,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854772</v>
+        <v>854937</v>
       </c>
       <c r="R60" t="n">
-        <v>7477881</v>
+        <v>7477782</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6747,17 +6753,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6766,7 +6767,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855240</v>
+        <v>124855277</v>
       </c>
       <c r="B61" t="n">
-        <v>105278</v>
+        <v>80057</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854937</v>
+        <v>855068</v>
       </c>
       <c r="R61" t="n">
-        <v>7477782</v>
+        <v>7478046</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7815,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855394</v>
+        <v>124855329</v>
       </c>
       <c r="B71" t="n">
-        <v>98269</v>
+        <v>56839</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7827,42 +7827,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102613</v>